--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89577B7-76F5-45AB-B2F7-949E484B5C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE80142A-1252-4480-8E44-BDCB3BA0D183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1671,20 +1671,191 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1715,12 +1886,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1766,178 +1931,13 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2416,33 +2416,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="205" t="s">
+      <c r="A1" s="203" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
-      <c r="I1" s="206"/>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="207"/>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="205"/>
       <c r="M1" s="38" t="s">
         <v>70</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="198" t="s">
+      <c r="O1" s="194" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="199"/>
-      <c r="Q1" s="199"/>
-      <c r="R1" s="199"/>
-      <c r="S1" s="200"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="196"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2461,165 +2461,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="80"/>
-      <c r="O2" s="201"/>
-      <c r="P2" s="202"/>
-      <c r="Q2" s="202"/>
-      <c r="R2" s="202"/>
-      <c r="S2" s="203"/>
+      <c r="O2" s="197"/>
+      <c r="P2" s="198"/>
+      <c r="Q2" s="198"/>
+      <c r="R2" s="198"/>
+      <c r="S2" s="199"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="211"/>
-      <c r="C3" s="212"/>
-      <c r="D3" s="213"/>
+      <c r="B3" s="209"/>
+      <c r="C3" s="210"/>
+      <c r="D3" s="211"/>
       <c r="H3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="218"/>
-      <c r="J3" s="219"/>
-      <c r="K3" s="220"/>
+      <c r="I3" s="216"/>
+      <c r="J3" s="217"/>
+      <c r="K3" s="218"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="73"/>
-      <c r="O3" s="208"/>
-      <c r="P3" s="209"/>
-      <c r="Q3" s="209"/>
-      <c r="R3" s="209"/>
-      <c r="S3" s="210"/>
+      <c r="O3" s="206"/>
+      <c r="P3" s="207"/>
+      <c r="Q3" s="207"/>
+      <c r="R3" s="207"/>
+      <c r="S3" s="208"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="192"/>
-      <c r="C4" s="193"/>
-      <c r="D4" s="194"/>
+      <c r="B4" s="188"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="190"/>
       <c r="H4" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="195"/>
-      <c r="J4" s="196"/>
-      <c r="K4" s="197"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="192"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="73"/>
-      <c r="O4" s="208"/>
-      <c r="P4" s="209"/>
-      <c r="Q4" s="209"/>
-      <c r="R4" s="209"/>
-      <c r="S4" s="210"/>
+      <c r="O4" s="206"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="208"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="214"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="216"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="H5" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="217"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="210"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="207"/>
+      <c r="K5" s="208"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="73"/>
-      <c r="O5" s="208"/>
-      <c r="P5" s="209"/>
-      <c r="Q5" s="209"/>
-      <c r="R5" s="209"/>
-      <c r="S5" s="210"/>
+      <c r="O5" s="206"/>
+      <c r="P5" s="207"/>
+      <c r="Q5" s="207"/>
+      <c r="R5" s="207"/>
+      <c r="S5" s="208"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="171"/>
-      <c r="C6" s="172"/>
-      <c r="D6" s="173"/>
+      <c r="B6" s="223"/>
+      <c r="C6" s="224"/>
+      <c r="D6" s="225"/>
       <c r="H6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="174"/>
-      <c r="J6" s="175"/>
-      <c r="K6" s="176"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="201"/>
+      <c r="K6" s="202"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="74"/>
-      <c r="O6" s="204"/>
-      <c r="P6" s="175"/>
-      <c r="Q6" s="175"/>
-      <c r="R6" s="175"/>
-      <c r="S6" s="176"/>
+      <c r="O6" s="200"/>
+      <c r="P6" s="201"/>
+      <c r="Q6" s="201"/>
+      <c r="R6" s="201"/>
+      <c r="S6" s="202"/>
     </row>
     <row r="7" spans="1:19" s="50" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="177" t="s">
+      <c r="A8" s="227" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="178"/>
-      <c r="C8" s="178"/>
-      <c r="D8" s="179"/>
-      <c r="F8" s="183" t="s">
+      <c r="B8" s="228"/>
+      <c r="C8" s="228"/>
+      <c r="D8" s="229"/>
+      <c r="F8" s="233" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="184"/>
-      <c r="H8" s="184"/>
-      <c r="I8" s="184"/>
-      <c r="J8" s="184"/>
-      <c r="K8" s="184"/>
-      <c r="L8" s="184"/>
-      <c r="M8" s="184"/>
-      <c r="N8" s="184"/>
-      <c r="O8" s="184"/>
-      <c r="P8" s="184"/>
-      <c r="Q8" s="184"/>
-      <c r="R8" s="184"/>
-      <c r="S8" s="189"/>
+      <c r="G8" s="234"/>
+      <c r="H8" s="234"/>
+      <c r="I8" s="234"/>
+      <c r="J8" s="234"/>
+      <c r="K8" s="234"/>
+      <c r="L8" s="234"/>
+      <c r="M8" s="234"/>
+      <c r="N8" s="234"/>
+      <c r="O8" s="234"/>
+      <c r="P8" s="234"/>
+      <c r="Q8" s="234"/>
+      <c r="R8" s="234"/>
+      <c r="S8" s="239"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="180"/>
-      <c r="B9" s="181"/>
-      <c r="C9" s="181"/>
-      <c r="D9" s="182"/>
-      <c r="F9" s="229" t="s">
+      <c r="A9" s="230"/>
+      <c r="B9" s="231"/>
+      <c r="C9" s="231"/>
+      <c r="D9" s="232"/>
+      <c r="F9" s="170" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="230"/>
-      <c r="H9" s="243" t="s">
+      <c r="G9" s="171"/>
+      <c r="H9" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="244"/>
-      <c r="J9" s="227" t="s">
+      <c r="I9" s="187"/>
+      <c r="J9" s="168" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="228"/>
-      <c r="L9" s="190" t="s">
+      <c r="K9" s="169"/>
+      <c r="L9" s="240" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="191"/>
-      <c r="N9" s="187" t="s">
+      <c r="M9" s="241"/>
+      <c r="N9" s="237" t="s">
         <v>80</v>
       </c>
-      <c r="O9" s="188"/>
-      <c r="P9" s="185" t="s">
+      <c r="O9" s="238"/>
+      <c r="P9" s="235" t="s">
         <v>68</v>
       </c>
-      <c r="Q9" s="186"/>
-      <c r="R9" s="187" t="s">
+      <c r="Q9" s="236"/>
+      <c r="R9" s="237" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="188"/>
+      <c r="S9" s="238"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="234" t="s">
+      <c r="A10" s="175" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2676,7 +2676,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="235"/>
+      <c r="A11" s="176"/>
       <c r="B11" s="56" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2767,7 +2767,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="235"/>
+      <c r="A12" s="176"/>
       <c r="B12" s="108" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -2859,7 +2859,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="235"/>
+      <c r="A13" s="176"/>
       <c r="B13" s="108" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -2955,7 +2955,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="235"/>
+      <c r="A14" s="176"/>
       <c r="B14" s="108" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3051,7 +3051,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="235"/>
+      <c r="A15" s="176"/>
       <c r="B15" s="108" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3147,7 +3147,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="235"/>
+      <c r="A16" s="176"/>
       <c r="B16" s="108" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3243,7 +3243,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="235"/>
+      <c r="A17" s="176"/>
       <c r="B17" s="108" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3339,7 +3339,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="235"/>
+      <c r="A18" s="176"/>
       <c r="B18" s="108" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3435,7 +3435,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="235"/>
+      <c r="A19" s="176"/>
       <c r="B19" s="108" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3531,7 +3531,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="235"/>
+      <c r="A20" s="176"/>
       <c r="B20" s="108" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3627,7 +3627,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="235"/>
+      <c r="A21" s="176"/>
       <c r="B21" s="108" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3723,7 +3723,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="236"/>
+      <c r="A22" s="177"/>
       <c r="B22" s="108" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3864,7 +3864,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="234" t="s">
+      <c r="A24" s="175" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="56" t="str">
@@ -3962,7 +3962,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="235"/>
+      <c r="A25" s="176"/>
       <c r="B25" s="67" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4058,7 +4058,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="235"/>
+      <c r="A26" s="176"/>
       <c r="B26" s="67" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4154,7 +4154,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="235"/>
+      <c r="A27" s="176"/>
       <c r="B27" s="67" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="237"/>
+      <c r="A28" s="178"/>
       <c r="B28" s="67" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4477,7 +4477,7 @@
       <c r="S31" s="160"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="224" t="s">
+      <c r="A32" s="165" t="s">
         <v>78</v>
       </c>
       <c r="B32" s="56" t="str" cm="1">
@@ -4564,7 +4564,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="225"/>
+      <c r="A33" s="166"/>
       <c r="B33" s="67" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4649,7 +4649,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="226"/>
+      <c r="A34" s="167"/>
       <c r="B34" s="67" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4773,7 +4773,7 @@
       <c r="S35" s="161"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="224" t="s">
+      <c r="A36" s="165" t="s">
         <v>79</v>
       </c>
       <c r="B36" s="56" t="str" cm="1">
@@ -4860,7 +4860,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="225"/>
+      <c r="A37" s="166"/>
       <c r="B37" s="67" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4945,7 +4945,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="226"/>
+      <c r="A38" s="167"/>
       <c r="B38" s="68" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5044,7 +5044,7 @@
       <c r="Q39" s="61"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="234" t="s">
+      <c r="A40" s="175" t="s">
         <v>50</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5056,25 +5056,25 @@
       <c r="D40" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="231" t="s">
+      <c r="F40" s="172" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="232"/>
-      <c r="H40" s="232"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="232"/>
-      <c r="O40" s="232"/>
-      <c r="P40" s="232"/>
-      <c r="Q40" s="232"/>
-      <c r="R40" s="232"/>
-      <c r="S40" s="233"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="173"/>
+      <c r="I40" s="173"/>
+      <c r="J40" s="173"/>
+      <c r="K40" s="173"/>
+      <c r="L40" s="173"/>
+      <c r="M40" s="173"/>
+      <c r="N40" s="173"/>
+      <c r="O40" s="173"/>
+      <c r="P40" s="173"/>
+      <c r="Q40" s="173"/>
+      <c r="R40" s="173"/>
+      <c r="S40" s="174"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="235"/>
+      <c r="A41" s="176"/>
       <c r="B41" s="35" t="s">
         <v>81</v>
       </c>
@@ -5137,7 +5137,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="235"/>
+      <c r="A42" s="176"/>
       <c r="B42" s="49" t="s">
         <v>88</v>
       </c>
@@ -5162,13 +5162,13 @@
       <c r="P42" s="66"/>
       <c r="Q42" s="78"/>
       <c r="R42" s="79"/>
-      <c r="S42" s="165">
+      <c r="S42" s="179">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="235"/>
+      <c r="A43" s="176"/>
       <c r="B43" s="49" t="s">
         <v>82</v>
       </c>
@@ -5180,26 +5180,26 @@
         <v>54</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="183" t="str">
+      <c r="F43" s="233" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="184"/>
-      <c r="H43" s="184"/>
-      <c r="I43" s="184"/>
-      <c r="J43" s="184"/>
-      <c r="K43" s="184"/>
-      <c r="L43" s="184"/>
-      <c r="M43" s="184"/>
-      <c r="N43" s="184"/>
-      <c r="O43" s="184"/>
-      <c r="P43" s="184"/>
-      <c r="Q43" s="184"/>
-      <c r="R43" s="184"/>
-      <c r="S43" s="238"/>
+      <c r="G43" s="234"/>
+      <c r="H43" s="234"/>
+      <c r="I43" s="234"/>
+      <c r="J43" s="234"/>
+      <c r="K43" s="234"/>
+      <c r="L43" s="234"/>
+      <c r="M43" s="234"/>
+      <c r="N43" s="234"/>
+      <c r="O43" s="234"/>
+      <c r="P43" s="234"/>
+      <c r="Q43" s="234"/>
+      <c r="R43" s="234"/>
+      <c r="S43" s="180"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="235"/>
+      <c r="A44" s="176"/>
       <c r="B44" s="49" t="s">
         <v>87</v>
       </c>
@@ -5255,7 +5255,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="235"/>
+      <c r="A45" s="176"/>
       <c r="B45" s="33" t="s">
         <v>89</v>
       </c>
@@ -5389,7 +5389,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="235"/>
+      <c r="A46" s="176"/>
       <c r="B46" s="33" t="s">
         <v>83</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="235"/>
+      <c r="A47" s="176"/>
       <c r="B47" s="33" t="s">
         <v>84</v>
       </c>
@@ -5414,31 +5414,31 @@
       <c r="D47" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="165" t="s">
+      <c r="F47" s="179" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="169" t="str">
+      <c r="G47" s="221" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="165" t="s">
+      <c r="J47" s="179" t="s">
         <v>86</v>
       </c>
-      <c r="K47" s="167">
+      <c r="K47" s="219">
         <v>1</v>
       </c>
-      <c r="N47" s="165" t="s">
+      <c r="N47" s="179" t="s">
         <v>108</v>
       </c>
-      <c r="O47" s="239"/>
-      <c r="P47" s="240"/>
-      <c r="R47" s="165" t="s">
+      <c r="O47" s="182"/>
+      <c r="P47" s="183"/>
+      <c r="R47" s="179" t="s">
         <v>114</v>
       </c>
-      <c r="S47" s="165"/>
+      <c r="S47" s="179"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="237"/>
+      <c r="A48" s="178"/>
       <c r="B48" s="36" t="s">
         <v>85</v>
       </c>
@@ -5449,15 +5449,15 @@
       <c r="D48" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="F48" s="166"/>
-      <c r="G48" s="170"/>
-      <c r="J48" s="166"/>
-      <c r="K48" s="168"/>
-      <c r="N48" s="238"/>
-      <c r="O48" s="241"/>
-      <c r="P48" s="242"/>
-      <c r="R48" s="238"/>
-      <c r="S48" s="166"/>
+      <c r="F48" s="181"/>
+      <c r="G48" s="222"/>
+      <c r="J48" s="181"/>
+      <c r="K48" s="220"/>
+      <c r="N48" s="180"/>
+      <c r="O48" s="184"/>
+      <c r="P48" s="185"/>
+      <c r="R48" s="180"/>
+      <c r="S48" s="181"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5466,7 +5466,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="221" t="s">
+      <c r="A50" s="162" t="s">
         <v>65</v>
       </c>
       <c r="B50" s="134"/>
@@ -5489,7 +5489,7 @@
       <c r="S50" s="136"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="222"/>
+      <c r="A51" s="163"/>
       <c r="B51" s="137"/>
       <c r="C51" s="139"/>
       <c r="D51" s="139"/>
@@ -5510,7 +5510,7 @@
       <c r="S51" s="138"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="222"/>
+      <c r="A52" s="163"/>
       <c r="B52" s="137"/>
       <c r="C52" s="139"/>
       <c r="D52" s="139"/>
@@ -5531,7 +5531,7 @@
       <c r="S52" s="138"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="222"/>
+      <c r="A53" s="163"/>
       <c r="B53" s="137"/>
       <c r="C53" s="139"/>
       <c r="D53" s="139"/>
@@ -5552,7 +5552,7 @@
       <c r="S53" s="138"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="222"/>
+      <c r="A54" s="163"/>
       <c r="B54" s="137"/>
       <c r="C54" s="139"/>
       <c r="D54" s="139"/>
@@ -5573,7 +5573,7 @@
       <c r="S54" s="138"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="222"/>
+      <c r="A55" s="163"/>
       <c r="B55" s="137"/>
       <c r="C55" s="139"/>
       <c r="D55" s="139"/>
@@ -5594,7 +5594,7 @@
       <c r="S55" s="138"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="222"/>
+      <c r="A56" s="163"/>
       <c r="B56" s="137"/>
       <c r="C56" s="139"/>
       <c r="D56" s="139"/>
@@ -5615,7 +5615,7 @@
       <c r="S56" s="138"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="222"/>
+      <c r="A57" s="163"/>
       <c r="B57" s="137"/>
       <c r="C57" s="139"/>
       <c r="D57" s="139"/>
@@ -5636,57 +5636,57 @@
       <c r="S57" s="138"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="222"/>
+      <c r="A58" s="163"/>
       <c r="B58" s="140"/>
       <c r="S58" s="141"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="222"/>
+      <c r="A59" s="163"/>
       <c r="B59" s="140"/>
       <c r="S59" s="141"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="222"/>
+      <c r="A60" s="163"/>
       <c r="B60" s="140"/>
       <c r="S60" s="141"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="222"/>
+      <c r="A61" s="163"/>
       <c r="B61" s="140"/>
       <c r="S61" s="141"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="222"/>
+      <c r="A62" s="163"/>
       <c r="B62" s="140"/>
       <c r="S62" s="141"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="222"/>
+      <c r="A63" s="163"/>
       <c r="B63" s="140"/>
       <c r="S63" s="141"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="222"/>
+      <c r="A64" s="163"/>
       <c r="B64" s="140"/>
       <c r="S64" s="141"/>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="222"/>
+      <c r="A65" s="163"/>
       <c r="B65" s="140"/>
       <c r="S65" s="141"/>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="222"/>
+      <c r="A66" s="163"/>
       <c r="B66" s="140"/>
       <c r="S66" s="141"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="222"/>
+      <c r="A67" s="163"/>
       <c r="B67" s="140"/>
       <c r="S67" s="141"/>
     </row>
     <row r="68" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A68" s="223"/>
+      <c r="A68" s="164"/>
       <c r="B68" s="142"/>
       <c r="C68" s="77"/>
       <c r="D68" s="77"/>
@@ -5708,6 +5708,31 @@
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A68"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A36:A38"/>
@@ -5724,31 +5749,6 @@
     <mergeCell ref="O47:P48"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="F47:F48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="F43:R43"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L9:M9"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8922,18 +8922,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customFormat="1">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="242" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="162"/>
-      <c r="J1" s="162"/>
+      <c r="B1" s="242"/>
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="242"/>
+      <c r="H1" s="242"/>
+      <c r="I1" s="242"/>
+      <c r="J1" s="242"/>
       <c r="K1" s="12"/>
       <c r="L1" s="5"/>
     </row>
@@ -8954,15 +8954,15 @@
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="163">
+      <c r="B3" s="243">
         <f>Fisa!B3:D3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -8973,11 +8973,11 @@
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="164">
+      <c r="B4" s="244">
         <f>Fisa!B6</f>
         <v>0</v>
       </c>
-      <c r="C4" s="164"/>
+      <c r="C4" s="244"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -12311,7 +12311,7 @@
         <v/>
       </c>
       <c r="I2">
-        <f>ROUNDUP(E2*1.03,0)</f>
+        <f>ROUNDUP(E2*1.05,0)</f>
         <v>0</v>
       </c>
       <c r="J2" t="str">
@@ -12335,7 +12335,7 @@
         <v/>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I23" si="2">ROUNDUP(E3*1.03,0)</f>
+        <f t="shared" ref="I3:I23" si="2">ROUNDUP(E3*1.05,0)</f>
         <v>0</v>
       </c>
       <c r="J3" t="str">

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE80142A-1252-4480-8E44-BDCB3BA0D183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CEFA8A-8D3A-4A91-9701-E7AECA6000B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="116">
   <si>
     <t>FIRMA:</t>
   </si>
@@ -1671,82 +1671,90 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1794,12 +1802,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1857,78 +1859,76 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2416,33 +2416,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="202" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="205"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="203"/>
+      <c r="L1" s="204"/>
       <c r="M1" s="38" t="s">
         <v>70</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="194" t="s">
+      <c r="O1" s="195" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="196"/>
+      <c r="P1" s="196"/>
+      <c r="Q1" s="196"/>
+      <c r="R1" s="196"/>
+      <c r="S1" s="197"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2461,165 +2461,167 @@
         <v>1</v>
       </c>
       <c r="N2" s="80"/>
-      <c r="O2" s="197"/>
-      <c r="P2" s="198"/>
-      <c r="Q2" s="198"/>
-      <c r="R2" s="198"/>
-      <c r="S2" s="199"/>
+      <c r="O2" s="198"/>
+      <c r="P2" s="199"/>
+      <c r="Q2" s="199"/>
+      <c r="R2" s="199"/>
+      <c r="S2" s="200"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="209"/>
-      <c r="C3" s="210"/>
-      <c r="D3" s="211"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
       <c r="H3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="216"/>
-      <c r="J3" s="217"/>
-      <c r="K3" s="218"/>
+      <c r="I3" s="215" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="216"/>
+      <c r="K3" s="217"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="73"/>
-      <c r="O3" s="206"/>
-      <c r="P3" s="207"/>
-      <c r="Q3" s="207"/>
-      <c r="R3" s="207"/>
-      <c r="S3" s="208"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="206"/>
+      <c r="Q3" s="206"/>
+      <c r="R3" s="206"/>
+      <c r="S3" s="207"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="188"/>
-      <c r="C4" s="189"/>
-      <c r="D4" s="190"/>
+      <c r="B4" s="189"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="191"/>
       <c r="H4" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="191"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="73"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="207"/>
-      <c r="Q4" s="207"/>
-      <c r="R4" s="207"/>
-      <c r="S4" s="208"/>
+      <c r="O4" s="205"/>
+      <c r="P4" s="206"/>
+      <c r="Q4" s="206"/>
+      <c r="R4" s="206"/>
+      <c r="S4" s="207"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="212"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="214"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="H5" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="215"/>
-      <c r="J5" s="207"/>
-      <c r="K5" s="208"/>
+      <c r="I5" s="214"/>
+      <c r="J5" s="206"/>
+      <c r="K5" s="207"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="73"/>
-      <c r="O5" s="206"/>
-      <c r="P5" s="207"/>
-      <c r="Q5" s="207"/>
-      <c r="R5" s="207"/>
-      <c r="S5" s="208"/>
+      <c r="O5" s="205"/>
+      <c r="P5" s="206"/>
+      <c r="Q5" s="206"/>
+      <c r="R5" s="206"/>
+      <c r="S5" s="207"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="223"/>
-      <c r="C6" s="224"/>
-      <c r="D6" s="225"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="170"/>
       <c r="H6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="226"/>
-      <c r="J6" s="201"/>
-      <c r="K6" s="202"/>
+      <c r="I6" s="171"/>
+      <c r="J6" s="172"/>
+      <c r="K6" s="173"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="74"/>
-      <c r="O6" s="200"/>
-      <c r="P6" s="201"/>
-      <c r="Q6" s="201"/>
-      <c r="R6" s="201"/>
-      <c r="S6" s="202"/>
+      <c r="O6" s="201"/>
+      <c r="P6" s="172"/>
+      <c r="Q6" s="172"/>
+      <c r="R6" s="172"/>
+      <c r="S6" s="173"/>
     </row>
     <row r="7" spans="1:19" s="50" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="227" t="s">
+      <c r="A8" s="174" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="228"/>
-      <c r="C8" s="228"/>
-      <c r="D8" s="229"/>
-      <c r="F8" s="233" t="s">
+      <c r="B8" s="175"/>
+      <c r="C8" s="175"/>
+      <c r="D8" s="176"/>
+      <c r="F8" s="180" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="234"/>
-      <c r="H8" s="234"/>
-      <c r="I8" s="234"/>
-      <c r="J8" s="234"/>
-      <c r="K8" s="234"/>
-      <c r="L8" s="234"/>
-      <c r="M8" s="234"/>
-      <c r="N8" s="234"/>
-      <c r="O8" s="234"/>
-      <c r="P8" s="234"/>
-      <c r="Q8" s="234"/>
-      <c r="R8" s="234"/>
-      <c r="S8" s="239"/>
+      <c r="G8" s="181"/>
+      <c r="H8" s="181"/>
+      <c r="I8" s="181"/>
+      <c r="J8" s="181"/>
+      <c r="K8" s="181"/>
+      <c r="L8" s="181"/>
+      <c r="M8" s="181"/>
+      <c r="N8" s="181"/>
+      <c r="O8" s="181"/>
+      <c r="P8" s="181"/>
+      <c r="Q8" s="181"/>
+      <c r="R8" s="181"/>
+      <c r="S8" s="186"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="230"/>
-      <c r="B9" s="231"/>
-      <c r="C9" s="231"/>
-      <c r="D9" s="232"/>
-      <c r="F9" s="170" t="s">
+      <c r="A9" s="177"/>
+      <c r="B9" s="178"/>
+      <c r="C9" s="178"/>
+      <c r="D9" s="179"/>
+      <c r="F9" s="226" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="171"/>
-      <c r="H9" s="186" t="s">
+      <c r="G9" s="227"/>
+      <c r="H9" s="240" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="187"/>
-      <c r="J9" s="168" t="s">
+      <c r="I9" s="241"/>
+      <c r="J9" s="224" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="169"/>
-      <c r="L9" s="240" t="s">
+      <c r="K9" s="225"/>
+      <c r="L9" s="187" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="241"/>
-      <c r="N9" s="237" t="s">
+      <c r="M9" s="188"/>
+      <c r="N9" s="184" t="s">
         <v>80</v>
       </c>
-      <c r="O9" s="238"/>
-      <c r="P9" s="235" t="s">
+      <c r="O9" s="185"/>
+      <c r="P9" s="182" t="s">
         <v>68</v>
       </c>
-      <c r="Q9" s="236"/>
-      <c r="R9" s="237" t="s">
+      <c r="Q9" s="183"/>
+      <c r="R9" s="184" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="238"/>
+      <c r="S9" s="185"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="175" t="s">
+      <c r="A10" s="231" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2676,7 +2678,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="176"/>
+      <c r="A11" s="232"/>
       <c r="B11" s="56" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2753,21 +2755,15 @@
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="Q11" s="29" t="str">
-        <f>IFERROR(IF(AND(P11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
-        <v/>
-      </c>
+      <c r="Q11" s="29"/>
       <c r="R11" s="56" t="str">
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="S11" s="29" t="str">
-        <f>IFERROR(IF(AND(R11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R11,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R11,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
-        <v/>
-      </c>
+      <c r="S11" s="29"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="176"/>
+      <c r="A12" s="232"/>
       <c r="B12" s="108" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -2853,13 +2849,10 @@
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
-      <c r="S12" s="30" t="str">
-        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(R12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R12,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R12,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
-        <v/>
-      </c>
+      <c r="S12" s="30"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="176"/>
+      <c r="A13" s="232"/>
       <c r="B13" s="108" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -2955,7 +2948,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="176"/>
+      <c r="A14" s="232"/>
       <c r="B14" s="108" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3051,7 +3044,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="176"/>
+      <c r="A15" s="232"/>
       <c r="B15" s="108" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3147,7 +3140,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="176"/>
+      <c r="A16" s="232"/>
       <c r="B16" s="108" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3243,7 +3236,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="176"/>
+      <c r="A17" s="232"/>
       <c r="B17" s="108" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3339,7 +3332,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="176"/>
+      <c r="A18" s="232"/>
       <c r="B18" s="108" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3435,7 +3428,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="176"/>
+      <c r="A19" s="232"/>
       <c r="B19" s="108" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3531,7 +3524,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="176"/>
+      <c r="A20" s="232"/>
       <c r="B20" s="108" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3627,7 +3620,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="176"/>
+      <c r="A21" s="232"/>
       <c r="B21" s="108" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3723,7 +3716,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="177"/>
+      <c r="A22" s="233"/>
       <c r="B22" s="108" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3864,26 +3857,11 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="175" t="s">
+      <c r="A24" s="231" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="56" t="str">
-        <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C24" s="58" t="str" cm="1">
-        <f t="array" ref="C24">IFERROR(
-  IF(D24="buc",
-    IF(B24&lt;&gt;"",
-      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B24)*(Deco!$W$2:$W$99="MDF"), 0)),
-    ""),
-    IF(AND(B24&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B24)*(Deco!$W$2:$W$99="MDF"), 0))="MDF"),
-      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B24)*(Deco!$W$2:$W$99="MDF"), 0)),
-    "")
-  ),
-"")</f>
-        <v/>
-      </c>
+      <c r="B24" s="56"/>
+      <c r="C24" s="58"/>
       <c r="D24" s="37" t="str" cm="1">
         <f t="array" ref="D24">IF(I3="Debitare căntuire", IF(OR(RIGHT(B24,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(B24,2)="SM",RIGHT(B24,2)="PM",RIGHT(B24,2)="PG",RIGHT(B24,2)="mm",RIGHT(B24,2)="mp",RIGHT(B24,2)="PA",RIGHT(B24,2)="3D"),"buc","mp"), "mp")</f>
         <v>mp</v>
@@ -3962,7 +3940,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="176"/>
+      <c r="A25" s="232"/>
       <c r="B25" s="67" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4058,7 +4036,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="176"/>
+      <c r="A26" s="232"/>
       <c r="B26" s="67" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4154,7 +4132,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="176"/>
+      <c r="A27" s="232"/>
       <c r="B27" s="67" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4228,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="178"/>
+      <c r="A28" s="234"/>
       <c r="B28" s="67" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4401,7 +4379,7 @@
       </c>
       <c r="D30" s="29" t="str">
         <f>IF(I3="Debitare căntuire", "buc", "mp")</f>
-        <v>mp</v>
+        <v>buc</v>
       </c>
       <c r="E30" s="48"/>
       <c r="F30" s="150"/>
@@ -4477,7 +4455,7 @@
       <c r="S31" s="160"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="165" t="s">
+      <c r="A32" s="221" t="s">
         <v>78</v>
       </c>
       <c r="B32" s="56" t="str" cm="1">
@@ -4564,7 +4542,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="166"/>
+      <c r="A33" s="222"/>
       <c r="B33" s="67" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4649,7 +4627,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="167"/>
+      <c r="A34" s="223"/>
       <c r="B34" s="67" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4773,7 +4751,7 @@
       <c r="S35" s="161"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="165" t="s">
+      <c r="A36" s="221" t="s">
         <v>79</v>
       </c>
       <c r="B36" s="56" t="str" cm="1">
@@ -4860,7 +4838,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="166"/>
+      <c r="A37" s="222"/>
       <c r="B37" s="67" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4945,7 +4923,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="167"/>
+      <c r="A38" s="223"/>
       <c r="B38" s="68" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5044,7 +5022,7 @@
       <c r="Q39" s="61"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="175" t="s">
+      <c r="A40" s="231" t="s">
         <v>50</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5056,25 +5034,25 @@
       <c r="D40" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="172" t="s">
+      <c r="F40" s="228" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="173"/>
-      <c r="H40" s="173"/>
-      <c r="I40" s="173"/>
-      <c r="J40" s="173"/>
-      <c r="K40" s="173"/>
-      <c r="L40" s="173"/>
-      <c r="M40" s="173"/>
-      <c r="N40" s="173"/>
-      <c r="O40" s="173"/>
-      <c r="P40" s="173"/>
-      <c r="Q40" s="173"/>
-      <c r="R40" s="173"/>
-      <c r="S40" s="174"/>
+      <c r="G40" s="229"/>
+      <c r="H40" s="229"/>
+      <c r="I40" s="229"/>
+      <c r="J40" s="229"/>
+      <c r="K40" s="229"/>
+      <c r="L40" s="229"/>
+      <c r="M40" s="229"/>
+      <c r="N40" s="229"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="229"/>
+      <c r="Q40" s="229"/>
+      <c r="R40" s="229"/>
+      <c r="S40" s="230"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="176"/>
+      <c r="A41" s="232"/>
       <c r="B41" s="35" t="s">
         <v>81</v>
       </c>
@@ -5137,7 +5115,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="176"/>
+      <c r="A42" s="232"/>
       <c r="B42" s="49" t="s">
         <v>88</v>
       </c>
@@ -5162,13 +5140,13 @@
       <c r="P42" s="66"/>
       <c r="Q42" s="78"/>
       <c r="R42" s="79"/>
-      <c r="S42" s="179">
+      <c r="S42" s="162">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="176"/>
+      <c r="A43" s="232"/>
       <c r="B43" s="49" t="s">
         <v>82</v>
       </c>
@@ -5180,26 +5158,26 @@
         <v>54</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="233" t="str">
+      <c r="F43" s="180" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="234"/>
-      <c r="H43" s="234"/>
-      <c r="I43" s="234"/>
-      <c r="J43" s="234"/>
-      <c r="K43" s="234"/>
-      <c r="L43" s="234"/>
-      <c r="M43" s="234"/>
-      <c r="N43" s="234"/>
-      <c r="O43" s="234"/>
-      <c r="P43" s="234"/>
-      <c r="Q43" s="234"/>
-      <c r="R43" s="234"/>
-      <c r="S43" s="180"/>
+      <c r="G43" s="181"/>
+      <c r="H43" s="181"/>
+      <c r="I43" s="181"/>
+      <c r="J43" s="181"/>
+      <c r="K43" s="181"/>
+      <c r="L43" s="181"/>
+      <c r="M43" s="181"/>
+      <c r="N43" s="181"/>
+      <c r="O43" s="181"/>
+      <c r="P43" s="181"/>
+      <c r="Q43" s="181"/>
+      <c r="R43" s="181"/>
+      <c r="S43" s="235"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="176"/>
+      <c r="A44" s="232"/>
       <c r="B44" s="49" t="s">
         <v>87</v>
       </c>
@@ -5255,7 +5233,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="176"/>
+      <c r="A45" s="232"/>
       <c r="B45" s="33" t="s">
         <v>89</v>
       </c>
@@ -5389,7 +5367,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="176"/>
+      <c r="A46" s="232"/>
       <c r="B46" s="33" t="s">
         <v>83</v>
       </c>
@@ -5403,7 +5381,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="176"/>
+      <c r="A47" s="232"/>
       <c r="B47" s="33" t="s">
         <v>84</v>
       </c>
@@ -5414,31 +5392,31 @@
       <c r="D47" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="179" t="s">
+      <c r="F47" s="162" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="221" t="str">
+      <c r="G47" s="166" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="179" t="s">
+      <c r="J47" s="162" t="s">
         <v>86</v>
       </c>
-      <c r="K47" s="219">
+      <c r="K47" s="164">
         <v>1</v>
       </c>
-      <c r="N47" s="179" t="s">
+      <c r="N47" s="162" t="s">
         <v>108</v>
       </c>
-      <c r="O47" s="182"/>
-      <c r="P47" s="183"/>
-      <c r="R47" s="179" t="s">
+      <c r="O47" s="236"/>
+      <c r="P47" s="237"/>
+      <c r="R47" s="162" t="s">
         <v>114</v>
       </c>
-      <c r="S47" s="179"/>
+      <c r="S47" s="162"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="178"/>
+      <c r="A48" s="234"/>
       <c r="B48" s="36" t="s">
         <v>85</v>
       </c>
@@ -5449,15 +5427,15 @@
       <c r="D48" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="F48" s="181"/>
-      <c r="G48" s="222"/>
-      <c r="J48" s="181"/>
-      <c r="K48" s="220"/>
-      <c r="N48" s="180"/>
-      <c r="O48" s="184"/>
-      <c r="P48" s="185"/>
-      <c r="R48" s="180"/>
-      <c r="S48" s="181"/>
+      <c r="F48" s="163"/>
+      <c r="G48" s="167"/>
+      <c r="J48" s="163"/>
+      <c r="K48" s="165"/>
+      <c r="N48" s="235"/>
+      <c r="O48" s="238"/>
+      <c r="P48" s="239"/>
+      <c r="R48" s="235"/>
+      <c r="S48" s="163"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5466,7 +5444,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="162" t="s">
+      <c r="A50" s="218" t="s">
         <v>65</v>
       </c>
       <c r="B50" s="134"/>
@@ -5489,7 +5467,7 @@
       <c r="S50" s="136"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="163"/>
+      <c r="A51" s="219"/>
       <c r="B51" s="137"/>
       <c r="C51" s="139"/>
       <c r="D51" s="139"/>
@@ -5510,7 +5488,7 @@
       <c r="S51" s="138"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="163"/>
+      <c r="A52" s="219"/>
       <c r="B52" s="137"/>
       <c r="C52" s="139"/>
       <c r="D52" s="139"/>
@@ -5531,7 +5509,7 @@
       <c r="S52" s="138"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="163"/>
+      <c r="A53" s="219"/>
       <c r="B53" s="137"/>
       <c r="C53" s="139"/>
       <c r="D53" s="139"/>
@@ -5552,7 +5530,7 @@
       <c r="S53" s="138"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="163"/>
+      <c r="A54" s="219"/>
       <c r="B54" s="137"/>
       <c r="C54" s="139"/>
       <c r="D54" s="139"/>
@@ -5573,7 +5551,7 @@
       <c r="S54" s="138"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="163"/>
+      <c r="A55" s="219"/>
       <c r="B55" s="137"/>
       <c r="C55" s="139"/>
       <c r="D55" s="139"/>
@@ -5594,7 +5572,7 @@
       <c r="S55" s="138"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="163"/>
+      <c r="A56" s="219"/>
       <c r="B56" s="137"/>
       <c r="C56" s="139"/>
       <c r="D56" s="139"/>
@@ -5615,7 +5593,7 @@
       <c r="S56" s="138"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="163"/>
+      <c r="A57" s="219"/>
       <c r="B57" s="137"/>
       <c r="C57" s="139"/>
       <c r="D57" s="139"/>
@@ -5636,57 +5614,57 @@
       <c r="S57" s="138"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="163"/>
+      <c r="A58" s="219"/>
       <c r="B58" s="140"/>
       <c r="S58" s="141"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="163"/>
+      <c r="A59" s="219"/>
       <c r="B59" s="140"/>
       <c r="S59" s="141"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="163"/>
+      <c r="A60" s="219"/>
       <c r="B60" s="140"/>
       <c r="S60" s="141"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="163"/>
+      <c r="A61" s="219"/>
       <c r="B61" s="140"/>
       <c r="S61" s="141"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="163"/>
+      <c r="A62" s="219"/>
       <c r="B62" s="140"/>
       <c r="S62" s="141"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="163"/>
+      <c r="A63" s="219"/>
       <c r="B63" s="140"/>
       <c r="S63" s="141"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="163"/>
+      <c r="A64" s="219"/>
       <c r="B64" s="140"/>
       <c r="S64" s="141"/>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="163"/>
+      <c r="A65" s="219"/>
       <c r="B65" s="140"/>
       <c r="S65" s="141"/>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="163"/>
+      <c r="A66" s="219"/>
       <c r="B66" s="140"/>
       <c r="S66" s="141"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="163"/>
+      <c r="A67" s="219"/>
       <c r="B67" s="140"/>
       <c r="S67" s="141"/>
     </row>
     <row r="68" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A68" s="164"/>
+      <c r="A68" s="220"/>
       <c r="B68" s="142"/>
       <c r="C68" s="77"/>
       <c r="D68" s="77"/>
@@ -5708,31 +5686,6 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="F43:R43"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A68"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A36:A38"/>
@@ -5749,6 +5702,31 @@
     <mergeCell ref="O47:P48"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="F47:F48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L9:M9"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5778,7 +5756,7 @@
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8352AD92-AE48-443F-8268-FEC6552ABA57}">
           <x14:formula1>
             <xm:f>Parametri!$A:$A</xm:f>
@@ -5851,7 +5829,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E2" s="102" t="str" cm="1">
-        <f t="array" ref="E2">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B11,3)="AGT",B2*3.416, IF(OR(RIGHT(Fisa!B11,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B11,2)="SM",RIGHT(Fisa!B11,2)="PM",RIGHT(Fisa!B11,2)="PG",RIGHT(Fisa!B11,2)="mm"), B2*5.796, B2)),B2)</f>
+        <f t="array" ref="E2">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B11,3)="AGT",B2*3.416, IF(OR(RIGHT(Fisa!B11,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B11,2)="SM",RIGHT(Fisa!B11,2)="PM",RIGHT(Fisa!B11,2)="PG",RIGHT(Fisa!B11,2)="mm",,RIGHT(Fisa!B11,2)="PG",RIGHT(Fisa!B11,2)="3D"), B2*5.796, B2)),B2)</f>
         <v/>
       </c>
       <c r="F2" t="s">
@@ -5876,7 +5854,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E3" s="102" t="str" cm="1">
-        <f t="array" ref="E3">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B12,3)="AGT",B3*3.416, IF(OR(RIGHT(Fisa!B12,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B12,2)="SM",RIGHT(Fisa!B12,2)="PM",RIGHT(Fisa!B12,2)="PG",RIGHT(Fisa!B12,2)="mm"), B3*5.796, B3)),B3)</f>
+        <f t="array" ref="E3">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B12,3)="AGT",B3*3.416, IF(OR(RIGHT(Fisa!B12,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B12,2)="SM",RIGHT(Fisa!B12,2)="PM",RIGHT(Fisa!B12,2)="PG",RIGHT(Fisa!B12,2)="mm",,RIGHT(Fisa!B12,2)="PG",RIGHT(Fisa!B12,2)="3D"), B3*5.796, B3)),B3)</f>
         <v/>
       </c>
       <c r="F3" t="s">
@@ -5901,7 +5879,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E4" s="102" t="str" cm="1">
-        <f t="array" ref="E4">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B13,3)="AGT",B4*3.416, IF(OR(RIGHT(Fisa!B13,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B13,2)="SM",RIGHT(Fisa!B13,2)="PM",RIGHT(Fisa!B13,2)="PG",RIGHT(Fisa!B13,2)="mm"), B4*5.796, B4)),B4)</f>
+        <f t="array" ref="E4">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B13,3)="AGT",B4*3.416, IF(OR(RIGHT(Fisa!B13,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B13,2)="SM",RIGHT(Fisa!B13,2)="PM",RIGHT(Fisa!B13,2)="PG",RIGHT(Fisa!B13,2)="mm",,RIGHT(Fisa!B13,2)="PG",RIGHT(Fisa!B13,2)="3D"), B4*5.796, B4)),B4)</f>
         <v/>
       </c>
       <c r="F4" t="s">
@@ -5926,7 +5904,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E5" s="102" t="str" cm="1">
-        <f t="array" ref="E5">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B14,3)="AGT",B5*3.416, IF(OR(RIGHT(Fisa!B14,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B14,2)="SM",RIGHT(Fisa!B14,2)="PM",RIGHT(Fisa!B14,2)="PG",RIGHT(Fisa!B14,2)="mm"), B5*5.796, B5)),B5)</f>
+        <f t="array" ref="E5">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B14,3)="AGT",B5*3.416, IF(OR(RIGHT(Fisa!B14,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B14,2)="SM",RIGHT(Fisa!B14,2)="PM",RIGHT(Fisa!B14,2)="PG",RIGHT(Fisa!B14,2)="mm",,RIGHT(Fisa!B14,2)="PG",RIGHT(Fisa!B14,2)="3D"), B5*5.796, B5)),B5)</f>
         <v/>
       </c>
       <c r="F5" t="s">
@@ -5951,7 +5929,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E6" s="102" t="str" cm="1">
-        <f t="array" ref="E6">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B15,3)="AGT",B6*3.416, IF(OR(RIGHT(Fisa!B15,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B15,2)="SM",RIGHT(Fisa!B15,2)="PM",RIGHT(Fisa!B15,2)="PG",RIGHT(Fisa!B15,2)="mm"), B6*5.796, B6)),B6)</f>
+        <f t="array" ref="E6">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B15,3)="AGT",B6*3.416, IF(OR(RIGHT(Fisa!B15,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B15,2)="SM",RIGHT(Fisa!B15,2)="PM",RIGHT(Fisa!B15,2)="PG",RIGHT(Fisa!B15,2)="mm",,RIGHT(Fisa!B15,2)="PG",RIGHT(Fisa!B15,2)="3D"), B6*5.796, B6)),B6)</f>
         <v/>
       </c>
       <c r="F6" t="s">
@@ -5976,7 +5954,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E7" s="102" t="str" cm="1">
-        <f t="array" ref="E7">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B16,3)="AGT",B7*3.416, IF(OR(RIGHT(Fisa!B16,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B16,2)="SM",RIGHT(Fisa!B16,2)="PM",RIGHT(Fisa!B16,2)="PG",RIGHT(Fisa!B16,2)="mm"), B7*5.796, B7)),B7)</f>
+        <f t="array" ref="E7">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B16,3)="AGT",B7*3.416, IF(OR(RIGHT(Fisa!B16,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B16,2)="SM",RIGHT(Fisa!B16,2)="PM",RIGHT(Fisa!B16,2)="PG",RIGHT(Fisa!B16,2)="mm",,RIGHT(Fisa!B16,2)="PG",RIGHT(Fisa!B16,2)="3D"), B7*5.796, B7)),B7)</f>
         <v/>
       </c>
       <c r="F7" t="s">
@@ -6001,7 +5979,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E8" s="102" t="str" cm="1">
-        <f t="array" ref="E8">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B17,3)="AGT",B8*3.416, IF(OR(RIGHT(Fisa!B17,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B17,2)="SM",RIGHT(Fisa!B17,2)="PM",RIGHT(Fisa!B17,2)="PG",RIGHT(Fisa!B17,2)="mm"), B8*5.796, B8)),B8)</f>
+        <f t="array" ref="E8">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B17,3)="AGT",B8*3.416, IF(OR(RIGHT(Fisa!B17,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B17,2)="SM",RIGHT(Fisa!B17,2)="PM",RIGHT(Fisa!B17,2)="PG",RIGHT(Fisa!B17,2)="mm",,RIGHT(Fisa!B17,2)="PG",RIGHT(Fisa!B17,2)="3D"), B8*5.796, B8)),B8)</f>
         <v/>
       </c>
       <c r="F8" t="s">
@@ -6026,7 +6004,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E9" s="102" t="str" cm="1">
-        <f t="array" ref="E9">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B18,3)="AGT",B9*3.416, IF(OR(RIGHT(Fisa!B18,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B18,2)="SM",RIGHT(Fisa!B18,2)="PM",RIGHT(Fisa!B18,2)="PG",RIGHT(Fisa!B18,2)="mm"), B9*5.796, B9)),B9)</f>
+        <f t="array" ref="E9">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B18,3)="AGT",B9*3.416, IF(OR(RIGHT(Fisa!B18,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B18,2)="SM",RIGHT(Fisa!B18,2)="PM",RIGHT(Fisa!B18,2)="PG",RIGHT(Fisa!B18,2)="mm",,RIGHT(Fisa!B18,2)="PG",RIGHT(Fisa!B18,2)="3D"), B9*5.796, B9)),B9)</f>
         <v/>
       </c>
       <c r="F9" t="s">
@@ -6051,7 +6029,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E10" s="102" t="str" cm="1">
-        <f t="array" ref="E10">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B19,3)="AGT",B10*3.416, IF(OR(RIGHT(Fisa!B19,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B19,2)="SM",RIGHT(Fisa!B19,2)="PM",RIGHT(Fisa!B19,2)="PG",RIGHT(Fisa!B19,2)="mm"), B10*5.796, B10)),B10)</f>
+        <f t="array" ref="E10">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B19,3)="AGT",B10*3.416, IF(OR(RIGHT(Fisa!B19,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B19,2)="SM",RIGHT(Fisa!B19,2)="PM",RIGHT(Fisa!B19,2)="PG",RIGHT(Fisa!B19,2)="mm",,RIGHT(Fisa!B19,2)="PG",RIGHT(Fisa!B19,2)="3D"), B10*5.796, B10)),B10)</f>
         <v/>
       </c>
       <c r="F10" t="s">
@@ -6076,7 +6054,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E11" s="102" t="str" cm="1">
-        <f t="array" ref="E11">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B20,3)="AGT",B11*3.416, IF(OR(RIGHT(Fisa!B20,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B20,2)="SM",RIGHT(Fisa!B20,2)="PM",RIGHT(Fisa!B20,2)="PG",RIGHT(Fisa!B20,2)="mm"), B11*5.796, B11)),B11)</f>
+        <f t="array" ref="E11">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B20,3)="AGT",B11*3.416, IF(OR(RIGHT(Fisa!B20,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B20,2)="SM",RIGHT(Fisa!B20,2)="PM",RIGHT(Fisa!B20,2)="PG",RIGHT(Fisa!B20,2)="mm",,RIGHT(Fisa!B20,2)="PG",RIGHT(Fisa!B20,2)="3D"), B11*5.796, B11)),B11)</f>
         <v/>
       </c>
       <c r="F11" t="s">
@@ -6101,7 +6079,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E12" s="102" t="str" cm="1">
-        <f t="array" ref="E12">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B21,3)="AGT",B12*3.416, IF(OR(RIGHT(Fisa!B21,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B21,2)="SM",RIGHT(Fisa!B21,2)="PM",RIGHT(Fisa!B21,2)="PG",RIGHT(Fisa!B21,2)="mm"), B12*5.796, B12)),B12)</f>
+        <f t="array" ref="E12">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B21,3)="AGT",B12*3.416, IF(OR(RIGHT(Fisa!B21,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B21,2)="SM",RIGHT(Fisa!B21,2)="PM",RIGHT(Fisa!B21,2)="PG",RIGHT(Fisa!B21,2)="mm",,RIGHT(Fisa!B21,2)="PG",RIGHT(Fisa!B21,2)="3D"), B12*5.796, B12)),B12)</f>
         <v/>
       </c>
       <c r="F12" t="s">
@@ -6126,7 +6104,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E13" s="102" t="str" cm="1">
-        <f t="array" ref="E13">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B22,3)="AGT",B13*3.416, IF(OR(RIGHT(Fisa!B22,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B22,2)="SM",RIGHT(Fisa!B22,2)="PM",RIGHT(Fisa!B22,2)="PG",RIGHT(Fisa!B22,2)="mm"), B13*5.796, B13)),B13)</f>
+        <f t="array" ref="E13">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B22,3)="AGT",B13*3.416, IF(OR(RIGHT(Fisa!B22,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B22,2)="SM",RIGHT(Fisa!B22,2)="PM",RIGHT(Fisa!B22,2)="PG",RIGHT(Fisa!B22,2)="mm",,RIGHT(Fisa!B22,2)="PG",RIGHT(Fisa!B22,2)="3D"), B13*5.796, B13)),B13)</f>
         <v/>
       </c>
       <c r="F13" t="s">
@@ -6135,12 +6113,12 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="str">
-        <f>IF(Fisa!B24="","", "MDF "&amp;Fisa!B24)</f>
-        <v/>
-      </c>
-      <c r="B14" t="str">
+        <f>IF(Fisa!B24="","",IF(RIGHT(Fisa!B24,2)="3D",Fisa!B24,"MDF "&amp;Fisa!B24))</f>
+        <v/>
+      </c>
+      <c r="B14">
         <f>Fisa!C24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C14" t="str">
         <f>_xlfn.CONCAT(Fisa!D24)</f>
@@ -6150,9 +6128,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E14" s="102" t="str" cm="1">
-        <f t="array" ref="E14">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B24,3)="AGT",B14*3.416, IF(OR(RIGHT(Fisa!B24,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B24,2)="SM",RIGHT(Fisa!B24,2)="PM",RIGHT(Fisa!B24,2)="PG",RIGHT(Fisa!B24,2)="mm"), B14*5.796, B14)),B14)</f>
-        <v/>
+      <c r="E14" s="102" cm="1">
+        <f t="array" ref="E14">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B24,3)="AGT",B14*3.416, IF(OR(RIGHT(Fisa!B24,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B24,2)="SM",RIGHT(Fisa!B24,2)="PM",RIGHT(Fisa!B24,2)="PG",RIGHT(Fisa!B24,2)="mm",,RIGHT(Fisa!B24,2)="PG",RIGHT(Fisa!B24,2)="3D"), B14*5.796, B14)),B14)</f>
+        <v>0</v>
       </c>
       <c r="F14" t="s">
         <v>52</v>
@@ -6160,7 +6138,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="str">
-        <f>IF(Fisa!B25="","", "MDF "&amp;Fisa!B25)</f>
+        <f>IF(Fisa!B25="","",IF(RIGHT(Fisa!B25,2)="3D",Fisa!B25,"MDF "&amp;Fisa!B25))</f>
         <v/>
       </c>
       <c r="B15" t="str">
@@ -6176,7 +6154,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E15" s="102" t="str" cm="1">
-        <f t="array" ref="E15">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B25,3)="AGT",B15*3.416, IF(OR(RIGHT(Fisa!B25,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B25,2)="SM",RIGHT(Fisa!B25,2)="PM",RIGHT(Fisa!B25,2)="PG",RIGHT(Fisa!B25,2)="mm"), B15*5.796, B15)),B15)</f>
+        <f t="array" ref="E15">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B25,3)="AGT",B15*3.416, IF(OR(RIGHT(Fisa!B25,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B25,2)="SM",RIGHT(Fisa!B25,2)="PM",RIGHT(Fisa!B25,2)="PG",RIGHT(Fisa!B25,2)="mm",,RIGHT(Fisa!B25,2)="PG",RIGHT(Fisa!B25,2)="3D"), B15*5.796, B15)),B15)</f>
         <v/>
       </c>
       <c r="F15" t="s">
@@ -6185,7 +6163,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="str">
-        <f>IF(Fisa!B26="","", "MDF "&amp;Fisa!B26)</f>
+        <f>IF(Fisa!B26="","",IF(RIGHT(Fisa!B26,2)="3D",Fisa!B26,"MDF "&amp;Fisa!B26))</f>
         <v/>
       </c>
       <c r="B16" t="str">
@@ -6201,7 +6179,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E16" s="102" t="str" cm="1">
-        <f t="array" ref="E16">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B26,3)="AGT",B16*3.416, IF(OR(RIGHT(Fisa!B26,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B26,2)="SM",RIGHT(Fisa!B26,2)="PM",RIGHT(Fisa!B26,2)="PG",RIGHT(Fisa!B26,2)="mm"), B16*5.796, B16)),B16)</f>
+        <f t="array" ref="E16">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B26,3)="AGT",B16*3.416, IF(OR(RIGHT(Fisa!B26,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B26,2)="SM",RIGHT(Fisa!B26,2)="PM",RIGHT(Fisa!B26,2)="PG",RIGHT(Fisa!B26,2)="mm",,RIGHT(Fisa!B26,2)="PG",RIGHT(Fisa!B26,2)="3D"), B16*5.796, B16)),B16)</f>
         <v/>
       </c>
       <c r="F16" t="s">
@@ -6210,7 +6188,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="str">
-        <f>IF(Fisa!B27="","", "MDF "&amp;Fisa!B27)</f>
+        <f>IF(Fisa!B27="","",IF(RIGHT(Fisa!B27,2)="3D",Fisa!B27,"MDF "&amp;Fisa!B27))</f>
         <v/>
       </c>
       <c r="B17" t="str">
@@ -6226,7 +6204,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E17" s="102" t="str" cm="1">
-        <f t="array" ref="E17">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B27,3)="AGT",B17*3.416, IF(OR(RIGHT(Fisa!B27,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B27,2)="SM",RIGHT(Fisa!B27,2)="PM",RIGHT(Fisa!B27,2)="PG",RIGHT(Fisa!B27,2)="mm"), B17*5.796, B17)),B17)</f>
+        <f t="array" ref="E17">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B27,3)="AGT",B17*3.416, IF(OR(RIGHT(Fisa!B27,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B27,2)="SM",RIGHT(Fisa!B27,2)="PM",RIGHT(Fisa!B27,2)="PG",RIGHT(Fisa!B27,2)="mm",,RIGHT(Fisa!B27,2)="PG",RIGHT(Fisa!B27,2)="3D"), B17*5.796, B17)),B17)</f>
         <v/>
       </c>
       <c r="F17" t="s">
@@ -6235,7 +6213,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="str">
-        <f>IF(Fisa!B28="","", "MDF "&amp;Fisa!B28)</f>
+        <f>IF(Fisa!B28="","",IF(RIGHT(Fisa!B28,2)="3D",Fisa!B28,"MDF "&amp;Fisa!B28))</f>
         <v/>
       </c>
       <c r="B18" t="str">
@@ -6251,7 +6229,7 @@
         <v xml:space="preserve"> mp</v>
       </c>
       <c r="E18" s="102" t="str" cm="1">
-        <f t="array" ref="E18">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B28,3)="AGT",B18*3.416, IF(OR(RIGHT(Fisa!B28,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B28,2)="SM",RIGHT(Fisa!B28,2)="PM",RIGHT(Fisa!B28,2)="PG",RIGHT(Fisa!B28,2)="mm"), B18*5.796, B18)),B18)</f>
+        <f t="array" ref="E18">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B28,3)="AGT",B18*3.416, IF(OR(RIGHT(Fisa!B28,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B28,2)="SM",RIGHT(Fisa!B28,2)="PM",RIGHT(Fisa!B28,2)="PG",RIGHT(Fisa!B28,2)="mm",,RIGHT(Fisa!B28,2)="PG",RIGHT(Fisa!B28,2)="3D"), B18*5.796, B18)),B18)</f>
         <v/>
       </c>
       <c r="F18" t="s">
@@ -6483,9 +6461,9 @@
         <f>CONCATENATE(Fisa!P11," ",Fisa!P9)</f>
         <v xml:space="preserve"> 43/1.5</v>
       </c>
-      <c r="B30" t="str">
+      <c r="B30">
         <f>Fisa!Q11</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D30" t="str">
         <f t="shared" si="2"/>
@@ -6497,9 +6475,9 @@
         <f>CONCATENATE(Fisa!R11," ",Fisa!R9)</f>
         <v xml:space="preserve"> 43/2</v>
       </c>
-      <c r="B31" t="str">
+      <c r="B31">
         <f>Fisa!S11</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D31" t="str">
         <f t="shared" si="2"/>
@@ -6595,9 +6573,9 @@
         <f>CONCATENATE(Fisa!R12," ",Fisa!R9)</f>
         <v xml:space="preserve"> 43/2</v>
       </c>
-      <c r="B38" t="str">
+      <c r="B38">
         <f>Fisa!S12</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D38" t="str">
         <f t="shared" si="2"/>
@@ -8085,15 +8063,15 @@
       </c>
       <c r="C144" t="str">
         <f>Fisa!D30</f>
-        <v>mp</v>
+        <v>buc</v>
       </c>
       <c r="D144" t="str">
         <f>CONCATENATE(A144," ",F144)</f>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E144" t="str">
+      <c r="E144" t="e">
         <f>IF(Fisa!I3="Debitare căntuire", B144*5.8995, B144)</f>
-        <v/>
+        <v>#VALUE!</v>
       </c>
       <c r="F144" t="s">
         <v>52</v>
@@ -8861,7 +8839,7 @@
         <v>26</v>
       </c>
       <c r="B200">
-        <f>Fisa!S41++Q41</f>
+        <f>Fisa!S41+Fisa!Q41</f>
         <v>0</v>
       </c>
       <c r="D200" t="str">
@@ -9035,7 +9013,7 @@
       </c>
       <c r="C7" s="8" t="str">
         <f>IF(Fisa!I3="Debitare căntuire", "Coli", "Mp")</f>
-        <v>Mp</v>
+        <v>Coli</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -9276,13 +9254,13 @@
       <c r="L19" s="5"/>
     </row>
     <row r="20" spans="1:12" customFormat="1">
-      <c r="B20" s="8" t="str">
+      <c r="B20" s="8">
         <f>Fisa!B24</f>
-        <v/>
-      </c>
-      <c r="C20" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="C20" s="8">
         <f>Fisa!C24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -10196,7 +10174,7 @@
       </c>
       <c r="C49" s="8" t="str">
         <f>IF(Fisa!I3="Debitare căntuire", "Coli", "Mp")</f>
-        <v>Mp</v>
+        <v>Coli</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -10209,13 +10187,13 @@
       <c r="L49" s="5"/>
     </row>
     <row r="50" spans="1:29" customFormat="1">
-      <c r="B50" s="10" t="str">
+      <c r="B50" s="10">
         <f>Fisa!B24</f>
-        <v/>
-      </c>
-      <c r="C50" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="C50" s="10">
         <f>Fisa!C24</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CEFA8A-8D3A-4A91-9701-E7AECA6000B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63F1A7E-22B7-4DF3-B43B-761E1A06A72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="116">
   <si>
     <t>FIRMA:</t>
   </si>
@@ -2477,9 +2477,7 @@
       <c r="H3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="215" t="s">
-        <v>43</v>
-      </c>
+      <c r="I3" s="215"/>
       <c r="J3" s="216"/>
       <c r="K3" s="217"/>
       <c r="M3" s="27">
@@ -2748,19 +2746,25 @@
         <v/>
       </c>
       <c r="O11" s="29" t="str">
-        <f>IFERROR(IF(AND(N11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
+        <f>IFERROR(IF(AND(N11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F11,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/0.8"),""),"")</f>
         <v/>
       </c>
       <c r="P11" s="56" t="str">
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="Q11" s="29"/>
+      <c r="Q11" s="29" t="str">
+        <f>IFERROR(IF(AND(P11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
+        <v/>
+      </c>
       <c r="R11" s="56" t="str">
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="S11" s="29"/>
+      <c r="S11" s="29" t="str">
+        <f>IFERROR(IF(AND(R11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R11,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R11,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="232"/>
@@ -2834,7 +2838,7 @@
         <v/>
       </c>
       <c r="O12" s="30" t="str">
-        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(N12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(N12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P12" s="67" t="str">
@@ -2849,7 +2853,10 @@
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
-      <c r="S12" s="30"/>
+      <c r="S12" s="30" t="str">
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(R12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R12,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R12,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="232"/>
@@ -2927,7 +2934,7 @@
         <v/>
       </c>
       <c r="O13" s="30" t="str">
-        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(N13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(N13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P13" s="67" t="str">
@@ -3023,7 +3030,7 @@
         <v/>
       </c>
       <c r="O14" s="30" t="str">
-        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(N14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(N14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P14" s="67" t="str">
@@ -3119,7 +3126,7 @@
         <v/>
       </c>
       <c r="O15" s="30" t="str">
-        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(N15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(N15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P15" s="67" t="str">
@@ -3215,7 +3222,7 @@
         <v/>
       </c>
       <c r="O16" s="30" t="str">
-        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(N16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(N16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P16" s="67" t="str">
@@ -3311,7 +3318,7 @@
         <v/>
       </c>
       <c r="O17" s="30" t="str">
-        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(N17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(N17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P17" s="67" t="str">
@@ -3407,7 +3414,7 @@
         <v/>
       </c>
       <c r="O18" s="30" t="str">
-        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(N18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(N18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P18" s="67" t="str">
@@ -3503,7 +3510,7 @@
         <v/>
       </c>
       <c r="O19" s="30" t="str">
-        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(N19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(N19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P19" s="67" t="str">
@@ -3599,7 +3606,7 @@
         <v/>
       </c>
       <c r="O20" s="30" t="str">
-        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(N20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(N20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P20" s="67" t="str">
@@ -3695,7 +3702,7 @@
         <v/>
       </c>
       <c r="O21" s="30" t="str">
-        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(N21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(N21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P21" s="67" t="str">
@@ -3791,7 +3798,7 @@
         <v/>
       </c>
       <c r="O22" s="30" t="str">
-        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(N22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(N22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P22" s="67" t="str">
@@ -3919,7 +3926,7 @@
         <v/>
       </c>
       <c r="O24" s="30" t="str">
-        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(N24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(N24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P24" s="67" t="str">
@@ -4015,7 +4022,7 @@
         <v/>
       </c>
       <c r="O25" s="30" t="str">
-        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(N25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(N25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P25" s="67" t="str">
@@ -4111,7 +4118,7 @@
         <v/>
       </c>
       <c r="O26" s="30" t="str">
-        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(N26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(N26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P26" s="67" t="str">
@@ -4207,7 +4214,7 @@
         <v/>
       </c>
       <c r="O27" s="30" t="str">
-        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(N27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(N27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P27" s="67" t="str">
@@ -4303,7 +4310,7 @@
         <v/>
       </c>
       <c r="O28" s="30" t="str">
-        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(N28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(N28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
         <v/>
       </c>
       <c r="P28" s="67" t="str">
@@ -4379,7 +4386,7 @@
       </c>
       <c r="D30" s="29" t="str">
         <f>IF(I3="Debitare căntuire", "buc", "mp")</f>
-        <v>buc</v>
+        <v>mp</v>
       </c>
       <c r="E30" s="48"/>
       <c r="F30" s="150"/>
@@ -4521,7 +4528,7 @@
         <v/>
       </c>
       <c r="O32" s="30" t="str">
-        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N32)&gt;0,"",IF(AND(N32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N32,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N32,Cant!$J$2:$J$100,"43/1.0"),"")),""))</f>
+        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N32)&gt;0,"",IF(AND(N32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N32,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N32,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N32,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N32,Cant!$J$2:$J$99,"43/0.8"),"")),""))</f>
         <v/>
       </c>
       <c r="P32" s="67" t="str">
@@ -4606,7 +4613,7 @@
         <v/>
       </c>
       <c r="O33" s="30" t="str">
-        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N33)&gt;0,"",IF(AND(N33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N33,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N33,Cant!$J$2:$J$100,"43/1.0"),"")),""))</f>
+        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N33)&gt;0,"",IF(AND(N33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N33,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N33,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N33,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N33,Cant!$J$2:$J$99,"43/0.8"),"")),""))</f>
         <v/>
       </c>
       <c r="P33" s="67" t="str">
@@ -4691,7 +4698,7 @@
         <v/>
       </c>
       <c r="O34" s="30" t="str">
-        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N34)&gt;0,"",IF(AND(N34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N34,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N34,Cant!$J$2:$J$100,"43/1.0"),"")),""))</f>
+        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N34)&gt;0,"",IF(AND(N34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N34,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N34,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N34,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N34,Cant!$J$2:$J$99,"43/0.8"),"")),""))</f>
         <v/>
       </c>
       <c r="P34" s="67" t="str">
@@ -4817,7 +4824,7 @@
         <v/>
       </c>
       <c r="O36" s="30" t="str">
-        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N36)&gt;0,"",IF(AND(N36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N36,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N36,Cant!$J$2:$J$100,"43/1.0"),"")),""))</f>
+        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N36)&gt;0,"",IF(AND(N36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N36,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N36,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N36,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N36,Cant!$J$2:$J$99,"43/0.8"),"")),""))</f>
         <v/>
       </c>
       <c r="P36" s="67" t="str">
@@ -4902,7 +4909,7 @@
         <v/>
       </c>
       <c r="O37" s="30" t="str">
-        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N37)&gt;0,"",IF(AND(N37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N37,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N37,Cant!$J$2:$J$100,"43/1.0"),"")),""))</f>
+        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N37)&gt;0,"",IF(AND(N37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N37,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N37,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N37,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N37,Cant!$J$2:$J$99,"43/0.8"),"")),""))</f>
         <v/>
       </c>
       <c r="P37" s="67" t="str">
@@ -4987,7 +4994,7 @@
         <v/>
       </c>
       <c r="O38" s="31" t="str">
-        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N38)&gt;0,"",IF(AND(N38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N38,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N38,Cant!$J$2:$J$100,"43/1.0"),"")),""))</f>
+        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N38)&gt;0,"",IF(AND(N38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N38,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N38,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N38,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N38,Cant!$J$2:$J$99,"43/0.8"),"")),""))</f>
         <v/>
       </c>
       <c r="P38" s="68" t="str">
@@ -6461,9 +6468,9 @@
         <f>CONCATENATE(Fisa!P11," ",Fisa!P9)</f>
         <v xml:space="preserve"> 43/1.5</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="str">
         <f>Fisa!Q11</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D30" t="str">
         <f t="shared" si="2"/>
@@ -6475,9 +6482,9 @@
         <f>CONCATENATE(Fisa!R11," ",Fisa!R9)</f>
         <v xml:space="preserve"> 43/2</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="str">
         <f>Fisa!S11</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D31" t="str">
         <f t="shared" si="2"/>
@@ -6573,9 +6580,9 @@
         <f>CONCATENATE(Fisa!R12," ",Fisa!R9)</f>
         <v xml:space="preserve"> 43/2</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="str">
         <f>Fisa!S12</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D38" t="str">
         <f t="shared" si="2"/>
@@ -8063,15 +8070,15 @@
       </c>
       <c r="C144" t="str">
         <f>Fisa!D30</f>
-        <v>buc</v>
+        <v>mp</v>
       </c>
       <c r="D144" t="str">
         <f>CONCATENATE(A144," ",F144)</f>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E144" t="e">
+      <c r="E144" t="str">
         <f>IF(Fisa!I3="Debitare căntuire", B144*5.8995, B144)</f>
-        <v>#VALUE!</v>
+        <v/>
       </c>
       <c r="F144" t="s">
         <v>52</v>
@@ -9013,7 +9020,7 @@
       </c>
       <c r="C7" s="8" t="str">
         <f>IF(Fisa!I3="Debitare căntuire", "Coli", "Mp")</f>
-        <v>Coli</v>
+        <v>Mp</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -10174,7 +10181,7 @@
       </c>
       <c r="C49" s="8" t="str">
         <f>IF(Fisa!I3="Debitare căntuire", "Coli", "Mp")</f>
-        <v>Coli</v>
+        <v>Mp</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63F1A7E-22B7-4DF3-B43B-761E1A06A72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AA5CD3-3A2D-40AF-B11A-AB869DBF4ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -1671,11 +1671,191 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1706,12 +1886,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1755,180 +1929,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2416,33 +2416,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="203" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="204"/>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="205"/>
       <c r="M1" s="38" t="s">
         <v>70</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="195" t="s">
+      <c r="O1" s="194" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="196"/>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="197"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="196"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2461,165 +2461,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="80"/>
-      <c r="O2" s="198"/>
-      <c r="P2" s="199"/>
-      <c r="Q2" s="199"/>
-      <c r="R2" s="199"/>
-      <c r="S2" s="200"/>
+      <c r="O2" s="197"/>
+      <c r="P2" s="198"/>
+      <c r="Q2" s="198"/>
+      <c r="R2" s="198"/>
+      <c r="S2" s="199"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="208"/>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="B3" s="209"/>
+      <c r="C3" s="210"/>
+      <c r="D3" s="211"/>
       <c r="H3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="215"/>
-      <c r="J3" s="216"/>
-      <c r="K3" s="217"/>
+      <c r="I3" s="216"/>
+      <c r="J3" s="217"/>
+      <c r="K3" s="218"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="73"/>
-      <c r="O3" s="205"/>
-      <c r="P3" s="206"/>
-      <c r="Q3" s="206"/>
-      <c r="R3" s="206"/>
-      <c r="S3" s="207"/>
+      <c r="O3" s="206"/>
+      <c r="P3" s="207"/>
+      <c r="Q3" s="207"/>
+      <c r="R3" s="207"/>
+      <c r="S3" s="208"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="189"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="B4" s="188"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="190"/>
       <c r="H4" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="192"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="194"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="192"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="73"/>
-      <c r="O4" s="205"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="206"/>
-      <c r="S4" s="207"/>
+      <c r="O4" s="206"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="208"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="211"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="213"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="H5" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="214"/>
-      <c r="J5" s="206"/>
-      <c r="K5" s="207"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="207"/>
+      <c r="K5" s="208"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="73"/>
-      <c r="O5" s="205"/>
-      <c r="P5" s="206"/>
-      <c r="Q5" s="206"/>
-      <c r="R5" s="206"/>
-      <c r="S5" s="207"/>
+      <c r="O5" s="206"/>
+      <c r="P5" s="207"/>
+      <c r="Q5" s="207"/>
+      <c r="R5" s="207"/>
+      <c r="S5" s="208"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="168"/>
-      <c r="C6" s="169"/>
-      <c r="D6" s="170"/>
+      <c r="B6" s="223"/>
+      <c r="C6" s="224"/>
+      <c r="D6" s="225"/>
       <c r="H6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="171"/>
-      <c r="J6" s="172"/>
-      <c r="K6" s="173"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="201"/>
+      <c r="K6" s="202"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="74"/>
-      <c r="O6" s="201"/>
-      <c r="P6" s="172"/>
-      <c r="Q6" s="172"/>
-      <c r="R6" s="172"/>
-      <c r="S6" s="173"/>
+      <c r="O6" s="200"/>
+      <c r="P6" s="201"/>
+      <c r="Q6" s="201"/>
+      <c r="R6" s="201"/>
+      <c r="S6" s="202"/>
     </row>
     <row r="7" spans="1:19" s="50" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="174" t="s">
+      <c r="A8" s="227" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="175"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="176"/>
-      <c r="F8" s="180" t="s">
+      <c r="B8" s="228"/>
+      <c r="C8" s="228"/>
+      <c r="D8" s="229"/>
+      <c r="F8" s="233" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="181"/>
-      <c r="H8" s="181"/>
-      <c r="I8" s="181"/>
-      <c r="J8" s="181"/>
-      <c r="K8" s="181"/>
-      <c r="L8" s="181"/>
-      <c r="M8" s="181"/>
-      <c r="N8" s="181"/>
-      <c r="O8" s="181"/>
-      <c r="P8" s="181"/>
-      <c r="Q8" s="181"/>
-      <c r="R8" s="181"/>
-      <c r="S8" s="186"/>
+      <c r="G8" s="234"/>
+      <c r="H8" s="234"/>
+      <c r="I8" s="234"/>
+      <c r="J8" s="234"/>
+      <c r="K8" s="234"/>
+      <c r="L8" s="234"/>
+      <c r="M8" s="234"/>
+      <c r="N8" s="234"/>
+      <c r="O8" s="234"/>
+      <c r="P8" s="234"/>
+      <c r="Q8" s="234"/>
+      <c r="R8" s="234"/>
+      <c r="S8" s="239"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="177"/>
-      <c r="B9" s="178"/>
-      <c r="C9" s="178"/>
-      <c r="D9" s="179"/>
-      <c r="F9" s="226" t="s">
+      <c r="A9" s="230"/>
+      <c r="B9" s="231"/>
+      <c r="C9" s="231"/>
+      <c r="D9" s="232"/>
+      <c r="F9" s="170" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="227"/>
-      <c r="H9" s="240" t="s">
+      <c r="G9" s="171"/>
+      <c r="H9" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="241"/>
-      <c r="J9" s="224" t="s">
+      <c r="I9" s="187"/>
+      <c r="J9" s="168" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="225"/>
-      <c r="L9" s="187" t="s">
+      <c r="K9" s="169"/>
+      <c r="L9" s="240" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="188"/>
-      <c r="N9" s="184" t="s">
+      <c r="M9" s="241"/>
+      <c r="N9" s="237" t="s">
         <v>80</v>
       </c>
-      <c r="O9" s="185"/>
-      <c r="P9" s="182" t="s">
+      <c r="O9" s="238"/>
+      <c r="P9" s="235" t="s">
         <v>68</v>
       </c>
-      <c r="Q9" s="183"/>
-      <c r="R9" s="184" t="s">
+      <c r="Q9" s="236"/>
+      <c r="R9" s="237" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="185"/>
+      <c r="S9" s="238"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="231" t="s">
+      <c r="A10" s="175" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2676,7 +2676,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="232"/>
+      <c r="A11" s="176"/>
       <c r="B11" s="56" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2746,7 +2746,7 @@
         <v/>
       </c>
       <c r="O11" s="29" t="str">
-        <f>IFERROR(IF(AND(N11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F11,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/0.8"),""),"")</f>
+        <f>IFERROR(IF(AND(N11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F11,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F11,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/0.8")++SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F11,Cant!$J$2:$J$99,"42/1.0"),""),"")</f>
         <v/>
       </c>
       <c r="P11" s="56" t="str">
@@ -2767,7 +2767,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="232"/>
+      <c r="A12" s="176"/>
       <c r="B12" s="108" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -2838,7 +2838,7 @@
         <v/>
       </c>
       <c r="O12" s="30" t="str">
-        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(N12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(N12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P12" s="67" t="str">
@@ -2859,7 +2859,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="232"/>
+      <c r="A13" s="176"/>
       <c r="B13" s="108" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -2934,7 +2934,7 @@
         <v/>
       </c>
       <c r="O13" s="30" t="str">
-        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(N13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(N13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P13" s="67" t="str">
@@ -2955,7 +2955,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="232"/>
+      <c r="A14" s="176"/>
       <c r="B14" s="108" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3030,7 +3030,7 @@
         <v/>
       </c>
       <c r="O14" s="30" t="str">
-        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(N14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(N14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P14" s="67" t="str">
@@ -3051,7 +3051,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="232"/>
+      <c r="A15" s="176"/>
       <c r="B15" s="108" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3126,7 +3126,7 @@
         <v/>
       </c>
       <c r="O15" s="30" t="str">
-        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(N15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(N15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P15" s="67" t="str">
@@ -3147,7 +3147,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="232"/>
+      <c r="A16" s="176"/>
       <c r="B16" s="108" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3222,7 +3222,7 @@
         <v/>
       </c>
       <c r="O16" s="30" t="str">
-        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(N16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(N16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P16" s="67" t="str">
@@ -3243,7 +3243,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="232"/>
+      <c r="A17" s="176"/>
       <c r="B17" s="108" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3318,7 +3318,7 @@
         <v/>
       </c>
       <c r="O17" s="30" t="str">
-        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(N17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(N17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P17" s="67" t="str">
@@ -3339,7 +3339,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="232"/>
+      <c r="A18" s="176"/>
       <c r="B18" s="108" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3414,7 +3414,7 @@
         <v/>
       </c>
       <c r="O18" s="30" t="str">
-        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(N18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(N18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P18" s="67" t="str">
@@ -3435,7 +3435,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="232"/>
+      <c r="A19" s="176"/>
       <c r="B19" s="108" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3510,7 +3510,7 @@
         <v/>
       </c>
       <c r="O19" s="30" t="str">
-        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(N19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(N19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P19" s="67" t="str">
@@ -3531,7 +3531,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="232"/>
+      <c r="A20" s="176"/>
       <c r="B20" s="108" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3606,7 +3606,7 @@
         <v/>
       </c>
       <c r="O20" s="30" t="str">
-        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(N20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(N20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P20" s="67" t="str">
@@ -3627,7 +3627,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="232"/>
+      <c r="A21" s="176"/>
       <c r="B21" s="108" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3702,7 +3702,7 @@
         <v/>
       </c>
       <c r="O21" s="30" t="str">
-        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(N21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(N21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P21" s="67" t="str">
@@ -3723,7 +3723,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="233"/>
+      <c r="A22" s="177"/>
       <c r="B22" s="108" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3798,7 +3798,7 @@
         <v/>
       </c>
       <c r="O22" s="30" t="str">
-        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(N22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(N22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P22" s="67" t="str">
@@ -3864,7 +3864,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="231" t="s">
+      <c r="A24" s="175" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="56"/>
@@ -3926,7 +3926,7 @@
         <v/>
       </c>
       <c r="O24" s="30" t="str">
-        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(N24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(N24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N24,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P24" s="67" t="str">
@@ -3947,7 +3947,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="232"/>
+      <c r="A25" s="176"/>
       <c r="B25" s="67" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4022,7 +4022,7 @@
         <v/>
       </c>
       <c r="O25" s="30" t="str">
-        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(N25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(N25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P25" s="67" t="str">
@@ -4043,7 +4043,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="232"/>
+      <c r="A26" s="176"/>
       <c r="B26" s="67" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4118,7 +4118,7 @@
         <v/>
       </c>
       <c r="O26" s="30" t="str">
-        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(N26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(N26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P26" s="67" t="str">
@@ -4139,7 +4139,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="232"/>
+      <c r="A27" s="176"/>
       <c r="B27" s="67" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4214,7 +4214,7 @@
         <v/>
       </c>
       <c r="O27" s="30" t="str">
-        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(N27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(N27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P27" s="67" t="str">
@@ -4235,7 +4235,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="234"/>
+      <c r="A28" s="178"/>
       <c r="B28" s="67" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4310,7 +4310,7 @@
         <v/>
       </c>
       <c r="O28" s="30" t="str">
-        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(N28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/0.8"),""),""))</f>
+        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(N28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"42/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P28" s="67" t="str">
@@ -4462,7 +4462,7 @@
       <c r="S31" s="160"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="221" t="s">
+      <c r="A32" s="165" t="s">
         <v>78</v>
       </c>
       <c r="B32" s="56" t="str" cm="1">
@@ -4528,7 +4528,7 @@
         <v/>
       </c>
       <c r="O32" s="30" t="str">
-        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N32)&gt;0,"",IF(AND(N32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N32,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N32,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N32,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N32,Cant!$J$2:$J$99,"43/0.8"),"")),""))</f>
+        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N32)&gt;0,"",IF(AND(N32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N32,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N32,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N32,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N32,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N32,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N32,Cant!$J$2:$J$99,"42/1.0"),"")),""))</f>
         <v/>
       </c>
       <c r="P32" s="67" t="str">
@@ -4549,7 +4549,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="222"/>
+      <c r="A33" s="166"/>
       <c r="B33" s="67" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4613,7 +4613,7 @@
         <v/>
       </c>
       <c r="O33" s="30" t="str">
-        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N33)&gt;0,"",IF(AND(N33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N33,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N33,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N33,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N33,Cant!$J$2:$J$99,"43/0.8"),"")),""))</f>
+        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N33)&gt;0,"",IF(AND(N33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N33,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N33,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N33,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N33,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N33,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N33,Cant!$J$2:$J$99,"42/1.0"),"")),""))</f>
         <v/>
       </c>
       <c r="P33" s="67" t="str">
@@ -4634,7 +4634,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="223"/>
+      <c r="A34" s="167"/>
       <c r="B34" s="67" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4698,7 +4698,7 @@
         <v/>
       </c>
       <c r="O34" s="30" t="str">
-        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N34)&gt;0,"",IF(AND(N34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N34,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N34,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N34,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N34,Cant!$J$2:$J$99,"43/0.8"),"")),""))</f>
+        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N34)&gt;0,"",IF(AND(N34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N34,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N34,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N34,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N34,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N34,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N34,Cant!$J$2:$J$99,"42/1.0"),"")),""))</f>
         <v/>
       </c>
       <c r="P34" s="67" t="str">
@@ -4758,7 +4758,7 @@
       <c r="S35" s="161"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="221" t="s">
+      <c r="A36" s="165" t="s">
         <v>79</v>
       </c>
       <c r="B36" s="56" t="str" cm="1">
@@ -4824,7 +4824,7 @@
         <v/>
       </c>
       <c r="O36" s="30" t="str">
-        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N36)&gt;0,"",IF(AND(N36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N36,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N36,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N36,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N36,Cant!$J$2:$J$99,"43/0.8"),"")),""))</f>
+        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N36)&gt;0,"",IF(AND(N36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N36,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N36,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N36,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N36,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N36,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N36,Cant!$J$2:$J$99,"42/1.0"),"")),""))</f>
         <v/>
       </c>
       <c r="P36" s="67" t="str">
@@ -4845,7 +4845,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="222"/>
+      <c r="A37" s="166"/>
       <c r="B37" s="67" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4909,7 +4909,7 @@
         <v/>
       </c>
       <c r="O37" s="30" t="str">
-        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N37)&gt;0,"",IF(AND(N37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N37,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N37,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N37,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N37,Cant!$J$2:$J$99,"43/0.8"),"")),""))</f>
+        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N37)&gt;0,"",IF(AND(N37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N37,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N37,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N37,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N37,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N37,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N37,Cant!$J$2:$J$99,"42/1.0"),"")),""))</f>
         <v/>
       </c>
       <c r="P37" s="67" t="str">
@@ -4930,7 +4930,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="223"/>
+      <c r="A38" s="167"/>
       <c r="B38" s="68" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4994,7 +4994,7 @@
         <v/>
       </c>
       <c r="O38" s="31" t="str">
-        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N38)&gt;0,"",IF(AND(N38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N38,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N38,Cant!$J$2:$J$99,"43/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N38,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N38,Cant!$J$2:$J$99,"43/0.8"),"")),""))</f>
+        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N38)&gt;0,"",IF(AND(N38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N38,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N38,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N38,Cant!$J$2:$J$99,"42/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N38,Cant!$J$2:$J$100,"43/1.0")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N38,Cant!$J$2:$J$99,"43/0.8")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N38,Cant!$J$2:$J$99,"42/1.0"),"")),""))</f>
         <v/>
       </c>
       <c r="P38" s="68" t="str">
@@ -5029,7 +5029,7 @@
       <c r="Q39" s="61"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="231" t="s">
+      <c r="A40" s="175" t="s">
         <v>50</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5041,25 +5041,25 @@
       <c r="D40" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="228" t="s">
+      <c r="F40" s="172" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="229"/>
-      <c r="H40" s="229"/>
-      <c r="I40" s="229"/>
-      <c r="J40" s="229"/>
-      <c r="K40" s="229"/>
-      <c r="L40" s="229"/>
-      <c r="M40" s="229"/>
-      <c r="N40" s="229"/>
-      <c r="O40" s="229"/>
-      <c r="P40" s="229"/>
-      <c r="Q40" s="229"/>
-      <c r="R40" s="229"/>
-      <c r="S40" s="230"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="173"/>
+      <c r="I40" s="173"/>
+      <c r="J40" s="173"/>
+      <c r="K40" s="173"/>
+      <c r="L40" s="173"/>
+      <c r="M40" s="173"/>
+      <c r="N40" s="173"/>
+      <c r="O40" s="173"/>
+      <c r="P40" s="173"/>
+      <c r="Q40" s="173"/>
+      <c r="R40" s="173"/>
+      <c r="S40" s="174"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="232"/>
+      <c r="A41" s="176"/>
       <c r="B41" s="35" t="s">
         <v>81</v>
       </c>
@@ -5122,7 +5122,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="232"/>
+      <c r="A42" s="176"/>
       <c r="B42" s="49" t="s">
         <v>88</v>
       </c>
@@ -5147,13 +5147,13 @@
       <c r="P42" s="66"/>
       <c r="Q42" s="78"/>
       <c r="R42" s="79"/>
-      <c r="S42" s="162">
+      <c r="S42" s="179">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="232"/>
+      <c r="A43" s="176"/>
       <c r="B43" s="49" t="s">
         <v>82</v>
       </c>
@@ -5165,26 +5165,26 @@
         <v>54</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="180" t="str">
+      <c r="F43" s="233" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="181"/>
-      <c r="H43" s="181"/>
-      <c r="I43" s="181"/>
-      <c r="J43" s="181"/>
-      <c r="K43" s="181"/>
-      <c r="L43" s="181"/>
-      <c r="M43" s="181"/>
-      <c r="N43" s="181"/>
-      <c r="O43" s="181"/>
-      <c r="P43" s="181"/>
-      <c r="Q43" s="181"/>
-      <c r="R43" s="181"/>
-      <c r="S43" s="235"/>
+      <c r="G43" s="234"/>
+      <c r="H43" s="234"/>
+      <c r="I43" s="234"/>
+      <c r="J43" s="234"/>
+      <c r="K43" s="234"/>
+      <c r="L43" s="234"/>
+      <c r="M43" s="234"/>
+      <c r="N43" s="234"/>
+      <c r="O43" s="234"/>
+      <c r="P43" s="234"/>
+      <c r="Q43" s="234"/>
+      <c r="R43" s="234"/>
+      <c r="S43" s="180"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="232"/>
+      <c r="A44" s="176"/>
       <c r="B44" s="49" t="s">
         <v>87</v>
       </c>
@@ -5240,7 +5240,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="232"/>
+      <c r="A45" s="176"/>
       <c r="B45" s="33" t="s">
         <v>89</v>
       </c>
@@ -5374,7 +5374,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="232"/>
+      <c r="A46" s="176"/>
       <c r="B46" s="33" t="s">
         <v>83</v>
       </c>
@@ -5388,7 +5388,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="232"/>
+      <c r="A47" s="176"/>
       <c r="B47" s="33" t="s">
         <v>84</v>
       </c>
@@ -5399,31 +5399,31 @@
       <c r="D47" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="162" t="s">
+      <c r="F47" s="179" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="166" t="str">
+      <c r="G47" s="221" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="162" t="s">
+      <c r="J47" s="179" t="s">
         <v>86</v>
       </c>
-      <c r="K47" s="164">
+      <c r="K47" s="219">
         <v>1</v>
       </c>
-      <c r="N47" s="162" t="s">
+      <c r="N47" s="179" t="s">
         <v>108</v>
       </c>
-      <c r="O47" s="236"/>
-      <c r="P47" s="237"/>
-      <c r="R47" s="162" t="s">
+      <c r="O47" s="182"/>
+      <c r="P47" s="183"/>
+      <c r="R47" s="179" t="s">
         <v>114</v>
       </c>
-      <c r="S47" s="162"/>
+      <c r="S47" s="179"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="234"/>
+      <c r="A48" s="178"/>
       <c r="B48" s="36" t="s">
         <v>85</v>
       </c>
@@ -5434,15 +5434,15 @@
       <c r="D48" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="F48" s="163"/>
-      <c r="G48" s="167"/>
-      <c r="J48" s="163"/>
-      <c r="K48" s="165"/>
-      <c r="N48" s="235"/>
-      <c r="O48" s="238"/>
-      <c r="P48" s="239"/>
-      <c r="R48" s="235"/>
-      <c r="S48" s="163"/>
+      <c r="F48" s="181"/>
+      <c r="G48" s="222"/>
+      <c r="J48" s="181"/>
+      <c r="K48" s="220"/>
+      <c r="N48" s="180"/>
+      <c r="O48" s="184"/>
+      <c r="P48" s="185"/>
+      <c r="R48" s="180"/>
+      <c r="S48" s="181"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5451,7 +5451,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="218" t="s">
+      <c r="A50" s="162" t="s">
         <v>65</v>
       </c>
       <c r="B50" s="134"/>
@@ -5474,7 +5474,7 @@
       <c r="S50" s="136"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="219"/>
+      <c r="A51" s="163"/>
       <c r="B51" s="137"/>
       <c r="C51" s="139"/>
       <c r="D51" s="139"/>
@@ -5495,7 +5495,7 @@
       <c r="S51" s="138"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="219"/>
+      <c r="A52" s="163"/>
       <c r="B52" s="137"/>
       <c r="C52" s="139"/>
       <c r="D52" s="139"/>
@@ -5516,7 +5516,7 @@
       <c r="S52" s="138"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="219"/>
+      <c r="A53" s="163"/>
       <c r="B53" s="137"/>
       <c r="C53" s="139"/>
       <c r="D53" s="139"/>
@@ -5537,7 +5537,7 @@
       <c r="S53" s="138"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="219"/>
+      <c r="A54" s="163"/>
       <c r="B54" s="137"/>
       <c r="C54" s="139"/>
       <c r="D54" s="139"/>
@@ -5558,7 +5558,7 @@
       <c r="S54" s="138"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="219"/>
+      <c r="A55" s="163"/>
       <c r="B55" s="137"/>
       <c r="C55" s="139"/>
       <c r="D55" s="139"/>
@@ -5579,7 +5579,7 @@
       <c r="S55" s="138"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="219"/>
+      <c r="A56" s="163"/>
       <c r="B56" s="137"/>
       <c r="C56" s="139"/>
       <c r="D56" s="139"/>
@@ -5600,7 +5600,7 @@
       <c r="S56" s="138"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="219"/>
+      <c r="A57" s="163"/>
       <c r="B57" s="137"/>
       <c r="C57" s="139"/>
       <c r="D57" s="139"/>
@@ -5621,57 +5621,57 @@
       <c r="S57" s="138"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="219"/>
+      <c r="A58" s="163"/>
       <c r="B58" s="140"/>
       <c r="S58" s="141"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="219"/>
+      <c r="A59" s="163"/>
       <c r="B59" s="140"/>
       <c r="S59" s="141"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="219"/>
+      <c r="A60" s="163"/>
       <c r="B60" s="140"/>
       <c r="S60" s="141"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="219"/>
+      <c r="A61" s="163"/>
       <c r="B61" s="140"/>
       <c r="S61" s="141"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="219"/>
+      <c r="A62" s="163"/>
       <c r="B62" s="140"/>
       <c r="S62" s="141"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="219"/>
+      <c r="A63" s="163"/>
       <c r="B63" s="140"/>
       <c r="S63" s="141"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="219"/>
+      <c r="A64" s="163"/>
       <c r="B64" s="140"/>
       <c r="S64" s="141"/>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="219"/>
+      <c r="A65" s="163"/>
       <c r="B65" s="140"/>
       <c r="S65" s="141"/>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="219"/>
+      <c r="A66" s="163"/>
       <c r="B66" s="140"/>
       <c r="S66" s="141"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="219"/>
+      <c r="A67" s="163"/>
       <c r="B67" s="140"/>
       <c r="S67" s="141"/>
     </row>
     <row r="68" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A68" s="220"/>
+      <c r="A68" s="164"/>
       <c r="B68" s="142"/>
       <c r="C68" s="77"/>
       <c r="D68" s="77"/>
@@ -5693,6 +5693,31 @@
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A68"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A36:A38"/>
@@ -5709,31 +5734,6 @@
     <mergeCell ref="O47:P48"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="F47:F48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="F43:R43"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L9:M9"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AA5CD3-3A2D-40AF-B11A-AB869DBF4ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3509BF60-C73A-4649-B070-72280732DEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -3867,8 +3867,23 @@
       <c r="A24" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="56"/>
-      <c r="C24" s="58"/>
+      <c r="B24" s="56" t="str" cm="1">
+        <f t="array" ref="B24">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),1))),"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="58" t="str" cm="1">
+        <f t="array" ref="C24">IFERROR(
+  IF(D24="buc",
+    IF(B24&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B24)*(Deco!$W$2:$W$99="MDF"), 0)),
+    ""),
+    IF(AND(B24&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B24)*(Deco!$W$2:$W$99="MDF"), 0))="MDF"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B24)*(Deco!$W$2:$W$99="MDF"), 0)),
+    "")
+  ),
+"")</f>
+        <v/>
+      </c>
       <c r="D24" s="37" t="str" cm="1">
         <f t="array" ref="D24">IF(I3="Debitare căntuire", IF(OR(RIGHT(B24,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(B24,2)="SM",RIGHT(B24,2)="PM",RIGHT(B24,2)="PG",RIGHT(B24,2)="mm",RIGHT(B24,2)="mp",RIGHT(B24,2)="PA",RIGHT(B24,2)="3D"),"buc","mp"), "mp")</f>
         <v>mp</v>
@@ -6123,9 +6138,9 @@
         <f>IF(Fisa!B24="","",IF(RIGHT(Fisa!B24,2)="3D",Fisa!B24,"MDF "&amp;Fisa!B24))</f>
         <v/>
       </c>
-      <c r="B14">
+      <c r="B14" t="str">
         <f>Fisa!C24</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C14" t="str">
         <f>_xlfn.CONCAT(Fisa!D24)</f>
@@ -6135,9 +6150,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E14" s="102" cm="1">
+      <c r="E14" s="102" t="str" cm="1">
         <f t="array" ref="E14">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B24,3)="AGT",B14*3.416, IF(OR(RIGHT(Fisa!B24,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B24,2)="SM",RIGHT(Fisa!B24,2)="PM",RIGHT(Fisa!B24,2)="PG",RIGHT(Fisa!B24,2)="mm",,RIGHT(Fisa!B24,2)="PG",RIGHT(Fisa!B24,2)="3D"), B14*5.796, B14)),B14)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="F14" t="s">
         <v>52</v>
@@ -9261,13 +9276,13 @@
       <c r="L19" s="5"/>
     </row>
     <row r="20" spans="1:12" customFormat="1">
-      <c r="B20" s="8">
+      <c r="B20" s="8" t="str">
         <f>Fisa!B24</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="8">
+        <v/>
+      </c>
+      <c r="C20" s="8" t="str">
         <f>Fisa!C24</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -10194,13 +10209,13 @@
       <c r="L49" s="5"/>
     </row>
     <row r="50" spans="1:29" customFormat="1">
-      <c r="B50" s="10">
+      <c r="B50" s="10" t="str">
         <f>Fisa!B24</f>
-        <v>0</v>
-      </c>
-      <c r="C50" s="10">
+        <v/>
+      </c>
+      <c r="C50" s="10" t="str">
         <f>Fisa!C24</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3509BF60-C73A-4649-B070-72280732DEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A047FFA7-6A9F-42FD-B120-0842FF60FC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Proforma!$A$1:$B$201</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -4404,7 +4404,7 @@
         <v>mp</v>
       </c>
       <c r="E30" s="48"/>
-      <c r="F30" s="150"/>
+      <c r="F30" s="151"/>
       <c r="G30" s="81"/>
       <c r="H30" s="85" t="str">
         <f t="shared" si="0"/>
@@ -4481,7 +4481,7 @@
         <v>78</v>
       </c>
       <c r="B32" s="56" t="str" cm="1">
-        <f t="array" ref="B32">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),1))),"")</f>
+        <f t="array" ref="B32">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),1))),"")</f>
         <v/>
       </c>
       <c r="C32" s="58" t="str">
@@ -4566,7 +4566,7 @@
     <row r="33" spans="1:19">
       <c r="A33" s="166"/>
       <c r="B33" s="67" t="str" cm="1">
-        <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
+        <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),2))),"")</f>
         <v/>
       </c>
       <c r="C33" s="109" t="str">
@@ -4651,7 +4651,7 @@
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
       <c r="A34" s="167"/>
       <c r="B34" s="67" t="str" cm="1">
-        <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
+        <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),3))),"")</f>
         <v/>
       </c>
       <c r="C34" s="109" t="str">
@@ -4733,7 +4733,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:19" s="50" customFormat="1" ht="2.1" hidden="1" customHeight="1">
+    <row r="35" spans="1:19" s="50" customFormat="1" ht="14.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A35" s="55"/>
       <c r="B35" s="62"/>
       <c r="C35" s="48"/>
@@ -5752,7 +5752,7 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="56" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="54" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -5821,7 +5821,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="102"/>
   </cols>
   <sheetData>
@@ -8911,7 +8911,7 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="3" customWidth="1"/>
     <col min="4" max="6" width="10.42578125" style="3" customWidth="1"/>
     <col min="7" max="7" width="10.28515625" style="3" customWidth="1"/>
@@ -10976,6 +10976,7 @@
     <col min="22" max="22" width="9.140625" style="133"/>
     <col min="24" max="24" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
@@ -11028,19 +11029,23 @@
         OR(
             AND(D2=2800,E2=2070,OR(B2=19,B2=19.3)),
             AND(D2=2800,E2=1220,B2=18),
-            AND(D2=3050,E2=1300,B2=19.3),
-            AND(D2=2800,E2=1300,B2=17.5),
-            AND(D2=2800,E2=1300,B2=19),
-            RIGHT(A2,6)="MDF 3D"
+            AND(D2=3050,E2=1300,B2=19),
+            AND(D2=3050,E2=1310,B2=19),
+            AND(D2=2800,E2=1300,OR(B2=17.5,B2=19)),
+            AND(RIGHT(A2,6)="MDF 3D",B2&lt;&gt;36)
         ),
-        NOT(OR(ISNUMBER(FIND(" TM",A2)),ISNUMBER(FIND("TM/ST",A2))))
+        NOT(OR(
+            ISNUMBER(FIND(" TM",A2)),
+            ISNUMBER(FIND("TM/ST",A2))
+        )),
+        RIGHT(A2,6)&lt;&gt;"ROH P2"
     ),
     "MDF",
     IF(
         AND(
             D2=2800,
-            E2=2070,
-            OR(B2=18,B2=18.6,B2=8,B2=10,B2=16),
+            OR(E2=2070,E2=1000),
+            OR(B2=18,B2=18.6,B2=8,B2=10,B2=16,B2=19),
             RIGHT(A2,6)&lt;&gt;"MDF 3D"
         ),
         "PAL",
@@ -11063,39 +11068,47 @@
                 IF(
                     AND(
                         D2=4100,
-                        OR(E2=600,E2=650,E2=920),
+                        OR(E2=600,E2=650,E2=920,E2=1200),
                         OR(B2=38,B2=20)
                     ),
                     "BLAT",
                     IF(
                         AND(
                             D2=4100,
-                            E2=640,
-                            OR(B2=9.2,B2=8,B2=8,8)
+                            OR(E2=600,E2=650,E2=920),
+                            OR(B2=12)
                         ),
-                        "PS",
+                        "LC",
                         IF(
                             AND(
-                                OR(
-                                    AND(D2=2800,E2=2070,OR(B2=38,B2=38.6)),
-                                    AND(D2=2800,E2=1220,B2=36),
-                                    AND(D2=3050,E2=1300,B2=38.6),
-                                    AND(D2=2800,E2=1300,B2=35),
-                                    AND(D2=2800,E2=1300,B2=38),
-                                    AND(RIGHT(A2,6)="MDF 3D",B2=36)
-                                ),
-                                NOT(OR(ISNUMBER(FIND(" TM",A2)),ISNUMBER(FIND("TM/ST",A2))))
+                                D2=4100,
+                                E2=640,
+                                OR(B2=9.2,B2=8,B2=8.8)
                             ),
-                            "DB MDF",
+                            "PS",
                             IF(
                                 AND(
-                                    D2=2800,
-                                    E2=2070,
-                                    OR(B2=36,B2=37.2,B2=32,B2=26,B2=28),
-                                    RIGHT(A2,6)&lt;&gt;"MDF 3D"
+                                    OR(
+                                        AND(D2=2800,E2=2070,OR(B2=38,B2=38.6)),
+                                        AND(D2=2800,E2=1220,B2=36),
+                                        AND(D2=3050,OR(E2=1300,E2=1310),OR(B2=38.6,B2=38,B2=38.1)),
+                                        AND(D2=2800,E2=1300,B2=35),
+                                        AND(D2=2800,E2=1300,B2=38),
+                                        AND(RIGHT(A2,6)="MDF 3D",B2=36)
+                                    ),
+                                    NOT(OR(ISNUMBER(FIND(" TM",A2)),ISNUMBER(FIND("TM/ST",A2))))
                                 ),
-                                "DB PAL",
-                                IF(B2=2.7,"HDF","N/A")
+                                "DB MDF",
+                                IF(
+                                    AND(
+                                        D2=2800,
+                                        E2=2070,
+                                        OR(B2=36,B2=37.2,B2=32,B2=26,B2=28),
+                                        RIGHT(A2,6)&lt;&gt;"MDF 3D"
+                                    ),
+                                    "DB PAL",
+                                    IF(B2=2.7,"HDF","N/A")
+                                )
                             )
                         )
                     )
@@ -11138,6 +11151,7 @@
             IFERROR(LEFT(X2, FIND("/",X2)-1), X2)
         )
     )
+    &amp;IF(W2="LC"," LC","")
 )</f>
         <v/>
       </c>
@@ -11180,19 +11194,23 @@
         OR(
             AND(D3=2800,E3=2070,OR(B3=19,B3=19.3)),
             AND(D3=2800,E3=1220,B3=18),
-            AND(D3=3050,E3=1300,B3=19.3),
-            AND(D3=2800,E3=1300,B3=17.5),
-            AND(D3=2800,E3=1300,B3=19),
-            RIGHT(A3,6)="MDF 3D"
+            AND(D3=3050,E3=1300,B3=19),
+            AND(D3=3050,E3=1310,B3=19),
+            AND(D3=2800,E3=1300,OR(B3=17.5,B3=19)),
+            AND(RIGHT(A3,6)="MDF 3D",B3&lt;&gt;36)
         ),
-        NOT(OR(ISNUMBER(FIND(" TM",A3)),ISNUMBER(FIND("TM/ST",A3))))
+        NOT(OR(
+            ISNUMBER(FIND(" TM",A3)),
+            ISNUMBER(FIND("TM/ST",A3))
+        )),
+        RIGHT(A3,6)&lt;&gt;"ROH P2"
     ),
     "MDF",
     IF(
         AND(
             D3=2800,
-            E3=2070,
-            OR(B3=18,B3=18.6,B3=8,B3=10,B3=16),
+            OR(E3=2070,E3=1000),
+            OR(B3=18,B3=18.6,B3=8,B3=10,B3=16,B3=19),
             RIGHT(A3,6)&lt;&gt;"MDF 3D"
         ),
         "PAL",
@@ -11215,39 +11233,47 @@
                 IF(
                     AND(
                         D3=4100,
-                        OR(E3=600,E3=650,E3=920),
+                        OR(E3=600,E3=650,E3=920,E3=1200),
                         OR(B3=38,B3=20)
                     ),
                     "BLAT",
                     IF(
                         AND(
                             D3=4100,
-                            E3=640,
-                            OR(B3=9.2,B3=8,B3=8,8)
+                            OR(E3=600,E3=650,E3=920),
+                            OR(B3=12)
                         ),
-                        "PS",
+                        "LC",
                         IF(
                             AND(
-                                OR(
-                                    AND(D3=2800,E3=2070,OR(B3=38,B3=38.6)),
-                                    AND(D3=2800,E3=1220,B3=36),
-                                    AND(D3=3050,E3=1300,B3=38.6),
-                                    AND(D3=2800,E3=1300,B3=35),
-                                    AND(D3=2800,E3=1300,B3=38),
-                                    AND(RIGHT(A3,6)="MDF 3D",B3=36)
-                                ),
-                                NOT(OR(ISNUMBER(FIND(" TM",A3)),ISNUMBER(FIND("TM/ST",A3))))
+                                D3=4100,
+                                E3=640,
+                                OR(B3=9.2,B3=8,B3=8.8)
                             ),
-                            "DB MDF",
+                            "PS",
                             IF(
                                 AND(
-                                    D3=2800,
-                                    E3=2070,
-                                    OR(B3=36,B3=37.2,B3=32,B3=26,B3=28),
-                                    RIGHT(A3,6)&lt;&gt;"MDF 3D"
+                                    OR(
+                                        AND(D3=2800,E3=2070,OR(B3=38,B3=38.6)),
+                                        AND(D3=2800,E3=1220,B3=36),
+                                        AND(D3=3050,OR(E3=1300,E3=1310),OR(B3=38.6,B3=38,B3=38.1)),
+                                        AND(D3=2800,E3=1300,B3=35),
+                                        AND(D3=2800,E3=1300,B3=38),
+                                        AND(RIGHT(A3,6)="MDF 3D",B3=36)
+                                    ),
+                                    NOT(OR(ISNUMBER(FIND(" TM",A3)),ISNUMBER(FIND("TM/ST",A3))))
                                 ),
-                                "DB PAL",
-                                IF(B3=2.7,"HDF","N/A")
+                                "DB MDF",
+                                IF(
+                                    AND(
+                                        D3=2800,
+                                        E3=2070,
+                                        OR(B3=36,B3=37.2,B3=32,B3=26,B3=28),
+                                        RIGHT(A3,6)&lt;&gt;"MDF 3D"
+                                    ),
+                                    "DB PAL",
+                                    IF(B3=2.7,"HDF","N/A")
+                                )
                             )
                         )
                     )
@@ -11290,6 +11316,7 @@
             IFERROR(LEFT(X3, FIND("/",X3)-1), X3)
         )
     )
+    &amp;IF(W3="LC"," LC","")
 )</f>
         <v/>
       </c>
@@ -12331,7 +12358,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="H3" t="str">
-        <f t="shared" ref="H3:H17" si="1">RIGHT(A3,3)</f>
+        <f t="shared" ref="H3:H23" si="1">RIGHT(A3,3)</f>
         <v/>
       </c>
       <c r="I3">
@@ -12682,6 +12709,10 @@
       </c>
     </row>
     <row r="18" spans="8:13">
+      <c r="H18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I18">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12700,6 +12731,10 @@
       </c>
     </row>
     <row r="19" spans="8:13">
+      <c r="H19" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I19">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12718,6 +12753,10 @@
       </c>
     </row>
     <row r="20" spans="8:13">
+      <c r="H20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I20">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12736,6 +12775,10 @@
       </c>
     </row>
     <row r="21" spans="8:13">
+      <c r="H21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I21">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12754,6 +12797,10 @@
       </c>
     </row>
     <row r="22" spans="8:13">
+      <c r="H22" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I22">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12772,6 +12819,10 @@
       </c>
     </row>
     <row r="23" spans="8:13">
+      <c r="H23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="I23">
         <f t="shared" si="2"/>
         <v>0</v>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A047FFA7-6A9F-42FD-B120-0842FF60FC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CF0862-AB8A-48FE-9A20-E736A2CC7A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -1671,82 +1671,90 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1794,12 +1802,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1857,78 +1859,76 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2416,33 +2416,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="202" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="205"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="203"/>
+      <c r="L1" s="204"/>
       <c r="M1" s="38" t="s">
         <v>70</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="194" t="s">
+      <c r="O1" s="195" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="196"/>
+      <c r="P1" s="196"/>
+      <c r="Q1" s="196"/>
+      <c r="R1" s="196"/>
+      <c r="S1" s="197"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2461,165 +2461,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="80"/>
-      <c r="O2" s="197"/>
-      <c r="P2" s="198"/>
-      <c r="Q2" s="198"/>
-      <c r="R2" s="198"/>
-      <c r="S2" s="199"/>
+      <c r="O2" s="198"/>
+      <c r="P2" s="199"/>
+      <c r="Q2" s="199"/>
+      <c r="R2" s="199"/>
+      <c r="S2" s="200"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="209"/>
-      <c r="C3" s="210"/>
-      <c r="D3" s="211"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
       <c r="H3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="216"/>
-      <c r="J3" s="217"/>
-      <c r="K3" s="218"/>
+      <c r="I3" s="215"/>
+      <c r="J3" s="216"/>
+      <c r="K3" s="217"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="73"/>
-      <c r="O3" s="206"/>
-      <c r="P3" s="207"/>
-      <c r="Q3" s="207"/>
-      <c r="R3" s="207"/>
-      <c r="S3" s="208"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="206"/>
+      <c r="Q3" s="206"/>
+      <c r="R3" s="206"/>
+      <c r="S3" s="207"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="188"/>
-      <c r="C4" s="189"/>
-      <c r="D4" s="190"/>
+      <c r="B4" s="189"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="191"/>
       <c r="H4" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="191"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="73"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="207"/>
-      <c r="Q4" s="207"/>
-      <c r="R4" s="207"/>
-      <c r="S4" s="208"/>
+      <c r="O4" s="205"/>
+      <c r="P4" s="206"/>
+      <c r="Q4" s="206"/>
+      <c r="R4" s="206"/>
+      <c r="S4" s="207"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="212"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="214"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="H5" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="215"/>
-      <c r="J5" s="207"/>
-      <c r="K5" s="208"/>
+      <c r="I5" s="214"/>
+      <c r="J5" s="206"/>
+      <c r="K5" s="207"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="73"/>
-      <c r="O5" s="206"/>
-      <c r="P5" s="207"/>
-      <c r="Q5" s="207"/>
-      <c r="R5" s="207"/>
-      <c r="S5" s="208"/>
+      <c r="O5" s="205"/>
+      <c r="P5" s="206"/>
+      <c r="Q5" s="206"/>
+      <c r="R5" s="206"/>
+      <c r="S5" s="207"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="223"/>
-      <c r="C6" s="224"/>
-      <c r="D6" s="225"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="170"/>
       <c r="H6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="226"/>
-      <c r="J6" s="201"/>
-      <c r="K6" s="202"/>
+      <c r="I6" s="171"/>
+      <c r="J6" s="172"/>
+      <c r="K6" s="173"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="74"/>
-      <c r="O6" s="200"/>
-      <c r="P6" s="201"/>
-      <c r="Q6" s="201"/>
-      <c r="R6" s="201"/>
-      <c r="S6" s="202"/>
+      <c r="O6" s="201"/>
+      <c r="P6" s="172"/>
+      <c r="Q6" s="172"/>
+      <c r="R6" s="172"/>
+      <c r="S6" s="173"/>
     </row>
     <row r="7" spans="1:19" s="50" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="227" t="s">
+      <c r="A8" s="174" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="228"/>
-      <c r="C8" s="228"/>
-      <c r="D8" s="229"/>
-      <c r="F8" s="233" t="s">
+      <c r="B8" s="175"/>
+      <c r="C8" s="175"/>
+      <c r="D8" s="176"/>
+      <c r="F8" s="180" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="234"/>
-      <c r="H8" s="234"/>
-      <c r="I8" s="234"/>
-      <c r="J8" s="234"/>
-      <c r="K8" s="234"/>
-      <c r="L8" s="234"/>
-      <c r="M8" s="234"/>
-      <c r="N8" s="234"/>
-      <c r="O8" s="234"/>
-      <c r="P8" s="234"/>
-      <c r="Q8" s="234"/>
-      <c r="R8" s="234"/>
-      <c r="S8" s="239"/>
+      <c r="G8" s="181"/>
+      <c r="H8" s="181"/>
+      <c r="I8" s="181"/>
+      <c r="J8" s="181"/>
+      <c r="K8" s="181"/>
+      <c r="L8" s="181"/>
+      <c r="M8" s="181"/>
+      <c r="N8" s="181"/>
+      <c r="O8" s="181"/>
+      <c r="P8" s="181"/>
+      <c r="Q8" s="181"/>
+      <c r="R8" s="181"/>
+      <c r="S8" s="186"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="230"/>
-      <c r="B9" s="231"/>
-      <c r="C9" s="231"/>
-      <c r="D9" s="232"/>
-      <c r="F9" s="170" t="s">
+      <c r="A9" s="177"/>
+      <c r="B9" s="178"/>
+      <c r="C9" s="178"/>
+      <c r="D9" s="179"/>
+      <c r="F9" s="226" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="171"/>
-      <c r="H9" s="186" t="s">
+      <c r="G9" s="227"/>
+      <c r="H9" s="240" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="187"/>
-      <c r="J9" s="168" t="s">
+      <c r="I9" s="241"/>
+      <c r="J9" s="224" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="169"/>
-      <c r="L9" s="240" t="s">
+      <c r="K9" s="225"/>
+      <c r="L9" s="187" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="241"/>
-      <c r="N9" s="237" t="s">
+      <c r="M9" s="188"/>
+      <c r="N9" s="184" t="s">
         <v>80</v>
       </c>
-      <c r="O9" s="238"/>
-      <c r="P9" s="235" t="s">
+      <c r="O9" s="185"/>
+      <c r="P9" s="182" t="s">
         <v>68</v>
       </c>
-      <c r="Q9" s="236"/>
-      <c r="R9" s="237" t="s">
+      <c r="Q9" s="183"/>
+      <c r="R9" s="184" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="238"/>
+      <c r="S9" s="185"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="175" t="s">
+      <c r="A10" s="231" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2676,7 +2676,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="176"/>
+      <c r="A11" s="232"/>
       <c r="B11" s="56" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2767,7 +2767,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="176"/>
+      <c r="A12" s="232"/>
       <c r="B12" s="108" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -2859,7 +2859,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="176"/>
+      <c r="A13" s="232"/>
       <c r="B13" s="108" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -2955,7 +2955,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="176"/>
+      <c r="A14" s="232"/>
       <c r="B14" s="108" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3051,7 +3051,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="176"/>
+      <c r="A15" s="232"/>
       <c r="B15" s="108" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3147,7 +3147,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="176"/>
+      <c r="A16" s="232"/>
       <c r="B16" s="108" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3243,7 +3243,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="176"/>
+      <c r="A17" s="232"/>
       <c r="B17" s="108" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3339,7 +3339,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="176"/>
+      <c r="A18" s="232"/>
       <c r="B18" s="108" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3435,7 +3435,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="176"/>
+      <c r="A19" s="232"/>
       <c r="B19" s="108" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3531,7 +3531,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="176"/>
+      <c r="A20" s="232"/>
       <c r="B20" s="108" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3627,7 +3627,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="176"/>
+      <c r="A21" s="232"/>
       <c r="B21" s="108" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3723,7 +3723,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="177"/>
+      <c r="A22" s="233"/>
       <c r="B22" s="108" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3864,7 +3864,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="175" t="s">
+      <c r="A24" s="231" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="56" t="str" cm="1">
@@ -3962,7 +3962,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="176"/>
+      <c r="A25" s="232"/>
       <c r="B25" s="67" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4058,7 +4058,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="176"/>
+      <c r="A26" s="232"/>
       <c r="B26" s="67" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4154,7 +4154,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="176"/>
+      <c r="A27" s="232"/>
       <c r="B27" s="67" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="178"/>
+      <c r="A28" s="234"/>
       <c r="B28" s="67" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4477,7 +4477,7 @@
       <c r="S31" s="160"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="165" t="s">
+      <c r="A32" s="221" t="s">
         <v>78</v>
       </c>
       <c r="B32" s="56" t="str" cm="1">
@@ -4564,7 +4564,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="166"/>
+      <c r="A33" s="222"/>
       <c r="B33" s="67" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),2))),"")</f>
         <v/>
@@ -4649,7 +4649,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="167"/>
+      <c r="A34" s="223"/>
       <c r="B34" s="67" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),3))),"")</f>
         <v/>
@@ -4773,7 +4773,7 @@
       <c r="S35" s="161"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="165" t="s">
+      <c r="A36" s="221" t="s">
         <v>79</v>
       </c>
       <c r="B36" s="56" t="str" cm="1">
@@ -4860,7 +4860,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="166"/>
+      <c r="A37" s="222"/>
       <c r="B37" s="67" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4945,7 +4945,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="167"/>
+      <c r="A38" s="223"/>
       <c r="B38" s="68" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5044,7 +5044,7 @@
       <c r="Q39" s="61"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="175" t="s">
+      <c r="A40" s="231" t="s">
         <v>50</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5056,25 +5056,25 @@
       <c r="D40" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="172" t="s">
+      <c r="F40" s="228" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="173"/>
-      <c r="H40" s="173"/>
-      <c r="I40" s="173"/>
-      <c r="J40" s="173"/>
-      <c r="K40" s="173"/>
-      <c r="L40" s="173"/>
-      <c r="M40" s="173"/>
-      <c r="N40" s="173"/>
-      <c r="O40" s="173"/>
-      <c r="P40" s="173"/>
-      <c r="Q40" s="173"/>
-      <c r="R40" s="173"/>
-      <c r="S40" s="174"/>
+      <c r="G40" s="229"/>
+      <c r="H40" s="229"/>
+      <c r="I40" s="229"/>
+      <c r="J40" s="229"/>
+      <c r="K40" s="229"/>
+      <c r="L40" s="229"/>
+      <c r="M40" s="229"/>
+      <c r="N40" s="229"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="229"/>
+      <c r="Q40" s="229"/>
+      <c r="R40" s="229"/>
+      <c r="S40" s="230"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="176"/>
+      <c r="A41" s="232"/>
       <c r="B41" s="35" t="s">
         <v>81</v>
       </c>
@@ -5137,7 +5137,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="176"/>
+      <c r="A42" s="232"/>
       <c r="B42" s="49" t="s">
         <v>88</v>
       </c>
@@ -5162,13 +5162,13 @@
       <c r="P42" s="66"/>
       <c r="Q42" s="78"/>
       <c r="R42" s="79"/>
-      <c r="S42" s="179">
+      <c r="S42" s="162">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="176"/>
+      <c r="A43" s="232"/>
       <c r="B43" s="49" t="s">
         <v>82</v>
       </c>
@@ -5180,26 +5180,26 @@
         <v>54</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="233" t="str">
+      <c r="F43" s="180" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="234"/>
-      <c r="H43" s="234"/>
-      <c r="I43" s="234"/>
-      <c r="J43" s="234"/>
-      <c r="K43" s="234"/>
-      <c r="L43" s="234"/>
-      <c r="M43" s="234"/>
-      <c r="N43" s="234"/>
-      <c r="O43" s="234"/>
-      <c r="P43" s="234"/>
-      <c r="Q43" s="234"/>
-      <c r="R43" s="234"/>
-      <c r="S43" s="180"/>
+      <c r="G43" s="181"/>
+      <c r="H43" s="181"/>
+      <c r="I43" s="181"/>
+      <c r="J43" s="181"/>
+      <c r="K43" s="181"/>
+      <c r="L43" s="181"/>
+      <c r="M43" s="181"/>
+      <c r="N43" s="181"/>
+      <c r="O43" s="181"/>
+      <c r="P43" s="181"/>
+      <c r="Q43" s="181"/>
+      <c r="R43" s="181"/>
+      <c r="S43" s="235"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="176"/>
+      <c r="A44" s="232"/>
       <c r="B44" s="49" t="s">
         <v>87</v>
       </c>
@@ -5255,7 +5255,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="176"/>
+      <c r="A45" s="232"/>
       <c r="B45" s="33" t="s">
         <v>89</v>
       </c>
@@ -5389,7 +5389,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="176"/>
+      <c r="A46" s="232"/>
       <c r="B46" s="33" t="s">
         <v>83</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="176"/>
+      <c r="A47" s="232"/>
       <c r="B47" s="33" t="s">
         <v>84</v>
       </c>
@@ -5414,31 +5414,31 @@
       <c r="D47" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="179" t="s">
+      <c r="F47" s="162" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="221" t="str">
+      <c r="G47" s="166" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="179" t="s">
+      <c r="J47" s="162" t="s">
         <v>86</v>
       </c>
-      <c r="K47" s="219">
+      <c r="K47" s="164">
         <v>1</v>
       </c>
-      <c r="N47" s="179" t="s">
+      <c r="N47" s="162" t="s">
         <v>108</v>
       </c>
-      <c r="O47" s="182"/>
-      <c r="P47" s="183"/>
-      <c r="R47" s="179" t="s">
+      <c r="O47" s="236"/>
+      <c r="P47" s="237"/>
+      <c r="R47" s="162" t="s">
         <v>114</v>
       </c>
-      <c r="S47" s="179"/>
+      <c r="S47" s="162"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="178"/>
+      <c r="A48" s="234"/>
       <c r="B48" s="36" t="s">
         <v>85</v>
       </c>
@@ -5449,15 +5449,15 @@
       <c r="D48" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="F48" s="181"/>
-      <c r="G48" s="222"/>
-      <c r="J48" s="181"/>
-      <c r="K48" s="220"/>
-      <c r="N48" s="180"/>
-      <c r="O48" s="184"/>
-      <c r="P48" s="185"/>
-      <c r="R48" s="180"/>
-      <c r="S48" s="181"/>
+      <c r="F48" s="163"/>
+      <c r="G48" s="167"/>
+      <c r="J48" s="163"/>
+      <c r="K48" s="165"/>
+      <c r="N48" s="235"/>
+      <c r="O48" s="238"/>
+      <c r="P48" s="239"/>
+      <c r="R48" s="235"/>
+      <c r="S48" s="163"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5466,7 +5466,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="162" t="s">
+      <c r="A50" s="218" t="s">
         <v>65</v>
       </c>
       <c r="B50" s="134"/>
@@ -5489,7 +5489,7 @@
       <c r="S50" s="136"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="163"/>
+      <c r="A51" s="219"/>
       <c r="B51" s="137"/>
       <c r="C51" s="139"/>
       <c r="D51" s="139"/>
@@ -5510,7 +5510,7 @@
       <c r="S51" s="138"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="163"/>
+      <c r="A52" s="219"/>
       <c r="B52" s="137"/>
       <c r="C52" s="139"/>
       <c r="D52" s="139"/>
@@ -5531,7 +5531,7 @@
       <c r="S52" s="138"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="163"/>
+      <c r="A53" s="219"/>
       <c r="B53" s="137"/>
       <c r="C53" s="139"/>
       <c r="D53" s="139"/>
@@ -5552,7 +5552,7 @@
       <c r="S53" s="138"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="163"/>
+      <c r="A54" s="219"/>
       <c r="B54" s="137"/>
       <c r="C54" s="139"/>
       <c r="D54" s="139"/>
@@ -5573,7 +5573,7 @@
       <c r="S54" s="138"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="163"/>
+      <c r="A55" s="219"/>
       <c r="B55" s="137"/>
       <c r="C55" s="139"/>
       <c r="D55" s="139"/>
@@ -5594,7 +5594,7 @@
       <c r="S55" s="138"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="163"/>
+      <c r="A56" s="219"/>
       <c r="B56" s="137"/>
       <c r="C56" s="139"/>
       <c r="D56" s="139"/>
@@ -5615,7 +5615,7 @@
       <c r="S56" s="138"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="163"/>
+      <c r="A57" s="219"/>
       <c r="B57" s="137"/>
       <c r="C57" s="139"/>
       <c r="D57" s="139"/>
@@ -5636,57 +5636,57 @@
       <c r="S57" s="138"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="163"/>
+      <c r="A58" s="219"/>
       <c r="B58" s="140"/>
       <c r="S58" s="141"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="163"/>
+      <c r="A59" s="219"/>
       <c r="B59" s="140"/>
       <c r="S59" s="141"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="163"/>
+      <c r="A60" s="219"/>
       <c r="B60" s="140"/>
       <c r="S60" s="141"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="163"/>
+      <c r="A61" s="219"/>
       <c r="B61" s="140"/>
       <c r="S61" s="141"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="163"/>
+      <c r="A62" s="219"/>
       <c r="B62" s="140"/>
       <c r="S62" s="141"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="163"/>
+      <c r="A63" s="219"/>
       <c r="B63" s="140"/>
       <c r="S63" s="141"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="163"/>
+      <c r="A64" s="219"/>
       <c r="B64" s="140"/>
       <c r="S64" s="141"/>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="163"/>
+      <c r="A65" s="219"/>
       <c r="B65" s="140"/>
       <c r="S65" s="141"/>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="163"/>
+      <c r="A66" s="219"/>
       <c r="B66" s="140"/>
       <c r="S66" s="141"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="163"/>
+      <c r="A67" s="219"/>
       <c r="B67" s="140"/>
       <c r="S67" s="141"/>
     </row>
     <row r="68" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A68" s="164"/>
+      <c r="A68" s="220"/>
       <c r="B68" s="142"/>
       <c r="C68" s="77"/>
       <c r="D68" s="77"/>
@@ -5708,31 +5708,6 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="F43:R43"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A68"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A36:A38"/>
@@ -5749,6 +5724,31 @@
     <mergeCell ref="O47:P48"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="F47:F48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L9:M9"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12338,7 +12338,7 @@
         <v/>
       </c>
       <c r="I2">
-        <f>ROUNDUP(E2*1.05,0)</f>
+        <f>ROUNDUP(E2*1.03,0)</f>
         <v>0</v>
       </c>
       <c r="J2" t="str">
@@ -12362,7 +12362,7 @@
         <v/>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I23" si="2">ROUNDUP(E3*1.05,0)</f>
+        <f t="shared" ref="I3:I23" si="2">ROUNDUP(E3*1.03,0)</f>
         <v>0</v>
       </c>
       <c r="J3" t="str">

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CF0862-AB8A-48FE-9A20-E736A2CC7A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C57C1681-D468-4C63-B478-ACD1F6421CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1671,11 +1671,191 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1706,12 +1886,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1755,180 +1929,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2416,33 +2416,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="203" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="204"/>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="205"/>
       <c r="M1" s="38" t="s">
         <v>70</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="195" t="s">
+      <c r="O1" s="194" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="196"/>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="197"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="196"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2461,165 +2461,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="80"/>
-      <c r="O2" s="198"/>
-      <c r="P2" s="199"/>
-      <c r="Q2" s="199"/>
-      <c r="R2" s="199"/>
-      <c r="S2" s="200"/>
+      <c r="O2" s="197"/>
+      <c r="P2" s="198"/>
+      <c r="Q2" s="198"/>
+      <c r="R2" s="198"/>
+      <c r="S2" s="199"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="208"/>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="B3" s="209"/>
+      <c r="C3" s="210"/>
+      <c r="D3" s="211"/>
       <c r="H3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="215"/>
-      <c r="J3" s="216"/>
-      <c r="K3" s="217"/>
+      <c r="I3" s="216"/>
+      <c r="J3" s="217"/>
+      <c r="K3" s="218"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="73"/>
-      <c r="O3" s="205"/>
-      <c r="P3" s="206"/>
-      <c r="Q3" s="206"/>
-      <c r="R3" s="206"/>
-      <c r="S3" s="207"/>
+      <c r="O3" s="206"/>
+      <c r="P3" s="207"/>
+      <c r="Q3" s="207"/>
+      <c r="R3" s="207"/>
+      <c r="S3" s="208"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="189"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="B4" s="188"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="190"/>
       <c r="H4" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="192"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="194"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="192"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="73"/>
-      <c r="O4" s="205"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="206"/>
-      <c r="S4" s="207"/>
+      <c r="O4" s="206"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="208"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="211"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="213"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="H5" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="214"/>
-      <c r="J5" s="206"/>
-      <c r="K5" s="207"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="207"/>
+      <c r="K5" s="208"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="73"/>
-      <c r="O5" s="205"/>
-      <c r="P5" s="206"/>
-      <c r="Q5" s="206"/>
-      <c r="R5" s="206"/>
-      <c r="S5" s="207"/>
+      <c r="O5" s="206"/>
+      <c r="P5" s="207"/>
+      <c r="Q5" s="207"/>
+      <c r="R5" s="207"/>
+      <c r="S5" s="208"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="168"/>
-      <c r="C6" s="169"/>
-      <c r="D6" s="170"/>
+      <c r="B6" s="223"/>
+      <c r="C6" s="224"/>
+      <c r="D6" s="225"/>
       <c r="H6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="171"/>
-      <c r="J6" s="172"/>
-      <c r="K6" s="173"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="201"/>
+      <c r="K6" s="202"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="74"/>
-      <c r="O6" s="201"/>
-      <c r="P6" s="172"/>
-      <c r="Q6" s="172"/>
-      <c r="R6" s="172"/>
-      <c r="S6" s="173"/>
+      <c r="O6" s="200"/>
+      <c r="P6" s="201"/>
+      <c r="Q6" s="201"/>
+      <c r="R6" s="201"/>
+      <c r="S6" s="202"/>
     </row>
     <row r="7" spans="1:19" s="50" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="174" t="s">
+      <c r="A8" s="227" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="175"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="176"/>
-      <c r="F8" s="180" t="s">
+      <c r="B8" s="228"/>
+      <c r="C8" s="228"/>
+      <c r="D8" s="229"/>
+      <c r="F8" s="233" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="181"/>
-      <c r="H8" s="181"/>
-      <c r="I8" s="181"/>
-      <c r="J8" s="181"/>
-      <c r="K8" s="181"/>
-      <c r="L8" s="181"/>
-      <c r="M8" s="181"/>
-      <c r="N8" s="181"/>
-      <c r="O8" s="181"/>
-      <c r="P8" s="181"/>
-      <c r="Q8" s="181"/>
-      <c r="R8" s="181"/>
-      <c r="S8" s="186"/>
+      <c r="G8" s="234"/>
+      <c r="H8" s="234"/>
+      <c r="I8" s="234"/>
+      <c r="J8" s="234"/>
+      <c r="K8" s="234"/>
+      <c r="L8" s="234"/>
+      <c r="M8" s="234"/>
+      <c r="N8" s="234"/>
+      <c r="O8" s="234"/>
+      <c r="P8" s="234"/>
+      <c r="Q8" s="234"/>
+      <c r="R8" s="234"/>
+      <c r="S8" s="239"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="177"/>
-      <c r="B9" s="178"/>
-      <c r="C9" s="178"/>
-      <c r="D9" s="179"/>
-      <c r="F9" s="226" t="s">
+      <c r="A9" s="230"/>
+      <c r="B9" s="231"/>
+      <c r="C9" s="231"/>
+      <c r="D9" s="232"/>
+      <c r="F9" s="170" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="227"/>
-      <c r="H9" s="240" t="s">
+      <c r="G9" s="171"/>
+      <c r="H9" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="241"/>
-      <c r="J9" s="224" t="s">
+      <c r="I9" s="187"/>
+      <c r="J9" s="168" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="225"/>
-      <c r="L9" s="187" t="s">
+      <c r="K9" s="169"/>
+      <c r="L9" s="240" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="188"/>
-      <c r="N9" s="184" t="s">
+      <c r="M9" s="241"/>
+      <c r="N9" s="237" t="s">
         <v>80</v>
       </c>
-      <c r="O9" s="185"/>
-      <c r="P9" s="182" t="s">
+      <c r="O9" s="238"/>
+      <c r="P9" s="235" t="s">
         <v>68</v>
       </c>
-      <c r="Q9" s="183"/>
-      <c r="R9" s="184" t="s">
+      <c r="Q9" s="236"/>
+      <c r="R9" s="237" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="185"/>
+      <c r="S9" s="238"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="231" t="s">
+      <c r="A10" s="175" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2676,7 +2676,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="232"/>
+      <c r="A11" s="176"/>
       <c r="B11" s="56" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2754,7 +2754,7 @@
         <v/>
       </c>
       <c r="Q11" s="29" t="str">
-        <f>IFERROR(IF(AND(P11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
+        <f>IFERROR(IF(AND(P11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"24/1.5"),""),"")</f>
         <v/>
       </c>
       <c r="R11" s="56" t="str">
@@ -2767,7 +2767,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="232"/>
+      <c r="A12" s="176"/>
       <c r="B12" s="108" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -2846,7 +2846,7 @@
         <v/>
       </c>
       <c r="Q12" s="30" t="str">
-        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(P12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(P12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R12" s="67" t="str">
@@ -2859,7 +2859,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="232"/>
+      <c r="A13" s="176"/>
       <c r="B13" s="108" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -2942,7 +2942,7 @@
         <v/>
       </c>
       <c r="Q13" s="30" t="str">
-        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(P13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(P13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R13" s="67" t="str">
@@ -2955,7 +2955,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="232"/>
+      <c r="A14" s="176"/>
       <c r="B14" s="108" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3038,7 +3038,7 @@
         <v/>
       </c>
       <c r="Q14" s="30" t="str">
-        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(P14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(P14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R14" s="67" t="str">
@@ -3051,7 +3051,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="232"/>
+      <c r="A15" s="176"/>
       <c r="B15" s="108" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3134,7 +3134,7 @@
         <v/>
       </c>
       <c r="Q15" s="30" t="str">
-        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(P15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(P15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R15" s="67" t="str">
@@ -3147,7 +3147,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="232"/>
+      <c r="A16" s="176"/>
       <c r="B16" s="108" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3230,7 +3230,7 @@
         <v/>
       </c>
       <c r="Q16" s="30" t="str">
-        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(P16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(P16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R16" s="67" t="str">
@@ -3243,7 +3243,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="232"/>
+      <c r="A17" s="176"/>
       <c r="B17" s="108" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3326,7 +3326,7 @@
         <v/>
       </c>
       <c r="Q17" s="30" t="str">
-        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(P17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(P17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R17" s="67" t="str">
@@ -3339,7 +3339,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="232"/>
+      <c r="A18" s="176"/>
       <c r="B18" s="108" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3422,7 +3422,7 @@
         <v/>
       </c>
       <c r="Q18" s="30" t="str">
-        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(P18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(P18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R18" s="67" t="str">
@@ -3435,7 +3435,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="232"/>
+      <c r="A19" s="176"/>
       <c r="B19" s="108" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3518,7 +3518,7 @@
         <v/>
       </c>
       <c r="Q19" s="30" t="str">
-        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(P19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(P19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R19" s="67" t="str">
@@ -3531,7 +3531,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="232"/>
+      <c r="A20" s="176"/>
       <c r="B20" s="108" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3614,7 +3614,7 @@
         <v/>
       </c>
       <c r="Q20" s="30" t="str">
-        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(P20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(P20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R20" s="67" t="str">
@@ -3627,7 +3627,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="232"/>
+      <c r="A21" s="176"/>
       <c r="B21" s="108" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3710,7 +3710,7 @@
         <v/>
       </c>
       <c r="Q21" s="30" t="str">
-        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(P21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(P21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R21" s="67" t="str">
@@ -3723,7 +3723,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="233"/>
+      <c r="A22" s="177"/>
       <c r="B22" s="108" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3806,7 +3806,7 @@
         <v/>
       </c>
       <c r="Q22" s="30" t="str">
-        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(P22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(P22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R22" s="67" t="str">
@@ -3864,7 +3864,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="231" t="s">
+      <c r="A24" s="175" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="56" t="str" cm="1">
@@ -3949,7 +3949,7 @@
         <v/>
       </c>
       <c r="Q24" s="30" t="str">
-        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(P24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(P24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R24" s="67" t="str">
@@ -3962,7 +3962,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="232"/>
+      <c r="A25" s="176"/>
       <c r="B25" s="67" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4045,7 +4045,7 @@
         <v/>
       </c>
       <c r="Q25" s="30" t="str">
-        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(P25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(P25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R25" s="67" t="str">
@@ -4058,7 +4058,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="232"/>
+      <c r="A26" s="176"/>
       <c r="B26" s="67" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4141,7 +4141,7 @@
         <v/>
       </c>
       <c r="Q26" s="30" t="str">
-        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(P26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(P26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R26" s="67" t="str">
@@ -4154,7 +4154,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="232"/>
+      <c r="A27" s="176"/>
       <c r="B27" s="67" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4237,7 +4237,7 @@
         <v/>
       </c>
       <c r="Q27" s="30" t="str">
-        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(P27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(P27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R27" s="67" t="str">
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="234"/>
+      <c r="A28" s="178"/>
       <c r="B28" s="67" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4333,7 +4333,7 @@
         <v/>
       </c>
       <c r="Q28" s="30" t="str">
-        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(P28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P28,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P28,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
+        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(P28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P28,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P28,Cant!$J$2:$J$99,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P28,Cant!$J$2:$J$99,"43/1.5")+SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P28,Cant!$J$2:$J$99,"24/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R28" s="67" t="str">
@@ -4477,7 +4477,7 @@
       <c r="S31" s="160"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="221" t="s">
+      <c r="A32" s="165" t="s">
         <v>78</v>
       </c>
       <c r="B32" s="56" t="str" cm="1">
@@ -4551,7 +4551,7 @@
         <v/>
       </c>
       <c r="Q32" s="30" t="str">
-        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P32)&gt;0,"",IF(AND(P32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P32,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P32,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
+        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P32)&gt;0,"",IF(AND(P32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P32,Cant!$J$2:$J$100,"43/1.5")+SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P32,Cant!$J$2:$J$100,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P32,Cant!$J$2:$J$100,"43/1.5")+SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P32,Cant!$J$2:$J$100,"24/1.5"),"")),""))</f>
         <v/>
       </c>
       <c r="R32" s="67" t="str">
@@ -4564,7 +4564,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="222"/>
+      <c r="A33" s="166"/>
       <c r="B33" s="67" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),2))),"")</f>
         <v/>
@@ -4636,7 +4636,7 @@
         <v/>
       </c>
       <c r="Q33" s="30" t="str">
-        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P33)&gt;0,"",IF(AND(P33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P33,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P33,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
+        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P33)&gt;0,"",IF(AND(P33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P33,Cant!$J$2:$J$100,"43/1.5")+SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P33,Cant!$J$2:$J$100,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P33,Cant!$J$2:$J$100,"43/1.5")+SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P33,Cant!$J$2:$J$100,"24/1.5"),"")),""))</f>
         <v/>
       </c>
       <c r="R33" s="67" t="str">
@@ -4649,7 +4649,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="223"/>
+      <c r="A34" s="167"/>
       <c r="B34" s="67" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),3))),"")</f>
         <v/>
@@ -4721,7 +4721,7 @@
         <v/>
       </c>
       <c r="Q34" s="30" t="str">
-        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P34)&gt;0,"",IF(AND(P34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P34,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P34,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
+        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P34)&gt;0,"",IF(AND(P34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P34,Cant!$J$2:$J$100,"43/1.5")+SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P34,Cant!$J$2:$J$100,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P34,Cant!$J$2:$J$100,"43/1.5")+SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P34,Cant!$J$2:$J$100,"24/1.5"),"")),""))</f>
         <v/>
       </c>
       <c r="R34" s="67" t="str">
@@ -4773,7 +4773,7 @@
       <c r="S35" s="161"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="221" t="s">
+      <c r="A36" s="165" t="s">
         <v>79</v>
       </c>
       <c r="B36" s="56" t="str" cm="1">
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="Q36" s="30" t="str">
-        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P36)&gt;0,"",IF(AND(P36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P36,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P36,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
+        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P36)&gt;0,"",IF(AND(P36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P36,Cant!$J$2:$J$100,"43/1.5")+SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P36,Cant!$J$2:$J$100,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P36,Cant!$J$2:$J$100,"43/1.5")+SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P36,Cant!$J$2:$J$100,"24/1.5"),"")),""))</f>
         <v/>
       </c>
       <c r="R36" s="67" t="str">
@@ -4860,7 +4860,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="222"/>
+      <c r="A37" s="166"/>
       <c r="B37" s="67" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4932,7 +4932,7 @@
         <v/>
       </c>
       <c r="Q37" s="30" t="str">
-        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P37)&gt;0,"",IF(AND(P37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P37,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P37,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
+        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P37)&gt;0,"",IF(AND(P37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P37,Cant!$J$2:$J$100,"43/1.5")+SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P37,Cant!$J$2:$J$100,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P37,Cant!$J$2:$J$100,"43/1.5")+SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P37,Cant!$J$2:$J$100,"24/1.5"),"")),""))</f>
         <v/>
       </c>
       <c r="R37" s="67" t="str">
@@ -4945,7 +4945,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="223"/>
+      <c r="A38" s="167"/>
       <c r="B38" s="68" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5017,7 +5017,7 @@
         <v/>
       </c>
       <c r="Q38" s="31" t="str">
-        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P38)&gt;0,"",IF(AND(P38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P38,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P38,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
+        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P38)&gt;0,"",IF(AND(P38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P38,Cant!$J$2:$J$100,"43/1.5")+SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P38,Cant!$J$2:$J$100,"24/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P38,Cant!$J$2:$J$100,"43/1.5")+SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P38,Cant!$J$2:$J$100,"24/1.5"),"")),""))</f>
         <v/>
       </c>
       <c r="R38" s="68" t="str">
@@ -5044,7 +5044,7 @@
       <c r="Q39" s="61"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="231" t="s">
+      <c r="A40" s="175" t="s">
         <v>50</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5056,25 +5056,25 @@
       <c r="D40" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="228" t="s">
+      <c r="F40" s="172" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="229"/>
-      <c r="H40" s="229"/>
-      <c r="I40" s="229"/>
-      <c r="J40" s="229"/>
-      <c r="K40" s="229"/>
-      <c r="L40" s="229"/>
-      <c r="M40" s="229"/>
-      <c r="N40" s="229"/>
-      <c r="O40" s="229"/>
-      <c r="P40" s="229"/>
-      <c r="Q40" s="229"/>
-      <c r="R40" s="229"/>
-      <c r="S40" s="230"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="173"/>
+      <c r="I40" s="173"/>
+      <c r="J40" s="173"/>
+      <c r="K40" s="173"/>
+      <c r="L40" s="173"/>
+      <c r="M40" s="173"/>
+      <c r="N40" s="173"/>
+      <c r="O40" s="173"/>
+      <c r="P40" s="173"/>
+      <c r="Q40" s="173"/>
+      <c r="R40" s="173"/>
+      <c r="S40" s="174"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="232"/>
+      <c r="A41" s="176"/>
       <c r="B41" s="35" t="s">
         <v>81</v>
       </c>
@@ -5137,7 +5137,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="232"/>
+      <c r="A42" s="176"/>
       <c r="B42" s="49" t="s">
         <v>88</v>
       </c>
@@ -5162,13 +5162,13 @@
       <c r="P42" s="66"/>
       <c r="Q42" s="78"/>
       <c r="R42" s="79"/>
-      <c r="S42" s="162">
+      <c r="S42" s="179">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="232"/>
+      <c r="A43" s="176"/>
       <c r="B43" s="49" t="s">
         <v>82</v>
       </c>
@@ -5180,26 +5180,26 @@
         <v>54</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="180" t="str">
+      <c r="F43" s="233" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="181"/>
-      <c r="H43" s="181"/>
-      <c r="I43" s="181"/>
-      <c r="J43" s="181"/>
-      <c r="K43" s="181"/>
-      <c r="L43" s="181"/>
-      <c r="M43" s="181"/>
-      <c r="N43" s="181"/>
-      <c r="O43" s="181"/>
-      <c r="P43" s="181"/>
-      <c r="Q43" s="181"/>
-      <c r="R43" s="181"/>
-      <c r="S43" s="235"/>
+      <c r="G43" s="234"/>
+      <c r="H43" s="234"/>
+      <c r="I43" s="234"/>
+      <c r="J43" s="234"/>
+      <c r="K43" s="234"/>
+      <c r="L43" s="234"/>
+      <c r="M43" s="234"/>
+      <c r="N43" s="234"/>
+      <c r="O43" s="234"/>
+      <c r="P43" s="234"/>
+      <c r="Q43" s="234"/>
+      <c r="R43" s="234"/>
+      <c r="S43" s="180"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="232"/>
+      <c r="A44" s="176"/>
       <c r="B44" s="49" t="s">
         <v>87</v>
       </c>
@@ -5255,7 +5255,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="232"/>
+      <c r="A45" s="176"/>
       <c r="B45" s="33" t="s">
         <v>89</v>
       </c>
@@ -5389,7 +5389,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="232"/>
+      <c r="A46" s="176"/>
       <c r="B46" s="33" t="s">
         <v>83</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="232"/>
+      <c r="A47" s="176"/>
       <c r="B47" s="33" t="s">
         <v>84</v>
       </c>
@@ -5414,31 +5414,31 @@
       <c r="D47" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="162" t="s">
+      <c r="F47" s="179" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="166" t="str">
+      <c r="G47" s="221" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="162" t="s">
+      <c r="J47" s="179" t="s">
         <v>86</v>
       </c>
-      <c r="K47" s="164">
+      <c r="K47" s="219">
         <v>1</v>
       </c>
-      <c r="N47" s="162" t="s">
+      <c r="N47" s="179" t="s">
         <v>108</v>
       </c>
-      <c r="O47" s="236"/>
-      <c r="P47" s="237"/>
-      <c r="R47" s="162" t="s">
+      <c r="O47" s="182"/>
+      <c r="P47" s="183"/>
+      <c r="R47" s="179" t="s">
         <v>114</v>
       </c>
-      <c r="S47" s="162"/>
+      <c r="S47" s="179"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="234"/>
+      <c r="A48" s="178"/>
       <c r="B48" s="36" t="s">
         <v>85</v>
       </c>
@@ -5449,15 +5449,15 @@
       <c r="D48" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="F48" s="163"/>
-      <c r="G48" s="167"/>
-      <c r="J48" s="163"/>
-      <c r="K48" s="165"/>
-      <c r="N48" s="235"/>
-      <c r="O48" s="238"/>
-      <c r="P48" s="239"/>
-      <c r="R48" s="235"/>
-      <c r="S48" s="163"/>
+      <c r="F48" s="181"/>
+      <c r="G48" s="222"/>
+      <c r="J48" s="181"/>
+      <c r="K48" s="220"/>
+      <c r="N48" s="180"/>
+      <c r="O48" s="184"/>
+      <c r="P48" s="185"/>
+      <c r="R48" s="180"/>
+      <c r="S48" s="181"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5466,7 +5466,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="218" t="s">
+      <c r="A50" s="162" t="s">
         <v>65</v>
       </c>
       <c r="B50" s="134"/>
@@ -5489,7 +5489,7 @@
       <c r="S50" s="136"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="219"/>
+      <c r="A51" s="163"/>
       <c r="B51" s="137"/>
       <c r="C51" s="139"/>
       <c r="D51" s="139"/>
@@ -5510,7 +5510,7 @@
       <c r="S51" s="138"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="219"/>
+      <c r="A52" s="163"/>
       <c r="B52" s="137"/>
       <c r="C52" s="139"/>
       <c r="D52" s="139"/>
@@ -5531,7 +5531,7 @@
       <c r="S52" s="138"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="219"/>
+      <c r="A53" s="163"/>
       <c r="B53" s="137"/>
       <c r="C53" s="139"/>
       <c r="D53" s="139"/>
@@ -5552,7 +5552,7 @@
       <c r="S53" s="138"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="219"/>
+      <c r="A54" s="163"/>
       <c r="B54" s="137"/>
       <c r="C54" s="139"/>
       <c r="D54" s="139"/>
@@ -5573,7 +5573,7 @@
       <c r="S54" s="138"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="219"/>
+      <c r="A55" s="163"/>
       <c r="B55" s="137"/>
       <c r="C55" s="139"/>
       <c r="D55" s="139"/>
@@ -5594,7 +5594,7 @@
       <c r="S55" s="138"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="219"/>
+      <c r="A56" s="163"/>
       <c r="B56" s="137"/>
       <c r="C56" s="139"/>
       <c r="D56" s="139"/>
@@ -5615,7 +5615,7 @@
       <c r="S56" s="138"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="219"/>
+      <c r="A57" s="163"/>
       <c r="B57" s="137"/>
       <c r="C57" s="139"/>
       <c r="D57" s="139"/>
@@ -5636,57 +5636,57 @@
       <c r="S57" s="138"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="219"/>
+      <c r="A58" s="163"/>
       <c r="B58" s="140"/>
       <c r="S58" s="141"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="219"/>
+      <c r="A59" s="163"/>
       <c r="B59" s="140"/>
       <c r="S59" s="141"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="219"/>
+      <c r="A60" s="163"/>
       <c r="B60" s="140"/>
       <c r="S60" s="141"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="219"/>
+      <c r="A61" s="163"/>
       <c r="B61" s="140"/>
       <c r="S61" s="141"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="219"/>
+      <c r="A62" s="163"/>
       <c r="B62" s="140"/>
       <c r="S62" s="141"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="219"/>
+      <c r="A63" s="163"/>
       <c r="B63" s="140"/>
       <c r="S63" s="141"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="219"/>
+      <c r="A64" s="163"/>
       <c r="B64" s="140"/>
       <c r="S64" s="141"/>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="219"/>
+      <c r="A65" s="163"/>
       <c r="B65" s="140"/>
       <c r="S65" s="141"/>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="219"/>
+      <c r="A66" s="163"/>
       <c r="B66" s="140"/>
       <c r="S66" s="141"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="219"/>
+      <c r="A67" s="163"/>
       <c r="B67" s="140"/>
       <c r="S67" s="141"/>
     </row>
     <row r="68" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A68" s="220"/>
+      <c r="A68" s="164"/>
       <c r="B68" s="142"/>
       <c r="C68" s="77"/>
       <c r="D68" s="77"/>
@@ -5708,6 +5708,31 @@
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A68"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A36:A38"/>
@@ -5724,31 +5749,6 @@
     <mergeCell ref="O47:P48"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="F47:F48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="F43:R43"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L9:M9"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11031,7 +11031,7 @@
             AND(D2=2800,E2=1220,B2=18),
             AND(D2=3050,E2=1300,B2=19),
             AND(D2=3050,E2=1310,B2=19),
-            AND(D2=2800,E2=1300,OR(B2=17.5,B2=19)),
+            AND(D2=2800,E2=1300,OR(B2=17.5,B2=18.5,B2=19)),
             AND(RIGHT(A2,6)="MDF 3D",B2&lt;&gt;36)
         ),
         NOT(OR(
@@ -11120,15 +11120,28 @@
         <v>N/A</v>
       </c>
       <c r="X2" t="str">
-        <f>IFERROR(
+        <f t="shared" ref="X2:X34" si="0">IFERROR(
+IF(
+ISNUMBER(SEARCH("2461LT",A2)),
+"Rehau 2461LT",
+IF(
+ISNUMBER(SEARCH("3146L",A2)),
+"Rehau 3146L",
+IF(
+ISNUMBER(SEARCH("1918L",A2)),
+"Rehau 1918L",
 IF(
 ISNUMBER(--LEFT(SUBSTITUTE(TRIM(MID(A2,FIND("-",A2)+1,50)),"LR ","LR"),1)),
 "AGT "&amp;SUBSTITUTE(TRIM(MID(A2,FIND("-",A2)+1,50)),"LR ","LR"),
 SUBSTITUTE(TRIM(MID(A2,FIND("-",A2)+1,50)),"LR ","LR")
 )
-&amp;IF(OR(E2=600,E2=650,E2=920),"/"&amp;E2,"")
-&amp;IF(E2=640," PS",""),"")
-&amp;IF(AND(OR(B2=8,B2=10,B2=16),D2=2800,E2=2070)," "&amp;B2&amp;"mm","")</f>
+)
+)
+)
+&amp;IF(OR(E2=600,E2=650,E2=920)," /"&amp;E2,"")
+&amp;IF(E2=640," PS","")
+&amp;IF(AND(OR(B2=8,B2=10,B2=16),D2=2800,E2=2070)," "&amp;B2&amp;"mm",""),
+"")</f>
         <v/>
       </c>
       <c r="Y2" t="str">
@@ -11185,18 +11198,18 @@
       <c r="T3" s="106"/>
       <c r="U3" s="115"/>
       <c r="V3" s="133" t="str">
-        <f t="shared" ref="V3:V34" si="0">IFERROR(IF(OR(W3="DB PAL",W3="DB MDF"),ROUND(Q3/13.5,0), ROUND(Q3/P3,2)),"")</f>
+        <f t="shared" ref="V3:V34" si="1">IFERROR(IF(OR(W3="DB PAL",W3="DB MDF"),ROUND(Q3/13.5,0), ROUND(Q3/P3,2)),"")</f>
         <v/>
       </c>
       <c r="W3" t="str">
-        <f t="shared" ref="W3:W34" si="1">IF(
+        <f t="shared" ref="W3:W34" si="2">IF(
     AND(
         OR(
             AND(D3=2800,E3=2070,OR(B3=19,B3=19.3)),
             AND(D3=2800,E3=1220,B3=18),
             AND(D3=3050,E3=1300,B3=19),
             AND(D3=3050,E3=1310,B3=19),
-            AND(D3=2800,E3=1300,OR(B3=17.5,B3=19)),
+            AND(D3=2800,E3=1300,OR(B3=17.5,B3=18.5,B3=19)),
             AND(RIGHT(A3,6)="MDF 3D",B3&lt;&gt;36)
         ),
         NOT(OR(
@@ -11285,15 +11298,7 @@
         <v>N/A</v>
       </c>
       <c r="X3" t="str">
-        <f t="shared" ref="X3:X34" si="2">IFERROR(
-IF(
-ISNUMBER(--LEFT(SUBSTITUTE(TRIM(MID(A3,FIND("-",A3)+1,50)),"LR ","LR"),1)),
-"AGT "&amp;SUBSTITUTE(TRIM(MID(A3,FIND("-",A3)+1,50)),"LR ","LR"),
-SUBSTITUTE(TRIM(MID(A3,FIND("-",A3)+1,50)),"LR ","LR")
-)
-&amp;IF(OR(E3=600,E3=650,E3=920)," /"&amp;E3,"")
-&amp;IF(E3=640," PS",""),"")
-&amp;IF(AND(OR(B3=8,B3=10,B3=16),D3=2800,E3=2070)," "&amp;B3&amp;"mm","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Y3" t="str">
@@ -11350,15 +11355,15 @@
       <c r="T4" s="115"/>
       <c r="U4" s="106"/>
       <c r="V4" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X4" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W4" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X4" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y4" t="str">
@@ -11380,15 +11385,36 @@
       <c r="T5" s="115"/>
       <c r="U5" s="106"/>
       <c r="V5" s="133" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="W5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X5" t="str">
-        <f t="shared" si="2"/>
+        <f>IFERROR(
+IF(
+ISNUMBER(SEARCH("2461LT",A5)),
+"Rehau 2461LT",
+IF(
+ISNUMBER(SEARCH("3146L",A5)),
+"Rehau 3146L",
+IF(
+ISNUMBER(SEARCH("1918L",A5)),
+"Rehau 1918L",
+IF(
+ISNUMBER(--LEFT(SUBSTITUTE(TRIM(MID(A5,FIND("-",A5)+1,50)),"LR ","LR"),1)),
+"AGT "&amp;SUBSTITUTE(TRIM(MID(A5,FIND("-",A5)+1,50)),"LR ","LR"),
+SUBSTITUTE(TRIM(MID(A5,FIND("-",A5)+1,50)),"LR ","LR")
+)
+)
+)
+)
+&amp;IF(OR(E5=600,E5=650,E5=920)," /"&amp;E5,"")
+&amp;IF(E5=640," PS","")
+&amp;IF(AND(OR(B5=8,B5=10,B5=16),D5=2800,E5=2070)," "&amp;B5&amp;"mm",""),
+"")</f>
         <v/>
       </c>
       <c r="Y5" t="str">
@@ -11410,15 +11436,15 @@
       <c r="T6" s="115"/>
       <c r="U6" s="106"/>
       <c r="V6" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X6" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W6" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X6" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y6" t="str">
@@ -11440,15 +11466,15 @@
       <c r="T7" s="106"/>
       <c r="U7" s="106"/>
       <c r="V7" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X7" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W7" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X7" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y7" t="str">
@@ -11470,15 +11496,15 @@
       <c r="T8" s="115"/>
       <c r="U8" s="106"/>
       <c r="V8" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X8" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W8" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X8" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y8" t="str">
@@ -11500,15 +11526,15 @@
       <c r="T9" s="115"/>
       <c r="U9" s="104"/>
       <c r="V9" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X9" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W9" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X9" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y9" t="str">
@@ -11530,15 +11556,15 @@
       <c r="T10" s="115"/>
       <c r="U10" s="115"/>
       <c r="V10" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W10" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X10" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W10" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X10" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y10" t="str">
@@ -11560,15 +11586,15 @@
       <c r="T11" s="115"/>
       <c r="U11" s="115"/>
       <c r="V11" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X11" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W11" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X11" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y11" t="str">
@@ -11590,15 +11616,15 @@
       <c r="T12" s="107"/>
       <c r="U12" s="107"/>
       <c r="V12" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X12" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W12" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X12" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y12" t="str">
@@ -11620,15 +11646,15 @@
       <c r="T13" s="123"/>
       <c r="U13" s="129"/>
       <c r="V13" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X13" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W13" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X13" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y13" t="str">
@@ -11650,15 +11676,15 @@
       <c r="T14" s="124"/>
       <c r="U14" s="129"/>
       <c r="V14" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X14" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W14" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X14" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y14" t="str">
@@ -11680,15 +11706,15 @@
       <c r="T15" s="124"/>
       <c r="U15" s="107"/>
       <c r="V15" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W15" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W15" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X15" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y15" t="str">
@@ -11710,15 +11736,15 @@
       <c r="T16" s="124"/>
       <c r="U16" s="106"/>
       <c r="V16" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W16" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X16" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W16" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X16" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y16" t="str">
@@ -11740,15 +11766,15 @@
       <c r="T17" s="124"/>
       <c r="U17" s="106"/>
       <c r="V17" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W17" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X17" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W17" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X17" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y17" t="str">
@@ -11787,15 +11813,15 @@
       <c r="T18" s="124"/>
       <c r="U18" s="106"/>
       <c r="V18" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W18" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X18" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W18" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X18" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y18" t="str">
@@ -11833,15 +11859,15 @@
       <c r="S19" s="124"/>
       <c r="T19" s="124"/>
       <c r="V19" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W19" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X19" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W19" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X19" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y19" t="str">
@@ -11879,15 +11905,15 @@
       <c r="S20" s="123"/>
       <c r="T20" s="119"/>
       <c r="V20" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W20" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X20" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W20" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X20" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y20" t="str">
@@ -11925,15 +11951,15 @@
       <c r="S21" s="124"/>
       <c r="T21" s="123"/>
       <c r="V21" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W21" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X21" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W21" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X21" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y21" t="str">
@@ -11951,15 +11977,15 @@
     </row>
     <row r="22" spans="1:27">
       <c r="V22" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W22" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X22" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W22" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X22" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y22" t="str">
@@ -11977,15 +12003,15 @@
     </row>
     <row r="23" spans="1:27">
       <c r="V23" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W23" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X23" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W23" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X23" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y23" t="str">
@@ -12003,15 +12029,15 @@
     </row>
     <row r="24" spans="1:27">
       <c r="V24" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X24" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W24" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X24" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y24" t="str">
@@ -12029,15 +12055,15 @@
     </row>
     <row r="25" spans="1:27">
       <c r="V25" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W25" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X25" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W25" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X25" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y25" t="str">
@@ -12055,15 +12081,15 @@
     </row>
     <row r="26" spans="1:27">
       <c r="V26" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W26" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X26" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W26" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X26" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y26" t="str">
@@ -12081,15 +12107,15 @@
     </row>
     <row r="27" spans="1:27">
       <c r="V27" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W27" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X27" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W27" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X27" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y27" t="str">
@@ -12107,15 +12133,15 @@
     </row>
     <row r="28" spans="1:27">
       <c r="V28" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W28" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X28" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W28" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X28" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y28" t="str">
@@ -12133,15 +12159,15 @@
     </row>
     <row r="29" spans="1:27">
       <c r="V29" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W29" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X29" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W29" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X29" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y29" t="str">
@@ -12159,15 +12185,15 @@
     </row>
     <row r="30" spans="1:27">
       <c r="V30" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W30" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X30" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W30" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X30" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y30" t="str">
@@ -12185,15 +12211,15 @@
     </row>
     <row r="31" spans="1:27">
       <c r="V31" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W31" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X31" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W31" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X31" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y31" t="str">
@@ -12211,15 +12237,15 @@
     </row>
     <row r="32" spans="1:27">
       <c r="V32" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W32" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X32" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W32" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X32" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y32" t="str">
@@ -12237,15 +12263,15 @@
     </row>
     <row r="33" spans="22:27">
       <c r="V33" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W33" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W33" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X33" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y33" t="str">
@@ -12263,15 +12289,15 @@
     </row>
     <row r="34" spans="22:27">
       <c r="V34" s="133" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W34" t="str">
+        <f t="shared" si="2"/>
+        <v>N/A</v>
+      </c>
+      <c r="X34" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="W34" t="str">
-        <f t="shared" si="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="X34" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y34" t="str">
@@ -12300,7 +12326,7 @@
   <cols>
     <col min="1" max="1" width="85.5703125" customWidth="1"/>
     <col min="12" max="12" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -12346,9 +12372,25 @@
         <v>/</v>
       </c>
       <c r="L2" t="str">
-        <f>IFERROR(IF(ISNUMBER(VALUE(MID(A2,FIND("-",A2)+1,1))),
+        <f t="shared" ref="L2:L23" si="1">IFERROR(
+IF(
+ISNUMBER(SEARCH("2461LT",A2)),
+"Rehau 2461LT",
+IF(
+ISNUMBER(SEARCH("3146L",A2)),
+"Rehau 3146L",
+IF(
+ISNUMBER(SEARCH("1918L",A2)),
+"Rehau 1918L",
+IF(
+ISNUMBER(VALUE(MID(A2,FIND("-",A2)+1,1))),
 "AGT "&amp;TRIM(MID(A2,FIND("-",A2)+1,FIND("@",SUBSTITUTE(A2,"-","@",LEN(A2)-LEN(SUBSTITUTE(A2,"-",""))))-FIND("-",A2)-1)),
-TRIM(MID(A2,FIND("-",A2)+1,FIND("@",SUBSTITUTE(A2,"-","@",LEN(A2)-LEN(SUBSTITUTE(A2,"-",""))))-FIND("-",A2)-1))),"")</f>
+TRIM(MID(A2,FIND("-",A2)+1,FIND("@",SUBSTITUTE(A2,"-","@",LEN(A2)-LEN(SUBSTITUTE(A2,"-",""))))-FIND("-",A2)-1))
+)
+)
+)
+),
+"")</f>
         <v/>
       </c>
       <c r="M2" t="str">
@@ -12358,11 +12400,11 @@
     </row>
     <row r="3" spans="1:13">
       <c r="H3" t="str">
-        <f t="shared" ref="H3:H23" si="1">RIGHT(A3,3)</f>
+        <f t="shared" ref="H3:H23" si="2">RIGHT(A3,3)</f>
         <v/>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I23" si="2">ROUNDUP(E3*1.03,0)</f>
+        <f t="shared" ref="I3:I23" si="3">ROUNDUP(E3*1.03,0)</f>
         <v>0</v>
       </c>
       <c r="J3" t="str">
@@ -12370,9 +12412,7 @@
         <v>/</v>
       </c>
       <c r="L3" t="str">
-        <f t="shared" ref="L3:L23" si="3">IFERROR(IF(ISNUMBER(VALUE(MID(A3,FIND("-",A3)+1,1))),
-"AGT "&amp;TRIM(MID(A3,FIND("-",A3)+1,FIND("@",SUBSTITUTE(A3,"-","@",LEN(A3)-LEN(SUBSTITUTE(A3,"-",""))))-FIND("-",A3)-1)),
-TRIM(MID(A3,FIND("-",A3)+1,FIND("@",SUBSTITUTE(A3,"-","@",LEN(A3)-LEN(SUBSTITUTE(A3,"-",""))))-FIND("-",A3)-1))),"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M3" t="str">
@@ -12382,11 +12422,11 @@
     </row>
     <row r="4" spans="1:13">
       <c r="H4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J4" t="str">
@@ -12394,7 +12434,7 @@
         <v>/</v>
       </c>
       <c r="L4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M4" t="str">
@@ -12404,11 +12444,11 @@
     </row>
     <row r="5" spans="1:13">
       <c r="H5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J5" t="str">
@@ -12416,7 +12456,25 @@
         <v>/</v>
       </c>
       <c r="L5" t="str">
-        <f t="shared" si="3"/>
+        <f>IFERROR(
+IF(
+ISNUMBER(SEARCH("2461LT",A5)),
+"Rehau 2461LT",
+IF(
+ISNUMBER(SEARCH("3146L",A5)),
+"Rehau 3146L",
+IF(
+ISNUMBER(SEARCH("1918L",A5)),
+"Rehau 1918L",
+IF(
+ISNUMBER(VALUE(MID(A5,FIND("-",A5)+1,1))),
+"AGT "&amp;TRIM(MID(A5,FIND("-",A5)+1,FIND("@",SUBSTITUTE(A5,"-","@",LEN(A5)-LEN(SUBSTITUTE(A5,"-",""))))-FIND("-",A5)-1)),
+TRIM(MID(A5,FIND("-",A5)+1,FIND("@",SUBSTITUTE(A5,"-","@",LEN(A5)-LEN(SUBSTITUTE(A5,"-",""))))-FIND("-",A5)-1))
+)
+)
+)
+),
+"")</f>
         <v/>
       </c>
       <c r="M5" t="str">
@@ -12426,11 +12484,11 @@
     </row>
     <row r="6" spans="1:13">
       <c r="H6" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J6" t="str">
@@ -12438,7 +12496,7 @@
         <v>/</v>
       </c>
       <c r="L6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M6" t="str">
@@ -12448,11 +12506,11 @@
     </row>
     <row r="7" spans="1:13">
       <c r="H7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J7" t="str">
@@ -12460,7 +12518,7 @@
         <v>/</v>
       </c>
       <c r="L7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M7" t="str">
@@ -12470,11 +12528,11 @@
     </row>
     <row r="8" spans="1:13">
       <c r="H8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J8" t="str">
@@ -12482,7 +12540,7 @@
         <v>/</v>
       </c>
       <c r="L8" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M8" t="str">
@@ -12492,11 +12550,11 @@
     </row>
     <row r="9" spans="1:13">
       <c r="H9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J9" t="str">
@@ -12504,7 +12562,7 @@
         <v>/</v>
       </c>
       <c r="L9" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M9" t="str">
@@ -12514,11 +12572,11 @@
     </row>
     <row r="10" spans="1:13">
       <c r="H10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J10" t="str">
@@ -12526,7 +12584,7 @@
         <v>/</v>
       </c>
       <c r="L10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M10" t="str">
@@ -12536,11 +12594,11 @@
     </row>
     <row r="11" spans="1:13">
       <c r="H11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J11" t="str">
@@ -12548,7 +12606,7 @@
         <v>/</v>
       </c>
       <c r="L11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M11" t="str">
@@ -12563,11 +12621,11 @@
       <c r="D12" s="105"/>
       <c r="E12" s="106"/>
       <c r="H12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J12" t="str">
@@ -12575,7 +12633,7 @@
         <v>/</v>
       </c>
       <c r="L12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M12" t="str">
@@ -12590,11 +12648,11 @@
       <c r="D13" s="105"/>
       <c r="E13" s="106"/>
       <c r="H13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J13" t="str">
@@ -12602,7 +12660,7 @@
         <v>/</v>
       </c>
       <c r="L13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M13" t="str">
@@ -12617,11 +12675,11 @@
       <c r="D14" s="105"/>
       <c r="E14" s="106"/>
       <c r="H14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J14" t="str">
@@ -12629,7 +12687,7 @@
         <v>/</v>
       </c>
       <c r="L14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M14" t="str">
@@ -12644,11 +12702,11 @@
       <c r="D15" s="116"/>
       <c r="E15" s="116"/>
       <c r="H15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J15" t="str">
@@ -12656,7 +12714,7 @@
         <v>/</v>
       </c>
       <c r="L15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M15" t="str">
@@ -12670,7 +12728,7 @@
         <v/>
       </c>
       <c r="I16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J16" t="str">
@@ -12678,7 +12736,7 @@
         <v>/</v>
       </c>
       <c r="L16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M16" t="str">
@@ -12688,11 +12746,11 @@
     </row>
     <row r="17" spans="8:13">
       <c r="H17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J17" t="str">
@@ -12700,7 +12758,7 @@
         <v>/</v>
       </c>
       <c r="L17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M17" t="str">
@@ -12710,11 +12768,11 @@
     </row>
     <row r="18" spans="8:13">
       <c r="H18" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J18" t="str">
@@ -12722,7 +12780,7 @@
         <v>/</v>
       </c>
       <c r="L18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M18" t="str">
@@ -12732,11 +12790,11 @@
     </row>
     <row r="19" spans="8:13">
       <c r="H19" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J19" t="str">
@@ -12744,7 +12802,7 @@
         <v>/</v>
       </c>
       <c r="L19" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M19" t="str">
@@ -12754,11 +12812,11 @@
     </row>
     <row r="20" spans="8:13">
       <c r="H20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J20" t="str">
@@ -12766,7 +12824,7 @@
         <v>/</v>
       </c>
       <c r="L20" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M20" t="str">
@@ -12776,11 +12834,11 @@
     </row>
     <row r="21" spans="8:13">
       <c r="H21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J21" t="str">
@@ -12788,7 +12846,7 @@
         <v>/</v>
       </c>
       <c r="L21" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M21" t="str">
@@ -12798,11 +12856,11 @@
     </row>
     <row r="22" spans="8:13">
       <c r="H22" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J22" t="str">
@@ -12810,7 +12868,7 @@
         <v>/</v>
       </c>
       <c r="L22" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M22" t="str">
@@ -12820,11 +12878,11 @@
     </row>
     <row r="23" spans="8:13">
       <c r="H23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J23" t="str">
@@ -12832,7 +12890,7 @@
         <v>/</v>
       </c>
       <c r="L23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M23" t="str">

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C57C1681-D468-4C63-B478-ACD1F6421CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAF2C3E-5C05-476E-B777-738C2F988295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Proforma!$A$1:$B$201</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -540,7 +540,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="204"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1671,82 +1671,90 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1794,12 +1802,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1857,78 +1859,76 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2416,33 +2416,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="202" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="205"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="203"/>
+      <c r="L1" s="204"/>
       <c r="M1" s="38" t="s">
         <v>70</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="194" t="s">
+      <c r="O1" s="195" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="196"/>
+      <c r="P1" s="196"/>
+      <c r="Q1" s="196"/>
+      <c r="R1" s="196"/>
+      <c r="S1" s="197"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2461,165 +2461,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="80"/>
-      <c r="O2" s="197"/>
-      <c r="P2" s="198"/>
-      <c r="Q2" s="198"/>
-      <c r="R2" s="198"/>
-      <c r="S2" s="199"/>
+      <c r="O2" s="198"/>
+      <c r="P2" s="199"/>
+      <c r="Q2" s="199"/>
+      <c r="R2" s="199"/>
+      <c r="S2" s="200"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="209"/>
-      <c r="C3" s="210"/>
-      <c r="D3" s="211"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
       <c r="H3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="216"/>
-      <c r="J3" s="217"/>
-      <c r="K3" s="218"/>
+      <c r="I3" s="215"/>
+      <c r="J3" s="216"/>
+      <c r="K3" s="217"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="73"/>
-      <c r="O3" s="206"/>
-      <c r="P3" s="207"/>
-      <c r="Q3" s="207"/>
-      <c r="R3" s="207"/>
-      <c r="S3" s="208"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="206"/>
+      <c r="Q3" s="206"/>
+      <c r="R3" s="206"/>
+      <c r="S3" s="207"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="188"/>
-      <c r="C4" s="189"/>
-      <c r="D4" s="190"/>
+      <c r="B4" s="189"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="191"/>
       <c r="H4" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="191"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="73"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="207"/>
-      <c r="Q4" s="207"/>
-      <c r="R4" s="207"/>
-      <c r="S4" s="208"/>
+      <c r="O4" s="205"/>
+      <c r="P4" s="206"/>
+      <c r="Q4" s="206"/>
+      <c r="R4" s="206"/>
+      <c r="S4" s="207"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="212"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="214"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="H5" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="215"/>
-      <c r="J5" s="207"/>
-      <c r="K5" s="208"/>
+      <c r="I5" s="214"/>
+      <c r="J5" s="206"/>
+      <c r="K5" s="207"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="73"/>
-      <c r="O5" s="206"/>
-      <c r="P5" s="207"/>
-      <c r="Q5" s="207"/>
-      <c r="R5" s="207"/>
-      <c r="S5" s="208"/>
+      <c r="O5" s="205"/>
+      <c r="P5" s="206"/>
+      <c r="Q5" s="206"/>
+      <c r="R5" s="206"/>
+      <c r="S5" s="207"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="223"/>
-      <c r="C6" s="224"/>
-      <c r="D6" s="225"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="170"/>
       <c r="H6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="226"/>
-      <c r="J6" s="201"/>
-      <c r="K6" s="202"/>
+      <c r="I6" s="171"/>
+      <c r="J6" s="172"/>
+      <c r="K6" s="173"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="74"/>
-      <c r="O6" s="200"/>
-      <c r="P6" s="201"/>
-      <c r="Q6" s="201"/>
-      <c r="R6" s="201"/>
-      <c r="S6" s="202"/>
+      <c r="O6" s="201"/>
+      <c r="P6" s="172"/>
+      <c r="Q6" s="172"/>
+      <c r="R6" s="172"/>
+      <c r="S6" s="173"/>
     </row>
     <row r="7" spans="1:19" s="50" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="227" t="s">
+      <c r="A8" s="174" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="228"/>
-      <c r="C8" s="228"/>
-      <c r="D8" s="229"/>
-      <c r="F8" s="233" t="s">
+      <c r="B8" s="175"/>
+      <c r="C8" s="175"/>
+      <c r="D8" s="176"/>
+      <c r="F8" s="180" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="234"/>
-      <c r="H8" s="234"/>
-      <c r="I8" s="234"/>
-      <c r="J8" s="234"/>
-      <c r="K8" s="234"/>
-      <c r="L8" s="234"/>
-      <c r="M8" s="234"/>
-      <c r="N8" s="234"/>
-      <c r="O8" s="234"/>
-      <c r="P8" s="234"/>
-      <c r="Q8" s="234"/>
-      <c r="R8" s="234"/>
-      <c r="S8" s="239"/>
+      <c r="G8" s="181"/>
+      <c r="H8" s="181"/>
+      <c r="I8" s="181"/>
+      <c r="J8" s="181"/>
+      <c r="K8" s="181"/>
+      <c r="L8" s="181"/>
+      <c r="M8" s="181"/>
+      <c r="N8" s="181"/>
+      <c r="O8" s="181"/>
+      <c r="P8" s="181"/>
+      <c r="Q8" s="181"/>
+      <c r="R8" s="181"/>
+      <c r="S8" s="186"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="230"/>
-      <c r="B9" s="231"/>
-      <c r="C9" s="231"/>
-      <c r="D9" s="232"/>
-      <c r="F9" s="170" t="s">
+      <c r="A9" s="177"/>
+      <c r="B9" s="178"/>
+      <c r="C9" s="178"/>
+      <c r="D9" s="179"/>
+      <c r="F9" s="226" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="171"/>
-      <c r="H9" s="186" t="s">
+      <c r="G9" s="227"/>
+      <c r="H9" s="240" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="187"/>
-      <c r="J9" s="168" t="s">
+      <c r="I9" s="241"/>
+      <c r="J9" s="224" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="169"/>
-      <c r="L9" s="240" t="s">
+      <c r="K9" s="225"/>
+      <c r="L9" s="187" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="241"/>
-      <c r="N9" s="237" t="s">
+      <c r="M9" s="188"/>
+      <c r="N9" s="184" t="s">
         <v>80</v>
       </c>
-      <c r="O9" s="238"/>
-      <c r="P9" s="235" t="s">
+      <c r="O9" s="185"/>
+      <c r="P9" s="182" t="s">
         <v>68</v>
       </c>
-      <c r="Q9" s="236"/>
-      <c r="R9" s="237" t="s">
+      <c r="Q9" s="183"/>
+      <c r="R9" s="184" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="238"/>
+      <c r="S9" s="185"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="175" t="s">
+      <c r="A10" s="231" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2676,7 +2676,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="176"/>
+      <c r="A11" s="232"/>
       <c r="B11" s="56" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2767,7 +2767,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="176"/>
+      <c r="A12" s="232"/>
       <c r="B12" s="108" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -2859,7 +2859,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="176"/>
+      <c r="A13" s="232"/>
       <c r="B13" s="108" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -2955,7 +2955,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="176"/>
+      <c r="A14" s="232"/>
       <c r="B14" s="108" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3051,7 +3051,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="176"/>
+      <c r="A15" s="232"/>
       <c r="B15" s="108" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3147,7 +3147,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="176"/>
+      <c r="A16" s="232"/>
       <c r="B16" s="108" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3243,7 +3243,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="176"/>
+      <c r="A17" s="232"/>
       <c r="B17" s="108" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3339,7 +3339,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="176"/>
+      <c r="A18" s="232"/>
       <c r="B18" s="108" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3435,7 +3435,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="176"/>
+      <c r="A19" s="232"/>
       <c r="B19" s="108" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3531,7 +3531,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="176"/>
+      <c r="A20" s="232"/>
       <c r="B20" s="108" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3627,7 +3627,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="176"/>
+      <c r="A21" s="232"/>
       <c r="B21" s="108" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3723,7 +3723,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="177"/>
+      <c r="A22" s="233"/>
       <c r="B22" s="108" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3864,7 +3864,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="175" t="s">
+      <c r="A24" s="231" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="56" t="str" cm="1">
@@ -3962,7 +3962,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="176"/>
+      <c r="A25" s="232"/>
       <c r="B25" s="67" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4058,7 +4058,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="176"/>
+      <c r="A26" s="232"/>
       <c r="B26" s="67" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4154,7 +4154,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="176"/>
+      <c r="A27" s="232"/>
       <c r="B27" s="67" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="178"/>
+      <c r="A28" s="234"/>
       <c r="B28" s="67" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4477,7 +4477,7 @@
       <c r="S31" s="160"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="165" t="s">
+      <c r="A32" s="221" t="s">
         <v>78</v>
       </c>
       <c r="B32" s="56" t="str" cm="1">
@@ -4564,7 +4564,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="166"/>
+      <c r="A33" s="222"/>
       <c r="B33" s="67" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),2))),"")</f>
         <v/>
@@ -4649,7 +4649,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="167"/>
+      <c r="A34" s="223"/>
       <c r="B34" s="67" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),3))),"")</f>
         <v/>
@@ -4773,7 +4773,7 @@
       <c r="S35" s="161"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="165" t="s">
+      <c r="A36" s="221" t="s">
         <v>79</v>
       </c>
       <c r="B36" s="56" t="str" cm="1">
@@ -4860,7 +4860,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="166"/>
+      <c r="A37" s="222"/>
       <c r="B37" s="67" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4945,7 +4945,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="167"/>
+      <c r="A38" s="223"/>
       <c r="B38" s="68" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5044,7 +5044,7 @@
       <c r="Q39" s="61"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="175" t="s">
+      <c r="A40" s="231" t="s">
         <v>50</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5056,25 +5056,25 @@
       <c r="D40" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="172" t="s">
+      <c r="F40" s="228" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="173"/>
-      <c r="H40" s="173"/>
-      <c r="I40" s="173"/>
-      <c r="J40" s="173"/>
-      <c r="K40" s="173"/>
-      <c r="L40" s="173"/>
-      <c r="M40" s="173"/>
-      <c r="N40" s="173"/>
-      <c r="O40" s="173"/>
-      <c r="P40" s="173"/>
-      <c r="Q40" s="173"/>
-      <c r="R40" s="173"/>
-      <c r="S40" s="174"/>
+      <c r="G40" s="229"/>
+      <c r="H40" s="229"/>
+      <c r="I40" s="229"/>
+      <c r="J40" s="229"/>
+      <c r="K40" s="229"/>
+      <c r="L40" s="229"/>
+      <c r="M40" s="229"/>
+      <c r="N40" s="229"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="229"/>
+      <c r="Q40" s="229"/>
+      <c r="R40" s="229"/>
+      <c r="S40" s="230"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="176"/>
+      <c r="A41" s="232"/>
       <c r="B41" s="35" t="s">
         <v>81</v>
       </c>
@@ -5137,7 +5137,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="176"/>
+      <c r="A42" s="232"/>
       <c r="B42" s="49" t="s">
         <v>88</v>
       </c>
@@ -5162,13 +5162,13 @@
       <c r="P42" s="66"/>
       <c r="Q42" s="78"/>
       <c r="R42" s="79"/>
-      <c r="S42" s="179">
+      <c r="S42" s="162">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="176"/>
+      <c r="A43" s="232"/>
       <c r="B43" s="49" t="s">
         <v>82</v>
       </c>
@@ -5180,26 +5180,26 @@
         <v>54</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="233" t="str">
+      <c r="F43" s="180" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="234"/>
-      <c r="H43" s="234"/>
-      <c r="I43" s="234"/>
-      <c r="J43" s="234"/>
-      <c r="K43" s="234"/>
-      <c r="L43" s="234"/>
-      <c r="M43" s="234"/>
-      <c r="N43" s="234"/>
-      <c r="O43" s="234"/>
-      <c r="P43" s="234"/>
-      <c r="Q43" s="234"/>
-      <c r="R43" s="234"/>
-      <c r="S43" s="180"/>
+      <c r="G43" s="181"/>
+      <c r="H43" s="181"/>
+      <c r="I43" s="181"/>
+      <c r="J43" s="181"/>
+      <c r="K43" s="181"/>
+      <c r="L43" s="181"/>
+      <c r="M43" s="181"/>
+      <c r="N43" s="181"/>
+      <c r="O43" s="181"/>
+      <c r="P43" s="181"/>
+      <c r="Q43" s="181"/>
+      <c r="R43" s="181"/>
+      <c r="S43" s="235"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="176"/>
+      <c r="A44" s="232"/>
       <c r="B44" s="49" t="s">
         <v>87</v>
       </c>
@@ -5255,7 +5255,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="176"/>
+      <c r="A45" s="232"/>
       <c r="B45" s="33" t="s">
         <v>89</v>
       </c>
@@ -5389,7 +5389,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="176"/>
+      <c r="A46" s="232"/>
       <c r="B46" s="33" t="s">
         <v>83</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="176"/>
+      <c r="A47" s="232"/>
       <c r="B47" s="33" t="s">
         <v>84</v>
       </c>
@@ -5414,31 +5414,31 @@
       <c r="D47" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="179" t="s">
+      <c r="F47" s="162" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="221" t="str">
+      <c r="G47" s="166" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="179" t="s">
+      <c r="J47" s="162" t="s">
         <v>86</v>
       </c>
-      <c r="K47" s="219">
+      <c r="K47" s="164">
         <v>1</v>
       </c>
-      <c r="N47" s="179" t="s">
+      <c r="N47" s="162" t="s">
         <v>108</v>
       </c>
-      <c r="O47" s="182"/>
-      <c r="P47" s="183"/>
-      <c r="R47" s="179" t="s">
+      <c r="O47" s="236"/>
+      <c r="P47" s="237"/>
+      <c r="R47" s="162" t="s">
         <v>114</v>
       </c>
-      <c r="S47" s="179"/>
+      <c r="S47" s="162"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="178"/>
+      <c r="A48" s="234"/>
       <c r="B48" s="36" t="s">
         <v>85</v>
       </c>
@@ -5449,15 +5449,15 @@
       <c r="D48" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="F48" s="181"/>
-      <c r="G48" s="222"/>
-      <c r="J48" s="181"/>
-      <c r="K48" s="220"/>
-      <c r="N48" s="180"/>
-      <c r="O48" s="184"/>
-      <c r="P48" s="185"/>
-      <c r="R48" s="180"/>
-      <c r="S48" s="181"/>
+      <c r="F48" s="163"/>
+      <c r="G48" s="167"/>
+      <c r="J48" s="163"/>
+      <c r="K48" s="165"/>
+      <c r="N48" s="235"/>
+      <c r="O48" s="238"/>
+      <c r="P48" s="239"/>
+      <c r="R48" s="235"/>
+      <c r="S48" s="163"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5466,7 +5466,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="162" t="s">
+      <c r="A50" s="218" t="s">
         <v>65</v>
       </c>
       <c r="B50" s="134"/>
@@ -5489,7 +5489,7 @@
       <c r="S50" s="136"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="163"/>
+      <c r="A51" s="219"/>
       <c r="B51" s="137"/>
       <c r="C51" s="139"/>
       <c r="D51" s="139"/>
@@ -5510,7 +5510,7 @@
       <c r="S51" s="138"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="163"/>
+      <c r="A52" s="219"/>
       <c r="B52" s="137"/>
       <c r="C52" s="139"/>
       <c r="D52" s="139"/>
@@ -5531,7 +5531,7 @@
       <c r="S52" s="138"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="163"/>
+      <c r="A53" s="219"/>
       <c r="B53" s="137"/>
       <c r="C53" s="139"/>
       <c r="D53" s="139"/>
@@ -5552,7 +5552,7 @@
       <c r="S53" s="138"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="163"/>
+      <c r="A54" s="219"/>
       <c r="B54" s="137"/>
       <c r="C54" s="139"/>
       <c r="D54" s="139"/>
@@ -5573,7 +5573,7 @@
       <c r="S54" s="138"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="163"/>
+      <c r="A55" s="219"/>
       <c r="B55" s="137"/>
       <c r="C55" s="139"/>
       <c r="D55" s="139"/>
@@ -5594,7 +5594,7 @@
       <c r="S55" s="138"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="163"/>
+      <c r="A56" s="219"/>
       <c r="B56" s="137"/>
       <c r="C56" s="139"/>
       <c r="D56" s="139"/>
@@ -5615,7 +5615,7 @@
       <c r="S56" s="138"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="163"/>
+      <c r="A57" s="219"/>
       <c r="B57" s="137"/>
       <c r="C57" s="139"/>
       <c r="D57" s="139"/>
@@ -5636,57 +5636,57 @@
       <c r="S57" s="138"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="163"/>
+      <c r="A58" s="219"/>
       <c r="B58" s="140"/>
       <c r="S58" s="141"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="163"/>
+      <c r="A59" s="219"/>
       <c r="B59" s="140"/>
       <c r="S59" s="141"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="163"/>
+      <c r="A60" s="219"/>
       <c r="B60" s="140"/>
       <c r="S60" s="141"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="163"/>
+      <c r="A61" s="219"/>
       <c r="B61" s="140"/>
       <c r="S61" s="141"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="163"/>
+      <c r="A62" s="219"/>
       <c r="B62" s="140"/>
       <c r="S62" s="141"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="163"/>
+      <c r="A63" s="219"/>
       <c r="B63" s="140"/>
       <c r="S63" s="141"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="163"/>
+      <c r="A64" s="219"/>
       <c r="B64" s="140"/>
       <c r="S64" s="141"/>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="163"/>
+      <c r="A65" s="219"/>
       <c r="B65" s="140"/>
       <c r="S65" s="141"/>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="163"/>
+      <c r="A66" s="219"/>
       <c r="B66" s="140"/>
       <c r="S66" s="141"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="163"/>
+      <c r="A67" s="219"/>
       <c r="B67" s="140"/>
       <c r="S67" s="141"/>
     </row>
     <row r="68" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A68" s="164"/>
+      <c r="A68" s="220"/>
       <c r="B68" s="142"/>
       <c r="C68" s="77"/>
       <c r="D68" s="77"/>
@@ -5708,31 +5708,6 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="F43:R43"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A68"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A36:A38"/>
@@ -5749,6 +5724,31 @@
     <mergeCell ref="O47:P48"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="F47:F48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L9:M9"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11120,10 +11120,13 @@
         <v>N/A</v>
       </c>
       <c r="X2" t="str">
-        <f t="shared" ref="X2:X34" si="0">IFERROR(
+        <f>IFERROR(
 IF(
 ISNUMBER(SEARCH("2461LT",A2)),
 "Rehau 2461LT",
+IF(
+ISNUMBER(SEARCH("2461L",A2)),
+"Rehau 2461L",
 IF(
 ISNUMBER(SEARCH("3146L",A2)),
 "Rehau 3146L",
@@ -11134,6 +11137,7 @@
 ISNUMBER(--LEFT(SUBSTITUTE(TRIM(MID(A2,FIND("-",A2)+1,50)),"LR ","LR"),1)),
 "AGT "&amp;SUBSTITUTE(TRIM(MID(A2,FIND("-",A2)+1,50)),"LR ","LR"),
 SUBSTITUTE(TRIM(MID(A2,FIND("-",A2)+1,50)),"LR ","LR")
+)
 )
 )
 )
@@ -11198,11 +11202,11 @@
       <c r="T3" s="106"/>
       <c r="U3" s="115"/>
       <c r="V3" s="133" t="str">
-        <f t="shared" ref="V3:V34" si="1">IFERROR(IF(OR(W3="DB PAL",W3="DB MDF"),ROUND(Q3/13.5,0), ROUND(Q3/P3,2)),"")</f>
+        <f t="shared" ref="V3:V34" si="0">IFERROR(IF(OR(W3="DB PAL",W3="DB MDF"),ROUND(Q3/13.5,0), ROUND(Q3/P3,2)),"")</f>
         <v/>
       </c>
       <c r="W3" t="str">
-        <f t="shared" ref="W3:W34" si="2">IF(
+        <f t="shared" ref="W3:W34" si="1">IF(
     AND(
         OR(
             AND(D3=2800,E3=2070,OR(B3=19,B3=19.3)),
@@ -11298,7 +11302,32 @@
         <v>N/A</v>
       </c>
       <c r="X3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="X3:X34" si="2">IFERROR(
+IF(
+ISNUMBER(SEARCH("2461LT",A3)),
+"Rehau 2461LT",
+IF(
+ISNUMBER(SEARCH("2461L",A3)),
+"Rehau 2461L",
+IF(
+ISNUMBER(SEARCH("3146L",A3)),
+"Rehau 3146L",
+IF(
+ISNUMBER(SEARCH("1918L",A3)),
+"Rehau 1918L",
+IF(
+ISNUMBER(--LEFT(SUBSTITUTE(TRIM(MID(A3,FIND("-",A3)+1,50)),"LR ","LR"),1)),
+"AGT "&amp;SUBSTITUTE(TRIM(MID(A3,FIND("-",A3)+1,50)),"LR ","LR"),
+SUBSTITUTE(TRIM(MID(A3,FIND("-",A3)+1,50)),"LR ","LR")
+)
+)
+)
+)
+)
+&amp;IF(OR(E3=600,E3=650,E3=920)," /"&amp;E3,"")
+&amp;IF(E3=640," PS","")
+&amp;IF(AND(OR(B3=8,B3=10,B3=16),D3=2800,E3=2070)," "&amp;B3&amp;"mm",""),
+"")</f>
         <v/>
       </c>
       <c r="Y3" t="str">
@@ -11355,15 +11384,15 @@
       <c r="T4" s="115"/>
       <c r="U4" s="106"/>
       <c r="V4" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W4" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y4" t="str">
@@ -11385,36 +11414,15 @@
       <c r="T5" s="115"/>
       <c r="U5" s="106"/>
       <c r="V5" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W5" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W5" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X5" t="str">
-        <f>IFERROR(
-IF(
-ISNUMBER(SEARCH("2461LT",A5)),
-"Rehau 2461LT",
-IF(
-ISNUMBER(SEARCH("3146L",A5)),
-"Rehau 3146L",
-IF(
-ISNUMBER(SEARCH("1918L",A5)),
-"Rehau 1918L",
-IF(
-ISNUMBER(--LEFT(SUBSTITUTE(TRIM(MID(A5,FIND("-",A5)+1,50)),"LR ","LR"),1)),
-"AGT "&amp;SUBSTITUTE(TRIM(MID(A5,FIND("-",A5)+1,50)),"LR ","LR"),
-SUBSTITUTE(TRIM(MID(A5,FIND("-",A5)+1,50)),"LR ","LR")
-)
-)
-)
-)
-&amp;IF(OR(E5=600,E5=650,E5=920)," /"&amp;E5,"")
-&amp;IF(E5=640," PS","")
-&amp;IF(AND(OR(B5=8,B5=10,B5=16),D5=2800,E5=2070)," "&amp;B5&amp;"mm",""),
-"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y5" t="str">
@@ -11436,15 +11444,15 @@
       <c r="T6" s="115"/>
       <c r="U6" s="106"/>
       <c r="V6" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W6" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y6" t="str">
@@ -11466,15 +11474,15 @@
       <c r="T7" s="106"/>
       <c r="U7" s="106"/>
       <c r="V7" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W7" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y7" t="str">
@@ -11496,15 +11504,15 @@
       <c r="T8" s="115"/>
       <c r="U8" s="106"/>
       <c r="V8" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W8" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W8" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y8" t="str">
@@ -11526,15 +11534,15 @@
       <c r="T9" s="115"/>
       <c r="U9" s="104"/>
       <c r="V9" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W9" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W9" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y9" t="str">
@@ -11556,15 +11564,15 @@
       <c r="T10" s="115"/>
       <c r="U10" s="115"/>
       <c r="V10" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W10" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W10" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y10" t="str">
@@ -11586,15 +11594,15 @@
       <c r="T11" s="115"/>
       <c r="U11" s="115"/>
       <c r="V11" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W11" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W11" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y11" t="str">
@@ -11616,15 +11624,15 @@
       <c r="T12" s="107"/>
       <c r="U12" s="107"/>
       <c r="V12" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W12" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W12" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y12" t="str">
@@ -11646,15 +11654,15 @@
       <c r="T13" s="123"/>
       <c r="U13" s="129"/>
       <c r="V13" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W13" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W13" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y13" t="str">
@@ -11676,15 +11684,15 @@
       <c r="T14" s="124"/>
       <c r="U14" s="129"/>
       <c r="V14" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W14" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W14" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y14" t="str">
@@ -11706,15 +11714,15 @@
       <c r="T15" s="124"/>
       <c r="U15" s="107"/>
       <c r="V15" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W15" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W15" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y15" t="str">
@@ -11736,15 +11744,15 @@
       <c r="T16" s="124"/>
       <c r="U16" s="106"/>
       <c r="V16" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W16" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W16" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y16" t="str">
@@ -11766,15 +11774,15 @@
       <c r="T17" s="124"/>
       <c r="U17" s="106"/>
       <c r="V17" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W17" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W17" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y17" t="str">
@@ -11813,15 +11821,15 @@
       <c r="T18" s="124"/>
       <c r="U18" s="106"/>
       <c r="V18" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W18" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W18" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X18" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y18" t="str">
@@ -11859,15 +11867,15 @@
       <c r="S19" s="124"/>
       <c r="T19" s="124"/>
       <c r="V19" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W19" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W19" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X19" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y19" t="str">
@@ -11905,15 +11913,15 @@
       <c r="S20" s="123"/>
       <c r="T20" s="119"/>
       <c r="V20" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W20" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W20" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y20" t="str">
@@ -11951,15 +11959,15 @@
       <c r="S21" s="124"/>
       <c r="T21" s="123"/>
       <c r="V21" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W21" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W21" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y21" t="str">
@@ -11977,15 +11985,15 @@
     </row>
     <row r="22" spans="1:27">
       <c r="V22" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W22" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W22" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y22" t="str">
@@ -12003,15 +12011,15 @@
     </row>
     <row r="23" spans="1:27">
       <c r="V23" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W23" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y23" t="str">
@@ -12029,15 +12037,15 @@
     </row>
     <row r="24" spans="1:27">
       <c r="V24" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W24" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W24" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y24" t="str">
@@ -12055,15 +12063,15 @@
     </row>
     <row r="25" spans="1:27">
       <c r="V25" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W25" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W25" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X25" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y25" t="str">
@@ -12081,15 +12089,15 @@
     </row>
     <row r="26" spans="1:27">
       <c r="V26" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W26" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W26" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X26" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y26" t="str">
@@ -12107,15 +12115,15 @@
     </row>
     <row r="27" spans="1:27">
       <c r="V27" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W27" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W27" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X27" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y27" t="str">
@@ -12133,15 +12141,15 @@
     </row>
     <row r="28" spans="1:27">
       <c r="V28" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W28" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W28" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y28" t="str">
@@ -12159,15 +12167,15 @@
     </row>
     <row r="29" spans="1:27">
       <c r="V29" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W29" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W29" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X29" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y29" t="str">
@@ -12185,15 +12193,15 @@
     </row>
     <row r="30" spans="1:27">
       <c r="V30" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W30" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W30" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X30" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y30" t="str">
@@ -12211,15 +12219,15 @@
     </row>
     <row r="31" spans="1:27">
       <c r="V31" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W31" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W31" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X31" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y31" t="str">
@@ -12237,15 +12245,15 @@
     </row>
     <row r="32" spans="1:27">
       <c r="V32" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W32" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W32" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y32" t="str">
@@ -12263,15 +12271,15 @@
     </row>
     <row r="33" spans="22:27">
       <c r="V33" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W33" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W33" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y33" t="str">
@@ -12289,15 +12297,15 @@
     </row>
     <row r="34" spans="22:27">
       <c r="V34" s="133" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W34" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W34" t="str">
-        <f t="shared" si="2"/>
         <v>N/A</v>
       </c>
       <c r="X34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Y34" t="str">

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAF2C3E-5C05-476E-B777-738C2F988295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DC1FAC-DD55-4DA4-807A-A16D770C385A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1671,11 +1671,191 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1706,12 +1886,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1755,180 +1929,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2416,33 +2416,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="203" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="204"/>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="205"/>
       <c r="M1" s="38" t="s">
         <v>70</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="195" t="s">
+      <c r="O1" s="194" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="196"/>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="197"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="196"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2461,165 +2461,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="80"/>
-      <c r="O2" s="198"/>
-      <c r="P2" s="199"/>
-      <c r="Q2" s="199"/>
-      <c r="R2" s="199"/>
-      <c r="S2" s="200"/>
+      <c r="O2" s="197"/>
+      <c r="P2" s="198"/>
+      <c r="Q2" s="198"/>
+      <c r="R2" s="198"/>
+      <c r="S2" s="199"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="208"/>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="B3" s="209"/>
+      <c r="C3" s="210"/>
+      <c r="D3" s="211"/>
       <c r="H3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="215"/>
-      <c r="J3" s="216"/>
-      <c r="K3" s="217"/>
+      <c r="I3" s="216"/>
+      <c r="J3" s="217"/>
+      <c r="K3" s="218"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="73"/>
-      <c r="O3" s="205"/>
-      <c r="P3" s="206"/>
-      <c r="Q3" s="206"/>
-      <c r="R3" s="206"/>
-      <c r="S3" s="207"/>
+      <c r="O3" s="206"/>
+      <c r="P3" s="207"/>
+      <c r="Q3" s="207"/>
+      <c r="R3" s="207"/>
+      <c r="S3" s="208"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="189"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="191"/>
+      <c r="B4" s="188"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="190"/>
       <c r="H4" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="192"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="194"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="192"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="73"/>
-      <c r="O4" s="205"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="206"/>
-      <c r="S4" s="207"/>
+      <c r="O4" s="206"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="208"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="211"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="213"/>
+      <c r="B5" s="212"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="214"/>
       <c r="H5" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="214"/>
-      <c r="J5" s="206"/>
-      <c r="K5" s="207"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="207"/>
+      <c r="K5" s="208"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="73"/>
-      <c r="O5" s="205"/>
-      <c r="P5" s="206"/>
-      <c r="Q5" s="206"/>
-      <c r="R5" s="206"/>
-      <c r="S5" s="207"/>
+      <c r="O5" s="206"/>
+      <c r="P5" s="207"/>
+      <c r="Q5" s="207"/>
+      <c r="R5" s="207"/>
+      <c r="S5" s="208"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="168"/>
-      <c r="C6" s="169"/>
-      <c r="D6" s="170"/>
+      <c r="B6" s="223"/>
+      <c r="C6" s="224"/>
+      <c r="D6" s="225"/>
       <c r="H6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="171"/>
-      <c r="J6" s="172"/>
-      <c r="K6" s="173"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="201"/>
+      <c r="K6" s="202"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="74"/>
-      <c r="O6" s="201"/>
-      <c r="P6" s="172"/>
-      <c r="Q6" s="172"/>
-      <c r="R6" s="172"/>
-      <c r="S6" s="173"/>
+      <c r="O6" s="200"/>
+      <c r="P6" s="201"/>
+      <c r="Q6" s="201"/>
+      <c r="R6" s="201"/>
+      <c r="S6" s="202"/>
     </row>
     <row r="7" spans="1:19" s="50" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="174" t="s">
+      <c r="A8" s="227" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="175"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="176"/>
-      <c r="F8" s="180" t="s">
+      <c r="B8" s="228"/>
+      <c r="C8" s="228"/>
+      <c r="D8" s="229"/>
+      <c r="F8" s="233" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="181"/>
-      <c r="H8" s="181"/>
-      <c r="I8" s="181"/>
-      <c r="J8" s="181"/>
-      <c r="K8" s="181"/>
-      <c r="L8" s="181"/>
-      <c r="M8" s="181"/>
-      <c r="N8" s="181"/>
-      <c r="O8" s="181"/>
-      <c r="P8" s="181"/>
-      <c r="Q8" s="181"/>
-      <c r="R8" s="181"/>
-      <c r="S8" s="186"/>
+      <c r="G8" s="234"/>
+      <c r="H8" s="234"/>
+      <c r="I8" s="234"/>
+      <c r="J8" s="234"/>
+      <c r="K8" s="234"/>
+      <c r="L8" s="234"/>
+      <c r="M8" s="234"/>
+      <c r="N8" s="234"/>
+      <c r="O8" s="234"/>
+      <c r="P8" s="234"/>
+      <c r="Q8" s="234"/>
+      <c r="R8" s="234"/>
+      <c r="S8" s="239"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="177"/>
-      <c r="B9" s="178"/>
-      <c r="C9" s="178"/>
-      <c r="D9" s="179"/>
-      <c r="F9" s="226" t="s">
+      <c r="A9" s="230"/>
+      <c r="B9" s="231"/>
+      <c r="C9" s="231"/>
+      <c r="D9" s="232"/>
+      <c r="F9" s="170" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="227"/>
-      <c r="H9" s="240" t="s">
+      <c r="G9" s="171"/>
+      <c r="H9" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="241"/>
-      <c r="J9" s="224" t="s">
+      <c r="I9" s="187"/>
+      <c r="J9" s="168" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="225"/>
-      <c r="L9" s="187" t="s">
+      <c r="K9" s="169"/>
+      <c r="L9" s="240" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="188"/>
-      <c r="N9" s="184" t="s">
+      <c r="M9" s="241"/>
+      <c r="N9" s="237" t="s">
         <v>80</v>
       </c>
-      <c r="O9" s="185"/>
-      <c r="P9" s="182" t="s">
+      <c r="O9" s="238"/>
+      <c r="P9" s="235" t="s">
         <v>68</v>
       </c>
-      <c r="Q9" s="183"/>
-      <c r="R9" s="184" t="s">
+      <c r="Q9" s="236"/>
+      <c r="R9" s="237" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="185"/>
+      <c r="S9" s="238"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="231" t="s">
+      <c r="A10" s="175" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2676,7 +2676,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="232"/>
+      <c r="A11" s="176"/>
       <c r="B11" s="56" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2767,7 +2767,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="232"/>
+      <c r="A12" s="176"/>
       <c r="B12" s="108" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -2859,7 +2859,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="232"/>
+      <c r="A13" s="176"/>
       <c r="B13" s="108" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -2955,7 +2955,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="232"/>
+      <c r="A14" s="176"/>
       <c r="B14" s="108" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3051,7 +3051,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="232"/>
+      <c r="A15" s="176"/>
       <c r="B15" s="108" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3147,7 +3147,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="232"/>
+      <c r="A16" s="176"/>
       <c r="B16" s="108" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3243,7 +3243,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="232"/>
+      <c r="A17" s="176"/>
       <c r="B17" s="108" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3339,7 +3339,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="232"/>
+      <c r="A18" s="176"/>
       <c r="B18" s="108" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3435,7 +3435,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="232"/>
+      <c r="A19" s="176"/>
       <c r="B19" s="108" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3531,7 +3531,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="232"/>
+      <c r="A20" s="176"/>
       <c r="B20" s="108" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3627,7 +3627,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="232"/>
+      <c r="A21" s="176"/>
       <c r="B21" s="108" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3723,7 +3723,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="233"/>
+      <c r="A22" s="177"/>
       <c r="B22" s="108" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3864,7 +3864,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="231" t="s">
+      <c r="A24" s="175" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="56" t="str" cm="1">
@@ -3962,7 +3962,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="232"/>
+      <c r="A25" s="176"/>
       <c r="B25" s="67" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4058,7 +4058,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="232"/>
+      <c r="A26" s="176"/>
       <c r="B26" s="67" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4154,7 +4154,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="232"/>
+      <c r="A27" s="176"/>
       <c r="B27" s="67" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="234"/>
+      <c r="A28" s="178"/>
       <c r="B28" s="67" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4477,7 +4477,7 @@
       <c r="S31" s="160"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="221" t="s">
+      <c r="A32" s="165" t="s">
         <v>78</v>
       </c>
       <c r="B32" s="56" t="str" cm="1">
@@ -4564,7 +4564,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="222"/>
+      <c r="A33" s="166"/>
       <c r="B33" s="67" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),2))),"")</f>
         <v/>
@@ -4649,7 +4649,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="223"/>
+      <c r="A34" s="167"/>
       <c r="B34" s="67" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),3))),"")</f>
         <v/>
@@ -4773,7 +4773,7 @@
       <c r="S35" s="161"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="221" t="s">
+      <c r="A36" s="165" t="s">
         <v>79</v>
       </c>
       <c r="B36" s="56" t="str" cm="1">
@@ -4860,7 +4860,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="222"/>
+      <c r="A37" s="166"/>
       <c r="B37" s="67" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4945,7 +4945,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="223"/>
+      <c r="A38" s="167"/>
       <c r="B38" s="68" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5044,7 +5044,7 @@
       <c r="Q39" s="61"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="231" t="s">
+      <c r="A40" s="175" t="s">
         <v>50</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5056,25 +5056,25 @@
       <c r="D40" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="228" t="s">
+      <c r="F40" s="172" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="229"/>
-      <c r="H40" s="229"/>
-      <c r="I40" s="229"/>
-      <c r="J40" s="229"/>
-      <c r="K40" s="229"/>
-      <c r="L40" s="229"/>
-      <c r="M40" s="229"/>
-      <c r="N40" s="229"/>
-      <c r="O40" s="229"/>
-      <c r="P40" s="229"/>
-      <c r="Q40" s="229"/>
-      <c r="R40" s="229"/>
-      <c r="S40" s="230"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="173"/>
+      <c r="I40" s="173"/>
+      <c r="J40" s="173"/>
+      <c r="K40" s="173"/>
+      <c r="L40" s="173"/>
+      <c r="M40" s="173"/>
+      <c r="N40" s="173"/>
+      <c r="O40" s="173"/>
+      <c r="P40" s="173"/>
+      <c r="Q40" s="173"/>
+      <c r="R40" s="173"/>
+      <c r="S40" s="174"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="232"/>
+      <c r="A41" s="176"/>
       <c r="B41" s="35" t="s">
         <v>81</v>
       </c>
@@ -5137,7 +5137,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="232"/>
+      <c r="A42" s="176"/>
       <c r="B42" s="49" t="s">
         <v>88</v>
       </c>
@@ -5162,13 +5162,13 @@
       <c r="P42" s="66"/>
       <c r="Q42" s="78"/>
       <c r="R42" s="79"/>
-      <c r="S42" s="162">
+      <c r="S42" s="179">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="232"/>
+      <c r="A43" s="176"/>
       <c r="B43" s="49" t="s">
         <v>82</v>
       </c>
@@ -5180,26 +5180,26 @@
         <v>54</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="180" t="str">
+      <c r="F43" s="233" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="181"/>
-      <c r="H43" s="181"/>
-      <c r="I43" s="181"/>
-      <c r="J43" s="181"/>
-      <c r="K43" s="181"/>
-      <c r="L43" s="181"/>
-      <c r="M43" s="181"/>
-      <c r="N43" s="181"/>
-      <c r="O43" s="181"/>
-      <c r="P43" s="181"/>
-      <c r="Q43" s="181"/>
-      <c r="R43" s="181"/>
-      <c r="S43" s="235"/>
+      <c r="G43" s="234"/>
+      <c r="H43" s="234"/>
+      <c r="I43" s="234"/>
+      <c r="J43" s="234"/>
+      <c r="K43" s="234"/>
+      <c r="L43" s="234"/>
+      <c r="M43" s="234"/>
+      <c r="N43" s="234"/>
+      <c r="O43" s="234"/>
+      <c r="P43" s="234"/>
+      <c r="Q43" s="234"/>
+      <c r="R43" s="234"/>
+      <c r="S43" s="180"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="232"/>
+      <c r="A44" s="176"/>
       <c r="B44" s="49" t="s">
         <v>87</v>
       </c>
@@ -5255,7 +5255,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="232"/>
+      <c r="A45" s="176"/>
       <c r="B45" s="33" t="s">
         <v>89</v>
       </c>
@@ -5389,7 +5389,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="232"/>
+      <c r="A46" s="176"/>
       <c r="B46" s="33" t="s">
         <v>83</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="232"/>
+      <c r="A47" s="176"/>
       <c r="B47" s="33" t="s">
         <v>84</v>
       </c>
@@ -5414,31 +5414,31 @@
       <c r="D47" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="162" t="s">
+      <c r="F47" s="179" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="166" t="str">
+      <c r="G47" s="221" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="162" t="s">
+      <c r="J47" s="179" t="s">
         <v>86</v>
       </c>
-      <c r="K47" s="164">
+      <c r="K47" s="219">
         <v>1</v>
       </c>
-      <c r="N47" s="162" t="s">
+      <c r="N47" s="179" t="s">
         <v>108</v>
       </c>
-      <c r="O47" s="236"/>
-      <c r="P47" s="237"/>
-      <c r="R47" s="162" t="s">
+      <c r="O47" s="182"/>
+      <c r="P47" s="183"/>
+      <c r="R47" s="179" t="s">
         <v>114</v>
       </c>
-      <c r="S47" s="162"/>
+      <c r="S47" s="179"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="234"/>
+      <c r="A48" s="178"/>
       <c r="B48" s="36" t="s">
         <v>85</v>
       </c>
@@ -5449,15 +5449,15 @@
       <c r="D48" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="F48" s="163"/>
-      <c r="G48" s="167"/>
-      <c r="J48" s="163"/>
-      <c r="K48" s="165"/>
-      <c r="N48" s="235"/>
-      <c r="O48" s="238"/>
-      <c r="P48" s="239"/>
-      <c r="R48" s="235"/>
-      <c r="S48" s="163"/>
+      <c r="F48" s="181"/>
+      <c r="G48" s="222"/>
+      <c r="J48" s="181"/>
+      <c r="K48" s="220"/>
+      <c r="N48" s="180"/>
+      <c r="O48" s="184"/>
+      <c r="P48" s="185"/>
+      <c r="R48" s="180"/>
+      <c r="S48" s="181"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5466,7 +5466,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="218" t="s">
+      <c r="A50" s="162" t="s">
         <v>65</v>
       </c>
       <c r="B50" s="134"/>
@@ -5489,7 +5489,7 @@
       <c r="S50" s="136"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="219"/>
+      <c r="A51" s="163"/>
       <c r="B51" s="137"/>
       <c r="C51" s="139"/>
       <c r="D51" s="139"/>
@@ -5510,7 +5510,7 @@
       <c r="S51" s="138"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="219"/>
+      <c r="A52" s="163"/>
       <c r="B52" s="137"/>
       <c r="C52" s="139"/>
       <c r="D52" s="139"/>
@@ -5531,7 +5531,7 @@
       <c r="S52" s="138"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="219"/>
+      <c r="A53" s="163"/>
       <c r="B53" s="137"/>
       <c r="C53" s="139"/>
       <c r="D53" s="139"/>
@@ -5552,7 +5552,7 @@
       <c r="S53" s="138"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="219"/>
+      <c r="A54" s="163"/>
       <c r="B54" s="137"/>
       <c r="C54" s="139"/>
       <c r="D54" s="139"/>
@@ -5573,7 +5573,7 @@
       <c r="S54" s="138"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="219"/>
+      <c r="A55" s="163"/>
       <c r="B55" s="137"/>
       <c r="C55" s="139"/>
       <c r="D55" s="139"/>
@@ -5594,7 +5594,7 @@
       <c r="S55" s="138"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="219"/>
+      <c r="A56" s="163"/>
       <c r="B56" s="137"/>
       <c r="C56" s="139"/>
       <c r="D56" s="139"/>
@@ -5615,7 +5615,7 @@
       <c r="S56" s="138"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="219"/>
+      <c r="A57" s="163"/>
       <c r="B57" s="137"/>
       <c r="C57" s="139"/>
       <c r="D57" s="139"/>
@@ -5636,57 +5636,57 @@
       <c r="S57" s="138"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="219"/>
+      <c r="A58" s="163"/>
       <c r="B58" s="140"/>
       <c r="S58" s="141"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="219"/>
+      <c r="A59" s="163"/>
       <c r="B59" s="140"/>
       <c r="S59" s="141"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="219"/>
+      <c r="A60" s="163"/>
       <c r="B60" s="140"/>
       <c r="S60" s="141"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="219"/>
+      <c r="A61" s="163"/>
       <c r="B61" s="140"/>
       <c r="S61" s="141"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="219"/>
+      <c r="A62" s="163"/>
       <c r="B62" s="140"/>
       <c r="S62" s="141"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="219"/>
+      <c r="A63" s="163"/>
       <c r="B63" s="140"/>
       <c r="S63" s="141"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="219"/>
+      <c r="A64" s="163"/>
       <c r="B64" s="140"/>
       <c r="S64" s="141"/>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="219"/>
+      <c r="A65" s="163"/>
       <c r="B65" s="140"/>
       <c r="S65" s="141"/>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="219"/>
+      <c r="A66" s="163"/>
       <c r="B66" s="140"/>
       <c r="S66" s="141"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="219"/>
+      <c r="A67" s="163"/>
       <c r="B67" s="140"/>
       <c r="S67" s="141"/>
     </row>
     <row r="68" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A68" s="220"/>
+      <c r="A68" s="164"/>
       <c r="B68" s="142"/>
       <c r="C68" s="77"/>
       <c r="D68" s="77"/>
@@ -5708,6 +5708,31 @@
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A68"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A36:A38"/>
@@ -5724,31 +5749,6 @@
     <mergeCell ref="O47:P48"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="F47:F48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="F43:R43"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L9:M9"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11150,25 +11150,25 @@
       </c>
       <c r="Y2" t="str">
         <f>IF(W2="","",
-    IF(
-        OR(
-            ISNUMBER(FIND(" ST",X2)),
-            ISNUMBER(FIND(" SM",X2)),
-            ISNUMBER(FIND(" PM",X2)),
-            ISNUMBER(FIND(" TM",X2)),
-            ISNUMBER(FIND(" PG",X2)),
-            ISNUMBER(FIND(" PA",X2))
-        ),
-        IF(OR(E2=600,E2=650,E2=920),
-            SUBSTITUTE(X2," ","",1),
-            IFERROR(LEFT(SUBSTITUTE(X2," ","",1), FIND("/",SUBSTITUTE(X2," ","",1))-1), SUBSTITUTE(X2," ","",1))
-        ),
-        IF(OR(E2=600,E2=650,E2=920),
-            X2,
-            IFERROR(LEFT(X2, FIND("/",X2)-1), X2)
-        )
-    )
-    &amp;IF(W2="LC"," LC","")
+IF(
+OR(
+ISNUMBER(FIND(" ST",X2)),
+ISNUMBER(FIND(" SM",X2)),
+ISNUMBER(FIND(" PM",X2)),
+ISNUMBER(FIND(" TM",X2)),
+ISNUMBER(FIND(" PG",X2)),
+ISNUMBER(FIND(" PA",X2))
+),
+IF(OR(E2=600,E2=650,E2=920,LEFT(A2,5)="CLMEL"),
+SUBSTITUTE(X2," ","",1),
+IFERROR(LEFT(SUBSTITUTE(X2," ","",1),FIND("/",SUBSTITUTE(X2," ","",1))-1),SUBSTITUTE(X2," ","",1))
+),
+IF(OR(E2=600,E2=650,E2=920,LEFT(A2,5)="CLMEL"),
+X2,
+IFERROR(LEFT(X2,FIND("/",X2)-1),X2)
+)
+)
+&amp;IF(W2="LC"," LC","")
 )</f>
         <v/>
       </c>
@@ -11332,25 +11332,25 @@
       </c>
       <c r="Y3" t="str">
         <f t="shared" ref="Y3:Y34" si="3">IF(W3="","",
-    IF(
-        OR(
-            ISNUMBER(FIND(" ST",X3)),
-            ISNUMBER(FIND(" SM",X3)),
-            ISNUMBER(FIND(" PM",X3)),
-            ISNUMBER(FIND(" TM",X3)),
-            ISNUMBER(FIND(" PG",X3)),
-            ISNUMBER(FIND(" PA",X3))
-        ),
-        IF(OR(E3=600,E3=650,E3=920),
-            SUBSTITUTE(X3," ","",1),
-            IFERROR(LEFT(SUBSTITUTE(X3," ","",1), FIND("/",SUBSTITUTE(X3," ","",1))-1), SUBSTITUTE(X3," ","",1))
-        ),
-        IF(OR(E3=600,E3=650,E3=920),
-            X3,
-            IFERROR(LEFT(X3, FIND("/",X3)-1), X3)
-        )
-    )
-    &amp;IF(W3="LC"," LC","")
+IF(
+OR(
+ISNUMBER(FIND(" ST",X3)),
+ISNUMBER(FIND(" SM",X3)),
+ISNUMBER(FIND(" PM",X3)),
+ISNUMBER(FIND(" TM",X3)),
+ISNUMBER(FIND(" PG",X3)),
+ISNUMBER(FIND(" PA",X3))
+),
+IF(OR(E3=600,E3=650,E3=920,LEFT(A3,5)="CLMEL"),
+SUBSTITUTE(X3," ","",1),
+IFERROR(LEFT(SUBSTITUTE(X3," ","",1),FIND("/",SUBSTITUTE(X3," ","",1))-1),SUBSTITUTE(X3," ","",1))
+),
+IF(OR(E3=600,E3=650,E3=920,LEFT(A3,5)="CLMEL"),
+X3,
+IFERROR(LEFT(X3,FIND("/",X3)-1),X3)
+)
+)
+&amp;IF(W3="LC"," LC","")
 )</f>
         <v/>
       </c>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DC1FAC-DD55-4DA4-807A-A16D770C385A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF21081-4C14-480F-B4A8-A7CE16D84001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1671,82 +1671,90 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1794,12 +1802,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1857,78 +1859,76 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2416,33 +2416,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="202" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="205"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="203"/>
+      <c r="L1" s="204"/>
       <c r="M1" s="38" t="s">
         <v>70</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="194" t="s">
+      <c r="O1" s="195" t="s">
         <v>69</v>
       </c>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="196"/>
+      <c r="P1" s="196"/>
+      <c r="Q1" s="196"/>
+      <c r="R1" s="196"/>
+      <c r="S1" s="197"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2461,165 +2461,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="80"/>
-      <c r="O2" s="197"/>
-      <c r="P2" s="198"/>
-      <c r="Q2" s="198"/>
-      <c r="R2" s="198"/>
-      <c r="S2" s="199"/>
+      <c r="O2" s="198"/>
+      <c r="P2" s="199"/>
+      <c r="Q2" s="199"/>
+      <c r="R2" s="199"/>
+      <c r="S2" s="200"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="209"/>
-      <c r="C3" s="210"/>
-      <c r="D3" s="211"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
       <c r="H3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="216"/>
-      <c r="J3" s="217"/>
-      <c r="K3" s="218"/>
+      <c r="I3" s="215"/>
+      <c r="J3" s="216"/>
+      <c r="K3" s="217"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="73"/>
-      <c r="O3" s="206"/>
-      <c r="P3" s="207"/>
-      <c r="Q3" s="207"/>
-      <c r="R3" s="207"/>
-      <c r="S3" s="208"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="206"/>
+      <c r="Q3" s="206"/>
+      <c r="R3" s="206"/>
+      <c r="S3" s="207"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="188"/>
-      <c r="C4" s="189"/>
-      <c r="D4" s="190"/>
+      <c r="B4" s="189"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="191"/>
       <c r="H4" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="191"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="193"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="73"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="207"/>
-      <c r="Q4" s="207"/>
-      <c r="R4" s="207"/>
-      <c r="S4" s="208"/>
+      <c r="O4" s="205"/>
+      <c r="P4" s="206"/>
+      <c r="Q4" s="206"/>
+      <c r="R4" s="206"/>
+      <c r="S4" s="207"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="212"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="214"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="212"/>
+      <c r="D5" s="213"/>
       <c r="H5" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="215"/>
-      <c r="J5" s="207"/>
-      <c r="K5" s="208"/>
+      <c r="I5" s="214"/>
+      <c r="J5" s="206"/>
+      <c r="K5" s="207"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="73"/>
-      <c r="O5" s="206"/>
-      <c r="P5" s="207"/>
-      <c r="Q5" s="207"/>
-      <c r="R5" s="207"/>
-      <c r="S5" s="208"/>
+      <c r="O5" s="205"/>
+      <c r="P5" s="206"/>
+      <c r="Q5" s="206"/>
+      <c r="R5" s="206"/>
+      <c r="S5" s="207"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="223"/>
-      <c r="C6" s="224"/>
-      <c r="D6" s="225"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="170"/>
       <c r="H6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="226"/>
-      <c r="J6" s="201"/>
-      <c r="K6" s="202"/>
+      <c r="I6" s="171"/>
+      <c r="J6" s="172"/>
+      <c r="K6" s="173"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="74"/>
-      <c r="O6" s="200"/>
-      <c r="P6" s="201"/>
-      <c r="Q6" s="201"/>
-      <c r="R6" s="201"/>
-      <c r="S6" s="202"/>
+      <c r="O6" s="201"/>
+      <c r="P6" s="172"/>
+      <c r="Q6" s="172"/>
+      <c r="R6" s="172"/>
+      <c r="S6" s="173"/>
     </row>
     <row r="7" spans="1:19" s="50" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="227" t="s">
+      <c r="A8" s="174" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="228"/>
-      <c r="C8" s="228"/>
-      <c r="D8" s="229"/>
-      <c r="F8" s="233" t="s">
+      <c r="B8" s="175"/>
+      <c r="C8" s="175"/>
+      <c r="D8" s="176"/>
+      <c r="F8" s="180" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="234"/>
-      <c r="H8" s="234"/>
-      <c r="I8" s="234"/>
-      <c r="J8" s="234"/>
-      <c r="K8" s="234"/>
-      <c r="L8" s="234"/>
-      <c r="M8" s="234"/>
-      <c r="N8" s="234"/>
-      <c r="O8" s="234"/>
-      <c r="P8" s="234"/>
-      <c r="Q8" s="234"/>
-      <c r="R8" s="234"/>
-      <c r="S8" s="239"/>
+      <c r="G8" s="181"/>
+      <c r="H8" s="181"/>
+      <c r="I8" s="181"/>
+      <c r="J8" s="181"/>
+      <c r="K8" s="181"/>
+      <c r="L8" s="181"/>
+      <c r="M8" s="181"/>
+      <c r="N8" s="181"/>
+      <c r="O8" s="181"/>
+      <c r="P8" s="181"/>
+      <c r="Q8" s="181"/>
+      <c r="R8" s="181"/>
+      <c r="S8" s="186"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="230"/>
-      <c r="B9" s="231"/>
-      <c r="C9" s="231"/>
-      <c r="D9" s="232"/>
-      <c r="F9" s="170" t="s">
+      <c r="A9" s="177"/>
+      <c r="B9" s="178"/>
+      <c r="C9" s="178"/>
+      <c r="D9" s="179"/>
+      <c r="F9" s="226" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="171"/>
-      <c r="H9" s="186" t="s">
+      <c r="G9" s="227"/>
+      <c r="H9" s="240" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="187"/>
-      <c r="J9" s="168" t="s">
+      <c r="I9" s="241"/>
+      <c r="J9" s="224" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="169"/>
-      <c r="L9" s="240" t="s">
+      <c r="K9" s="225"/>
+      <c r="L9" s="187" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="241"/>
-      <c r="N9" s="237" t="s">
+      <c r="M9" s="188"/>
+      <c r="N9" s="184" t="s">
         <v>80</v>
       </c>
-      <c r="O9" s="238"/>
-      <c r="P9" s="235" t="s">
+      <c r="O9" s="185"/>
+      <c r="P9" s="182" t="s">
         <v>68</v>
       </c>
-      <c r="Q9" s="236"/>
-      <c r="R9" s="237" t="s">
+      <c r="Q9" s="183"/>
+      <c r="R9" s="184" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="238"/>
+      <c r="S9" s="185"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="175" t="s">
+      <c r="A10" s="231" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2676,7 +2676,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="176"/>
+      <c r="A11" s="232"/>
       <c r="B11" s="56" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2767,7 +2767,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="176"/>
+      <c r="A12" s="232"/>
       <c r="B12" s="108" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -2859,7 +2859,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="176"/>
+      <c r="A13" s="232"/>
       <c r="B13" s="108" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -2955,7 +2955,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="176"/>
+      <c r="A14" s="232"/>
       <c r="B14" s="108" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3051,7 +3051,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="176"/>
+      <c r="A15" s="232"/>
       <c r="B15" s="108" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3147,7 +3147,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="176"/>
+      <c r="A16" s="232"/>
       <c r="B16" s="108" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3243,7 +3243,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="176"/>
+      <c r="A17" s="232"/>
       <c r="B17" s="108" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3339,7 +3339,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="176"/>
+      <c r="A18" s="232"/>
       <c r="B18" s="108" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3435,7 +3435,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="176"/>
+      <c r="A19" s="232"/>
       <c r="B19" s="108" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3531,7 +3531,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="176"/>
+      <c r="A20" s="232"/>
       <c r="B20" s="108" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3627,7 +3627,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="176"/>
+      <c r="A21" s="232"/>
       <c r="B21" s="108" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3723,7 +3723,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15" customHeight="1" thickBot="1">
-      <c r="A22" s="177"/>
+      <c r="A22" s="233"/>
       <c r="B22" s="108" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3864,7 +3864,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="175" t="s">
+      <c r="A24" s="231" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="56" t="str" cm="1">
@@ -3962,7 +3962,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="176"/>
+      <c r="A25" s="232"/>
       <c r="B25" s="67" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4058,7 +4058,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="176"/>
+      <c r="A26" s="232"/>
       <c r="B26" s="67" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4154,7 +4154,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="176"/>
+      <c r="A27" s="232"/>
       <c r="B27" s="67" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="178"/>
+      <c r="A28" s="234"/>
       <c r="B28" s="67" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4477,7 +4477,7 @@
       <c r="S31" s="160"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="165" t="s">
+      <c r="A32" s="221" t="s">
         <v>78</v>
       </c>
       <c r="B32" s="56" t="str" cm="1">
@@ -4564,7 +4564,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="166"/>
+      <c r="A33" s="222"/>
       <c r="B33" s="67" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),2))),"")</f>
         <v/>
@@ -4649,7 +4649,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="167"/>
+      <c r="A34" s="223"/>
       <c r="B34" s="67" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/((Deco!$W$2:$W$99="Blat")+(Deco!$W$2:$W$99="LC")),3))),"")</f>
         <v/>
@@ -4773,7 +4773,7 @@
       <c r="S35" s="161"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="165" t="s">
+      <c r="A36" s="221" t="s">
         <v>79</v>
       </c>
       <c r="B36" s="56" t="str" cm="1">
@@ -4860,7 +4860,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="166"/>
+      <c r="A37" s="222"/>
       <c r="B37" s="67" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4945,7 +4945,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="167"/>
+      <c r="A38" s="223"/>
       <c r="B38" s="68" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5044,7 +5044,7 @@
       <c r="Q39" s="61"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="175" t="s">
+      <c r="A40" s="231" t="s">
         <v>50</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5056,25 +5056,25 @@
       <c r="D40" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="172" t="s">
+      <c r="F40" s="228" t="s">
         <v>72</v>
       </c>
-      <c r="G40" s="173"/>
-      <c r="H40" s="173"/>
-      <c r="I40" s="173"/>
-      <c r="J40" s="173"/>
-      <c r="K40" s="173"/>
-      <c r="L40" s="173"/>
-      <c r="M40" s="173"/>
-      <c r="N40" s="173"/>
-      <c r="O40" s="173"/>
-      <c r="P40" s="173"/>
-      <c r="Q40" s="173"/>
-      <c r="R40" s="173"/>
-      <c r="S40" s="174"/>
+      <c r="G40" s="229"/>
+      <c r="H40" s="229"/>
+      <c r="I40" s="229"/>
+      <c r="J40" s="229"/>
+      <c r="K40" s="229"/>
+      <c r="L40" s="229"/>
+      <c r="M40" s="229"/>
+      <c r="N40" s="229"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="229"/>
+      <c r="Q40" s="229"/>
+      <c r="R40" s="229"/>
+      <c r="S40" s="230"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="176"/>
+      <c r="A41" s="232"/>
       <c r="B41" s="35" t="s">
         <v>81</v>
       </c>
@@ -5137,7 +5137,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="176"/>
+      <c r="A42" s="232"/>
       <c r="B42" s="49" t="s">
         <v>88</v>
       </c>
@@ -5162,13 +5162,13 @@
       <c r="P42" s="66"/>
       <c r="Q42" s="78"/>
       <c r="R42" s="79"/>
-      <c r="S42" s="179">
+      <c r="S42" s="162">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="176"/>
+      <c r="A43" s="232"/>
       <c r="B43" s="49" t="s">
         <v>82</v>
       </c>
@@ -5180,26 +5180,26 @@
         <v>54</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="233" t="str">
+      <c r="F43" s="180" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="234"/>
-      <c r="H43" s="234"/>
-      <c r="I43" s="234"/>
-      <c r="J43" s="234"/>
-      <c r="K43" s="234"/>
-      <c r="L43" s="234"/>
-      <c r="M43" s="234"/>
-      <c r="N43" s="234"/>
-      <c r="O43" s="234"/>
-      <c r="P43" s="234"/>
-      <c r="Q43" s="234"/>
-      <c r="R43" s="234"/>
-      <c r="S43" s="180"/>
+      <c r="G43" s="181"/>
+      <c r="H43" s="181"/>
+      <c r="I43" s="181"/>
+      <c r="J43" s="181"/>
+      <c r="K43" s="181"/>
+      <c r="L43" s="181"/>
+      <c r="M43" s="181"/>
+      <c r="N43" s="181"/>
+      <c r="O43" s="181"/>
+      <c r="P43" s="181"/>
+      <c r="Q43" s="181"/>
+      <c r="R43" s="181"/>
+      <c r="S43" s="235"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="176"/>
+      <c r="A44" s="232"/>
       <c r="B44" s="49" t="s">
         <v>87</v>
       </c>
@@ -5255,7 +5255,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="176"/>
+      <c r="A45" s="232"/>
       <c r="B45" s="33" t="s">
         <v>89</v>
       </c>
@@ -5389,7 +5389,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="176"/>
+      <c r="A46" s="232"/>
       <c r="B46" s="33" t="s">
         <v>83</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="176"/>
+      <c r="A47" s="232"/>
       <c r="B47" s="33" t="s">
         <v>84</v>
       </c>
@@ -5414,31 +5414,31 @@
       <c r="D47" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="179" t="s">
+      <c r="F47" s="162" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="221" t="str">
+      <c r="G47" s="166" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="179" t="s">
+      <c r="J47" s="162" t="s">
         <v>86</v>
       </c>
-      <c r="K47" s="219">
+      <c r="K47" s="164">
         <v>1</v>
       </c>
-      <c r="N47" s="179" t="s">
+      <c r="N47" s="162" t="s">
         <v>108</v>
       </c>
-      <c r="O47" s="182"/>
-      <c r="P47" s="183"/>
-      <c r="R47" s="179" t="s">
+      <c r="O47" s="236"/>
+      <c r="P47" s="237"/>
+      <c r="R47" s="162" t="s">
         <v>114</v>
       </c>
-      <c r="S47" s="179"/>
+      <c r="S47" s="162"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="178"/>
+      <c r="A48" s="234"/>
       <c r="B48" s="36" t="s">
         <v>85</v>
       </c>
@@ -5449,15 +5449,15 @@
       <c r="D48" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="F48" s="181"/>
-      <c r="G48" s="222"/>
-      <c r="J48" s="181"/>
-      <c r="K48" s="220"/>
-      <c r="N48" s="180"/>
-      <c r="O48" s="184"/>
-      <c r="P48" s="185"/>
-      <c r="R48" s="180"/>
-      <c r="S48" s="181"/>
+      <c r="F48" s="163"/>
+      <c r="G48" s="167"/>
+      <c r="J48" s="163"/>
+      <c r="K48" s="165"/>
+      <c r="N48" s="235"/>
+      <c r="O48" s="238"/>
+      <c r="P48" s="239"/>
+      <c r="R48" s="235"/>
+      <c r="S48" s="163"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5466,7 +5466,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="162" t="s">
+      <c r="A50" s="218" t="s">
         <v>65</v>
       </c>
       <c r="B50" s="134"/>
@@ -5489,7 +5489,7 @@
       <c r="S50" s="136"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="163"/>
+      <c r="A51" s="219"/>
       <c r="B51" s="137"/>
       <c r="C51" s="139"/>
       <c r="D51" s="139"/>
@@ -5510,7 +5510,7 @@
       <c r="S51" s="138"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="163"/>
+      <c r="A52" s="219"/>
       <c r="B52" s="137"/>
       <c r="C52" s="139"/>
       <c r="D52" s="139"/>
@@ -5531,7 +5531,7 @@
       <c r="S52" s="138"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="163"/>
+      <c r="A53" s="219"/>
       <c r="B53" s="137"/>
       <c r="C53" s="139"/>
       <c r="D53" s="139"/>
@@ -5552,7 +5552,7 @@
       <c r="S53" s="138"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="163"/>
+      <c r="A54" s="219"/>
       <c r="B54" s="137"/>
       <c r="C54" s="139"/>
       <c r="D54" s="139"/>
@@ -5573,7 +5573,7 @@
       <c r="S54" s="138"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="163"/>
+      <c r="A55" s="219"/>
       <c r="B55" s="137"/>
       <c r="C55" s="139"/>
       <c r="D55" s="139"/>
@@ -5594,7 +5594,7 @@
       <c r="S55" s="138"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="163"/>
+      <c r="A56" s="219"/>
       <c r="B56" s="137"/>
       <c r="C56" s="139"/>
       <c r="D56" s="139"/>
@@ -5615,7 +5615,7 @@
       <c r="S56" s="138"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="163"/>
+      <c r="A57" s="219"/>
       <c r="B57" s="137"/>
       <c r="C57" s="139"/>
       <c r="D57" s="139"/>
@@ -5636,57 +5636,57 @@
       <c r="S57" s="138"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="163"/>
+      <c r="A58" s="219"/>
       <c r="B58" s="140"/>
       <c r="S58" s="141"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="163"/>
+      <c r="A59" s="219"/>
       <c r="B59" s="140"/>
       <c r="S59" s="141"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="163"/>
+      <c r="A60" s="219"/>
       <c r="B60" s="140"/>
       <c r="S60" s="141"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="163"/>
+      <c r="A61" s="219"/>
       <c r="B61" s="140"/>
       <c r="S61" s="141"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="163"/>
+      <c r="A62" s="219"/>
       <c r="B62" s="140"/>
       <c r="S62" s="141"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="163"/>
+      <c r="A63" s="219"/>
       <c r="B63" s="140"/>
       <c r="S63" s="141"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="163"/>
+      <c r="A64" s="219"/>
       <c r="B64" s="140"/>
       <c r="S64" s="141"/>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="163"/>
+      <c r="A65" s="219"/>
       <c r="B65" s="140"/>
       <c r="S65" s="141"/>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="163"/>
+      <c r="A66" s="219"/>
       <c r="B66" s="140"/>
       <c r="S66" s="141"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="163"/>
+      <c r="A67" s="219"/>
       <c r="B67" s="140"/>
       <c r="S67" s="141"/>
     </row>
     <row r="68" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A68" s="164"/>
+      <c r="A68" s="220"/>
       <c r="B68" s="142"/>
       <c r="C68" s="77"/>
       <c r="D68" s="77"/>
@@ -5708,31 +5708,6 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="F43:R43"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A68"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A36:A38"/>
@@ -5749,6 +5724,31 @@
     <mergeCell ref="O47:P48"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="F47:F48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L9:M9"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12380,10 +12380,13 @@
         <v>/</v>
       </c>
       <c r="L2" t="str">
-        <f t="shared" ref="L2:L23" si="1">IFERROR(
+        <f>IFERROR(
 IF(
 ISNUMBER(SEARCH("2461LT",A2)),
 "Rehau 2461LT",
+IF(
+ISNUMBER(SEARCH("2461L",A2)),
+"Rehau 2461L",
 IF(
 ISNUMBER(SEARCH("3146L",A2)),
 "Rehau 3146L",
@@ -12397,7 +12400,7 @@
 )
 )
 )
-),
+)),
 "")</f>
         <v/>
       </c>
@@ -12408,11 +12411,11 @@
     </row>
     <row r="3" spans="1:13">
       <c r="H3" t="str">
-        <f t="shared" ref="H3:H23" si="2">RIGHT(A3,3)</f>
+        <f t="shared" ref="H3:H23" si="1">RIGHT(A3,3)</f>
         <v/>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I23" si="3">ROUNDUP(E3*1.03,0)</f>
+        <f t="shared" ref="I3:I23" si="2">ROUNDUP(E3*1.03,0)</f>
         <v>0</v>
       </c>
       <c r="J3" t="str">
@@ -12420,7 +12423,28 @@
         <v>/</v>
       </c>
       <c r="L3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="L3:L23" si="3">IFERROR(
+IF(
+ISNUMBER(SEARCH("2461LT",A3)),
+"Rehau 2461LT",
+IF(
+ISNUMBER(SEARCH("2461L",A3)),
+"Rehau 2461L",
+IF(
+ISNUMBER(SEARCH("3146L",A3)),
+"Rehau 3146L",
+IF(
+ISNUMBER(SEARCH("1918L",A3)),
+"Rehau 1918L",
+IF(
+ISNUMBER(VALUE(MID(A3,FIND("-",A3)+1,1))),
+"AGT "&amp;TRIM(MID(A3,FIND("-",A3)+1,FIND("@",SUBSTITUTE(A3,"-","@",LEN(A3)-LEN(SUBSTITUTE(A3,"-",""))))-FIND("-",A3)-1)),
+TRIM(MID(A3,FIND("-",A3)+1,FIND("@",SUBSTITUTE(A3,"-","@",LEN(A3)-LEN(SUBSTITUTE(A3,"-",""))))-FIND("-",A3)-1))
+)
+)
+)
+)),
+"")</f>
         <v/>
       </c>
       <c r="M3" t="str">
@@ -12430,11 +12454,11 @@
     </row>
     <row r="4" spans="1:13">
       <c r="H4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J4" t="str">
@@ -12442,7 +12466,7 @@
         <v>/</v>
       </c>
       <c r="L4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M4" t="str">
@@ -12452,11 +12476,11 @@
     </row>
     <row r="5" spans="1:13">
       <c r="H5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J5" t="str">
@@ -12464,25 +12488,7 @@
         <v>/</v>
       </c>
       <c r="L5" t="str">
-        <f>IFERROR(
-IF(
-ISNUMBER(SEARCH("2461LT",A5)),
-"Rehau 2461LT",
-IF(
-ISNUMBER(SEARCH("3146L",A5)),
-"Rehau 3146L",
-IF(
-ISNUMBER(SEARCH("1918L",A5)),
-"Rehau 1918L",
-IF(
-ISNUMBER(VALUE(MID(A5,FIND("-",A5)+1,1))),
-"AGT "&amp;TRIM(MID(A5,FIND("-",A5)+1,FIND("@",SUBSTITUTE(A5,"-","@",LEN(A5)-LEN(SUBSTITUTE(A5,"-",""))))-FIND("-",A5)-1)),
-TRIM(MID(A5,FIND("-",A5)+1,FIND("@",SUBSTITUTE(A5,"-","@",LEN(A5)-LEN(SUBSTITUTE(A5,"-",""))))-FIND("-",A5)-1))
-)
-)
-)
-),
-"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M5" t="str">
@@ -12492,11 +12498,11 @@
     </row>
     <row r="6" spans="1:13">
       <c r="H6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J6" t="str">
@@ -12504,7 +12510,7 @@
         <v>/</v>
       </c>
       <c r="L6" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M6" t="str">
@@ -12514,11 +12520,11 @@
     </row>
     <row r="7" spans="1:13">
       <c r="H7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J7" t="str">
@@ -12526,7 +12532,7 @@
         <v>/</v>
       </c>
       <c r="L7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M7" t="str">
@@ -12536,11 +12542,11 @@
     </row>
     <row r="8" spans="1:13">
       <c r="H8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J8" t="str">
@@ -12548,7 +12554,7 @@
         <v>/</v>
       </c>
       <c r="L8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M8" t="str">
@@ -12558,11 +12564,11 @@
     </row>
     <row r="9" spans="1:13">
       <c r="H9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J9" t="str">
@@ -12570,7 +12576,7 @@
         <v>/</v>
       </c>
       <c r="L9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M9" t="str">
@@ -12580,11 +12586,11 @@
     </row>
     <row r="10" spans="1:13">
       <c r="H10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J10" t="str">
@@ -12592,7 +12598,7 @@
         <v>/</v>
       </c>
       <c r="L10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M10" t="str">
@@ -12602,11 +12608,11 @@
     </row>
     <row r="11" spans="1:13">
       <c r="H11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J11" t="str">
@@ -12614,7 +12620,7 @@
         <v>/</v>
       </c>
       <c r="L11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M11" t="str">
@@ -12629,11 +12635,11 @@
       <c r="D12" s="105"/>
       <c r="E12" s="106"/>
       <c r="H12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J12" t="str">
@@ -12641,7 +12647,7 @@
         <v>/</v>
       </c>
       <c r="L12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M12" t="str">
@@ -12656,11 +12662,11 @@
       <c r="D13" s="105"/>
       <c r="E13" s="106"/>
       <c r="H13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J13" t="str">
@@ -12668,7 +12674,7 @@
         <v>/</v>
       </c>
       <c r="L13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M13" t="str">
@@ -12683,11 +12689,11 @@
       <c r="D14" s="105"/>
       <c r="E14" s="106"/>
       <c r="H14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J14" t="str">
@@ -12695,7 +12701,7 @@
         <v>/</v>
       </c>
       <c r="L14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M14" t="str">
@@ -12710,11 +12716,11 @@
       <c r="D15" s="116"/>
       <c r="E15" s="116"/>
       <c r="H15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J15" t="str">
@@ -12722,7 +12728,7 @@
         <v>/</v>
       </c>
       <c r="L15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M15" t="str">
@@ -12736,7 +12742,7 @@
         <v/>
       </c>
       <c r="I16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J16" t="str">
@@ -12744,7 +12750,7 @@
         <v>/</v>
       </c>
       <c r="L16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M16" t="str">
@@ -12754,11 +12760,11 @@
     </row>
     <row r="17" spans="8:13">
       <c r="H17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J17" t="str">
@@ -12766,7 +12772,7 @@
         <v>/</v>
       </c>
       <c r="L17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M17" t="str">
@@ -12776,11 +12782,11 @@
     </row>
     <row r="18" spans="8:13">
       <c r="H18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J18" t="str">
@@ -12788,7 +12794,7 @@
         <v>/</v>
       </c>
       <c r="L18" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M18" t="str">
@@ -12798,11 +12804,11 @@
     </row>
     <row r="19" spans="8:13">
       <c r="H19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J19" t="str">
@@ -12810,7 +12816,7 @@
         <v>/</v>
       </c>
       <c r="L19" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M19" t="str">
@@ -12820,11 +12826,11 @@
     </row>
     <row r="20" spans="8:13">
       <c r="H20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J20" t="str">
@@ -12832,7 +12838,7 @@
         <v>/</v>
       </c>
       <c r="L20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M20" t="str">
@@ -12842,11 +12848,11 @@
     </row>
     <row r="21" spans="8:13">
       <c r="H21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J21" t="str">
@@ -12854,7 +12860,7 @@
         <v>/</v>
       </c>
       <c r="L21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M21" t="str">
@@ -12864,11 +12870,11 @@
     </row>
     <row r="22" spans="8:13">
       <c r="H22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J22" t="str">
@@ -12876,7 +12882,7 @@
         <v>/</v>
       </c>
       <c r="L22" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M22" t="str">
@@ -12886,11 +12892,11 @@
     </row>
     <row r="23" spans="8:13">
       <c r="H23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J23" t="str">
@@ -12898,7 +12904,7 @@
         <v>/</v>
       </c>
       <c r="L23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M23" t="str">
